--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="293">
   <si>
     <t>subsector</t>
   </si>
@@ -45,6 +45,174 @@
   </si>
   <si>
     <t>min_55</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t>Liquid Waste</t>
@@ -1117,181 +1285,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1470,10 +1638,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1652,10 +1820,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1834,10 +2002,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -2016,10 +2184,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>58</v>
@@ -2201,10 +2369,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>58</v>
@@ -2386,10 +2554,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C8">
         <v>58</v>
@@ -2571,10 +2739,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>58</v>
@@ -2756,10 +2924,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="C10">
         <v>58</v>
@@ -2941,10 +3109,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C11">
         <v>58</v>
@@ -3126,10 +3294,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -3311,10 +3479,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>58</v>
@@ -3496,10 +3664,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>58</v>
@@ -3681,10 +3849,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="C15">
         <v>58</v>
@@ -3866,10 +4034,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>59</v>
@@ -4051,10 +4219,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>59</v>
@@ -4236,10 +4404,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>59</v>
@@ -4421,10 +4589,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="C19">
         <v>59</v>
@@ -4606,10 +4774,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="C20">
         <v>59</v>
@@ -4791,10 +4959,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C21">
         <v>59</v>
@@ -4976,10 +5144,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>59</v>
@@ -5161,10 +5329,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="C23">
         <v>59</v>
@@ -5346,10 +5514,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>59</v>
@@ -5531,10 +5699,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="C25">
         <v>59</v>
@@ -5716,10 +5884,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C26">
         <v>60</v>
@@ -5901,10 +6069,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>60</v>
@@ -6086,10 +6254,10 @@
     </row>
     <row r="28" spans="1:65">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>60</v>
@@ -6271,10 +6439,10 @@
     </row>
     <row r="29" spans="1:65">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C29">
         <v>60</v>
@@ -6456,10 +6624,10 @@
     </row>
     <row r="30" spans="1:65">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="C30">
         <v>60</v>
@@ -6641,10 +6809,10 @@
     </row>
     <row r="31" spans="1:65">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C31">
         <v>60</v>
@@ -6826,10 +6994,10 @@
     </row>
     <row r="32" spans="1:65">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C32">
         <v>60</v>
@@ -7011,10 +7179,10 @@
     </row>
     <row r="33" spans="1:65">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="C33">
         <v>60</v>
@@ -7196,10 +7364,10 @@
     </row>
     <row r="34" spans="1:65">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>60</v>
@@ -7381,10 +7549,10 @@
     </row>
     <row r="35" spans="1:65">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="C35">
         <v>60</v>
@@ -7566,10 +7734,10 @@
     </row>
     <row r="36" spans="1:65">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -7748,10 +7916,10 @@
     </row>
     <row r="37" spans="1:65">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -7930,10 +8098,10 @@
     </row>
     <row r="38" spans="1:65">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -8112,10 +8280,10 @@
     </row>
     <row r="39" spans="1:65">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -8294,10 +8462,10 @@
     </row>
     <row r="40" spans="1:65">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -8476,10 +8644,10 @@
     </row>
     <row r="41" spans="1:65">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -8658,10 +8826,10 @@
     </row>
     <row r="42" spans="1:65">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -8840,10 +9008,10 @@
     </row>
     <row r="43" spans="1:65">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -9022,10 +9190,10 @@
     </row>
     <row r="44" spans="1:65">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -9204,10 +9372,10 @@
     </row>
     <row r="45" spans="1:65">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -9386,10 +9554,10 @@
     </row>
     <row r="46" spans="1:65">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -9568,10 +9736,10 @@
     </row>
     <row r="47" spans="1:65">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -9750,10 +9918,10 @@
     </row>
     <row r="48" spans="1:65">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -9932,10 +10100,10 @@
     </row>
     <row r="49" spans="1:65">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -10114,10 +10282,10 @@
     </row>
     <row r="50" spans="1:65">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -10296,10 +10464,10 @@
     </row>
     <row r="51" spans="1:65">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -10478,10 +10646,10 @@
     </row>
     <row r="52" spans="1:65">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -10660,10 +10828,10 @@
     </row>
     <row r="53" spans="1:65">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -10842,10 +11010,10 @@
     </row>
     <row r="54" spans="1:65">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -11024,10 +11192,10 @@
     </row>
     <row r="55" spans="1:65">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -11206,10 +11374,10 @@
     </row>
     <row r="56" spans="1:65">
       <c r="A56" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -11388,10 +11556,10 @@
     </row>
     <row r="57" spans="1:65">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -11570,10 +11738,10 @@
     </row>
     <row r="58" spans="1:65">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -11752,10 +11920,10 @@
     </row>
     <row r="59" spans="1:65">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -11934,10 +12102,10 @@
     </row>
     <row r="60" spans="1:65">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -12116,10 +12284,10 @@
     </row>
     <row r="61" spans="1:65">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -12298,10 +12466,10 @@
     </row>
     <row r="62" spans="1:65">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -12480,10 +12648,10 @@
     </row>
     <row r="63" spans="1:65">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -12662,10 +12830,10 @@
     </row>
     <row r="64" spans="1:65">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -12844,10 +13012,10 @@
     </row>
     <row r="65" spans="1:65">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -13026,10 +13194,10 @@
     </row>
     <row r="66" spans="1:65">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -13208,10 +13376,10 @@
     </row>
     <row r="67" spans="1:65">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -13390,10 +13558,10 @@
     </row>
     <row r="68" spans="1:65">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -13572,10 +13740,10 @@
     </row>
     <row r="69" spans="1:65">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -13754,10 +13922,10 @@
     </row>
     <row r="70" spans="1:65">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -13936,10 +14104,10 @@
     </row>
     <row r="71" spans="1:65">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -14118,10 +14286,10 @@
     </row>
     <row r="72" spans="1:65">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -14300,10 +14468,10 @@
     </row>
     <row r="73" spans="1:65">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -14482,10 +14650,10 @@
     </row>
     <row r="74" spans="1:65">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -14664,10 +14832,10 @@
     </row>
     <row r="75" spans="1:65">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -14846,10 +15014,10 @@
     </row>
     <row r="76" spans="1:65">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -15028,10 +15196,10 @@
     </row>
     <row r="77" spans="1:65">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -15210,10 +15378,10 @@
     </row>
     <row r="78" spans="1:65">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -15392,10 +15560,10 @@
     </row>
     <row r="79" spans="1:65">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -15574,10 +15742,10 @@
     </row>
     <row r="80" spans="1:65">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -15756,10 +15924,10 @@
     </row>
     <row r="81" spans="1:65">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -15938,10 +16106,10 @@
     </row>
     <row r="82" spans="1:65">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -16120,10 +16288,10 @@
     </row>
     <row r="83" spans="1:65">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -16302,10 +16470,10 @@
     </row>
     <row r="84" spans="1:65">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -16484,10 +16652,10 @@
     </row>
     <row r="85" spans="1:65">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -16666,10 +16834,10 @@
     </row>
     <row r="86" spans="1:65">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -16848,10 +17016,10 @@
     </row>
     <row r="87" spans="1:65">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -17030,10 +17198,10 @@
     </row>
     <row r="88" spans="1:65">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -17212,10 +17380,10 @@
     </row>
     <row r="89" spans="1:65">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -17394,10 +17562,10 @@
     </row>
     <row r="90" spans="1:65">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -17576,10 +17744,10 @@
     </row>
     <row r="91" spans="1:65">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -17758,10 +17926,10 @@
     </row>
     <row r="92" spans="1:65">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -17940,10 +18108,10 @@
     </row>
     <row r="93" spans="1:65">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B93" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -18122,10 +18290,10 @@
     </row>
     <row r="94" spans="1:65">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B94" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -18304,10 +18472,10 @@
     </row>
     <row r="95" spans="1:65">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -18486,10 +18654,10 @@
     </row>
     <row r="96" spans="1:65">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B96" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -18668,10 +18836,10 @@
     </row>
     <row r="97" spans="1:65">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -18850,10 +19018,10 @@
     </row>
     <row r="98" spans="1:65">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -19032,10 +19200,10 @@
     </row>
     <row r="99" spans="1:65">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -19214,10 +19382,10 @@
     </row>
     <row r="100" spans="1:65">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B100" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -19396,10 +19564,10 @@
     </row>
     <row r="101" spans="1:65">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -19578,10 +19746,10 @@
     </row>
     <row r="102" spans="1:65">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B102" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -19760,10 +19928,10 @@
     </row>
     <row r="103" spans="1:65">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B103" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -19942,10 +20110,10 @@
     </row>
     <row r="104" spans="1:65">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -20124,10 +20292,10 @@
     </row>
     <row r="105" spans="1:65">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -20306,10 +20474,10 @@
     </row>
     <row r="106" spans="1:65">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -20488,10 +20656,10 @@
     </row>
     <row r="107" spans="1:65">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="C107">
         <v>61</v>
@@ -20673,10 +20841,10 @@
     </row>
     <row r="108" spans="1:65">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="C108">
         <v>61</v>
@@ -20858,10 +21026,10 @@
     </row>
     <row r="109" spans="1:65">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B109" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="C109">
         <v>61</v>
@@ -21043,10 +21211,10 @@
     </row>
     <row r="110" spans="1:65">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="C110">
         <v>61</v>
@@ -21228,10 +21396,10 @@
     </row>
     <row r="111" spans="1:65">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="C111">
         <v>61</v>
@@ -21413,10 +21581,10 @@
     </row>
     <row r="112" spans="1:65">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B112" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="C112">
         <v>61</v>
@@ -21598,10 +21766,10 @@
     </row>
     <row r="113" spans="1:65">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="C113">
         <v>61</v>
@@ -21783,10 +21951,10 @@
     </row>
     <row r="114" spans="1:65">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="C114">
         <v>61</v>
@@ -21968,10 +22136,10 @@
     </row>
     <row r="115" spans="1:65">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="C115">
         <v>61</v>
@@ -22153,10 +22321,10 @@
     </row>
     <row r="116" spans="1:65">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="C116">
         <v>61</v>
@@ -22338,10 +22506,10 @@
     </row>
     <row r="117" spans="1:65">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="C117">
         <v>61</v>
@@ -22523,10 +22691,10 @@
     </row>
     <row r="118" spans="1:65">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C118">
         <v>61</v>
@@ -22708,10 +22876,10 @@
     </row>
     <row r="119" spans="1:65">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B119" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="C119">
         <v>61</v>
@@ -22893,10 +23061,10 @@
     </row>
     <row r="120" spans="1:65">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="C120">
         <v>62</v>
@@ -23078,10 +23246,10 @@
     </row>
     <row r="121" spans="1:65">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="C121">
         <v>62</v>
@@ -23263,10 +23431,10 @@
     </row>
     <row r="122" spans="1:65">
       <c r="A122" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="C122">
         <v>62</v>
@@ -23448,10 +23616,10 @@
     </row>
     <row r="123" spans="1:65">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B123" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="C123">
         <v>62</v>
@@ -23633,10 +23801,10 @@
     </row>
     <row r="124" spans="1:65">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="C124">
         <v>62</v>
@@ -23818,10 +23986,10 @@
     </row>
     <row r="125" spans="1:65">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="C125">
         <v>62</v>
@@ -24003,10 +24171,10 @@
     </row>
     <row r="126" spans="1:65">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="C126">
         <v>62</v>
@@ -24188,10 +24356,10 @@
     </row>
     <row r="127" spans="1:65">
       <c r="A127" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="C127">
         <v>62</v>
@@ -24373,10 +24541,10 @@
     </row>
     <row r="128" spans="1:65">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="C128">
         <v>62</v>
@@ -24558,10 +24726,10 @@
     </row>
     <row r="129" spans="1:65">
       <c r="A129" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="C129">
         <v>62</v>
@@ -24743,10 +24911,10 @@
     </row>
     <row r="130" spans="1:65">
       <c r="A130" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="C130">
         <v>62</v>
@@ -24928,10 +25096,10 @@
     </row>
     <row r="131" spans="1:65">
       <c r="A131" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B131" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="C131">
         <v>62</v>
@@ -25113,10 +25281,10 @@
     </row>
     <row r="132" spans="1:65">
       <c r="A132" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B132" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="C132">
         <v>62</v>
@@ -25298,10 +25466,10 @@
     </row>
     <row r="133" spans="1:65">
       <c r="A133" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -25480,10 +25648,10 @@
     </row>
     <row r="134" spans="1:65">
       <c r="A134" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -25662,10 +25830,10 @@
     </row>
     <row r="135" spans="1:65">
       <c r="A135" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -25844,10 +26012,10 @@
     </row>
     <row r="136" spans="1:65">
       <c r="A136" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -26026,10 +26194,10 @@
     </row>
     <row r="137" spans="1:65">
       <c r="A137" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="C137">
         <v>63</v>
@@ -26211,10 +26379,10 @@
     </row>
     <row r="138" spans="1:65">
       <c r="A138" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B138" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C138">
         <v>63</v>
@@ -26396,10 +26564,10 @@
     </row>
     <row r="139" spans="1:65">
       <c r="A139" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B139" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="C139">
         <v>63</v>
@@ -26581,10 +26749,10 @@
     </row>
     <row r="140" spans="1:65">
       <c r="A140" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B140" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -26763,10 +26931,10 @@
     </row>
     <row r="141" spans="1:65">
       <c r="A141" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -26945,10 +27113,10 @@
     </row>
     <row r="142" spans="1:65">
       <c r="A142" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -27127,10 +27295,10 @@
     </row>
     <row r="143" spans="1:65">
       <c r="A143" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -27309,10 +27477,10 @@
     </row>
     <row r="144" spans="1:65">
       <c r="A144" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -27491,10 +27659,10 @@
     </row>
     <row r="145" spans="1:65">
       <c r="A145" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -27673,10 +27841,10 @@
     </row>
     <row r="146" spans="1:65">
       <c r="A146" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B146" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -27855,10 +28023,10 @@
     </row>
     <row r="147" spans="1:65">
       <c r="A147" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -28037,10 +28205,10 @@
     </row>
     <row r="148" spans="1:65">
       <c r="A148" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -28219,10 +28387,10 @@
     </row>
     <row r="149" spans="1:65">
       <c r="A149" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -28401,10 +28569,10 @@
     </row>
     <row r="150" spans="1:65">
       <c r="A150" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B150" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -28583,10 +28751,10 @@
     </row>
     <row r="151" spans="1:65">
       <c r="A151" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B151" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -28765,10 +28933,10 @@
     </row>
     <row r="152" spans="1:65">
       <c r="A152" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B152" t="s">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -28947,10 +29115,10 @@
     </row>
     <row r="153" spans="1:65">
       <c r="A153" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -29129,10 +29297,10 @@
     </row>
     <row r="154" spans="1:65">
       <c r="A154" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -29311,10 +29479,10 @@
     </row>
     <row r="155" spans="1:65">
       <c r="A155" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B155" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -29493,10 +29661,10 @@
     </row>
     <row r="156" spans="1:65">
       <c r="A156" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B156" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -29675,10 +29843,10 @@
     </row>
     <row r="157" spans="1:65">
       <c r="A157" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>223</v>
       </c>
       <c r="H157">
         <v>1</v>
@@ -29857,10 +30025,10 @@
     </row>
     <row r="158" spans="1:65">
       <c r="A158" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B158" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -30039,10 +30207,10 @@
     </row>
     <row r="159" spans="1:65">
       <c r="A159" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B159" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -30221,10 +30389,10 @@
     </row>
     <row r="160" spans="1:65">
       <c r="A160" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B160" t="s">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="H160">
         <v>1</v>
@@ -30403,10 +30571,10 @@
     </row>
     <row r="161" spans="1:65">
       <c r="A161" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B161" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -30585,10 +30753,10 @@
     </row>
     <row r="162" spans="1:65">
       <c r="A162" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B162" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -30767,10 +30935,10 @@
     </row>
     <row r="163" spans="1:65">
       <c r="A163" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B163" t="s">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="H163">
         <v>1</v>
@@ -30949,10 +31117,10 @@
     </row>
     <row r="164" spans="1:65">
       <c r="A164" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B164" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -31131,10 +31299,10 @@
     </row>
     <row r="165" spans="1:65">
       <c r="A165" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B165" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -31313,10 +31481,10 @@
     </row>
     <row r="166" spans="1:65">
       <c r="A166" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B166" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -31495,10 +31663,10 @@
     </row>
     <row r="167" spans="1:65">
       <c r="A167" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B167" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="H167">
         <v>1</v>
@@ -31677,10 +31845,10 @@
     </row>
     <row r="168" spans="1:65">
       <c r="A168" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B168" t="s">
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -31859,10 +32027,10 @@
     </row>
     <row r="169" spans="1:65">
       <c r="A169" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B169" t="s">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -32041,10 +32209,10 @@
     </row>
     <row r="170" spans="1:65">
       <c r="A170" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B170" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="H170">
         <v>1</v>
@@ -32223,10 +32391,10 @@
     </row>
     <row r="171" spans="1:65">
       <c r="A171" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B171" t="s">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -32405,10 +32573,10 @@
     </row>
     <row r="172" spans="1:65">
       <c r="A172" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B172" t="s">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -32587,10 +32755,10 @@
     </row>
     <row r="173" spans="1:65">
       <c r="A173" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B173" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="H173">
         <v>1</v>
@@ -32769,10 +32937,10 @@
     </row>
     <row r="174" spans="1:65">
       <c r="A174" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B174" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -32951,10 +33119,10 @@
     </row>
     <row r="175" spans="1:65">
       <c r="A175" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B175" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="H175">
         <v>1</v>
@@ -33133,10 +33301,10 @@
     </row>
     <row r="176" spans="1:65">
       <c r="A176" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B176" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="H176">
         <v>1</v>
@@ -33315,10 +33483,10 @@
     </row>
     <row r="177" spans="1:65">
       <c r="A177" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B177" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -33497,10 +33665,10 @@
     </row>
     <row r="178" spans="1:65">
       <c r="A178" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B178" t="s">
-        <v>188</v>
+        <v>244</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -33679,10 +33847,10 @@
     </row>
     <row r="179" spans="1:65">
       <c r="A179" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B179" t="s">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="H179">
         <v>1</v>
@@ -33861,10 +34029,10 @@
     </row>
     <row r="180" spans="1:65">
       <c r="A180" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B180" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -34043,10 +34211,10 @@
     </row>
     <row r="181" spans="1:65">
       <c r="A181" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B181" t="s">
-        <v>191</v>
+        <v>247</v>
       </c>
       <c r="H181">
         <v>1</v>
@@ -34225,10 +34393,10 @@
     </row>
     <row r="182" spans="1:65">
       <c r="A182" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B182" t="s">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -34407,10 +34575,10 @@
     </row>
     <row r="183" spans="1:65">
       <c r="A183" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B183" t="s">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="H183">
         <v>1</v>
@@ -34589,10 +34757,10 @@
     </row>
     <row r="184" spans="1:65">
       <c r="A184" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B184" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="H184">
         <v>1</v>
@@ -34771,10 +34939,10 @@
     </row>
     <row r="185" spans="1:65">
       <c r="A185" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B185" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="H185">
         <v>1</v>
@@ -34953,10 +35121,10 @@
     </row>
     <row r="186" spans="1:65">
       <c r="A186" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B186" t="s">
-        <v>196</v>
+        <v>252</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -35135,10 +35303,10 @@
     </row>
     <row r="187" spans="1:65">
       <c r="A187" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B187" t="s">
-        <v>197</v>
+        <v>253</v>
       </c>
       <c r="H187">
         <v>1</v>
@@ -35317,10 +35485,10 @@
     </row>
     <row r="188" spans="1:65">
       <c r="A188" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B188" t="s">
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -35499,10 +35667,10 @@
     </row>
     <row r="189" spans="1:65">
       <c r="A189" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B189" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="H189">
         <v>1</v>
@@ -35681,10 +35849,10 @@
     </row>
     <row r="190" spans="1:65">
       <c r="A190" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B190" t="s">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="H190">
         <v>1</v>
@@ -35863,10 +36031,10 @@
     </row>
     <row r="191" spans="1:65">
       <c r="A191" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B191" t="s">
-        <v>201</v>
+        <v>257</v>
       </c>
       <c r="H191">
         <v>1</v>
@@ -36045,10 +36213,10 @@
     </row>
     <row r="192" spans="1:65">
       <c r="A192" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B192" t="s">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="H192">
         <v>1</v>
@@ -36227,10 +36395,10 @@
     </row>
     <row r="193" spans="1:65">
       <c r="A193" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="H193">
         <v>1</v>
@@ -36409,10 +36577,10 @@
     </row>
     <row r="194" spans="1:65">
       <c r="A194" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B194" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="H194">
         <v>1</v>
@@ -36591,10 +36759,10 @@
     </row>
     <row r="195" spans="1:65">
       <c r="A195" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B195" t="s">
-        <v>205</v>
+        <v>261</v>
       </c>
       <c r="H195">
         <v>1</v>
@@ -36773,10 +36941,10 @@
     </row>
     <row r="196" spans="1:65">
       <c r="A196" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B196" t="s">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="H196">
         <v>1</v>
@@ -36955,10 +37123,10 @@
     </row>
     <row r="197" spans="1:65">
       <c r="A197" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B197" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
       <c r="H197">
         <v>1</v>
@@ -37137,10 +37305,10 @@
     </row>
     <row r="198" spans="1:65">
       <c r="A198" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B198" t="s">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="H198">
         <v>1</v>
@@ -37319,10 +37487,10 @@
     </row>
     <row r="199" spans="1:65">
       <c r="A199" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B199" t="s">
-        <v>209</v>
+        <v>265</v>
       </c>
       <c r="H199">
         <v>1</v>
@@ -37501,10 +37669,10 @@
     </row>
     <row r="200" spans="1:65">
       <c r="A200" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B200" t="s">
-        <v>210</v>
+        <v>266</v>
       </c>
       <c r="H200">
         <v>1</v>
@@ -37683,10 +37851,10 @@
     </row>
     <row r="201" spans="1:65">
       <c r="A201" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B201" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="H201">
         <v>1</v>
@@ -37865,10 +38033,10 @@
     </row>
     <row r="202" spans="1:65">
       <c r="A202" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B202" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="H202">
         <v>1</v>
@@ -38047,10 +38215,10 @@
     </row>
     <row r="203" spans="1:65">
       <c r="A203" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B203" t="s">
-        <v>213</v>
+        <v>269</v>
       </c>
       <c r="H203">
         <v>1</v>
@@ -38229,10 +38397,10 @@
     </row>
     <row r="204" spans="1:65">
       <c r="A204" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B204" t="s">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="H204">
         <v>1</v>
@@ -38411,10 +38579,10 @@
     </row>
     <row r="205" spans="1:65">
       <c r="A205" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B205" t="s">
-        <v>215</v>
+        <v>271</v>
       </c>
       <c r="H205">
         <v>1</v>
@@ -38593,10 +38761,10 @@
     </row>
     <row r="206" spans="1:65">
       <c r="A206" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B206" t="s">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="H206">
         <v>1</v>
@@ -38775,10 +38943,10 @@
     </row>
     <row r="207" spans="1:65">
       <c r="A207" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B207" t="s">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="H207">
         <v>1</v>
@@ -38957,10 +39125,10 @@
     </row>
     <row r="208" spans="1:65">
       <c r="A208" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B208" t="s">
-        <v>218</v>
+        <v>274</v>
       </c>
       <c r="H208">
         <v>1</v>
@@ -39139,10 +39307,10 @@
     </row>
     <row r="209" spans="1:65">
       <c r="A209" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B209" t="s">
-        <v>219</v>
+        <v>275</v>
       </c>
       <c r="H209">
         <v>1</v>
@@ -39321,10 +39489,10 @@
     </row>
     <row r="210" spans="1:65">
       <c r="A210" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B210" t="s">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="H210">
         <v>1</v>
@@ -39503,10 +39671,10 @@
     </row>
     <row r="211" spans="1:65">
       <c r="A211" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B211" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -39685,10 +39853,10 @@
     </row>
     <row r="212" spans="1:65">
       <c r="A212" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B212" t="s">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -39867,10 +40035,10 @@
     </row>
     <row r="213" spans="1:65">
       <c r="A213" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B213" t="s">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -40049,10 +40217,10 @@
     </row>
     <row r="214" spans="1:65">
       <c r="A214" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B214" t="s">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -40231,10 +40399,10 @@
     </row>
     <row r="215" spans="1:65">
       <c r="A215" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B215" t="s">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="H215">
         <v>1</v>
@@ -40413,10 +40581,10 @@
     </row>
     <row r="216" spans="1:65">
       <c r="A216" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B216" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="H216">
         <v>1</v>
@@ -40595,10 +40763,10 @@
     </row>
     <row r="217" spans="1:65">
       <c r="A217" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B217" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="H217">
         <v>1</v>
@@ -40777,10 +40945,10 @@
     </row>
     <row r="218" spans="1:65">
       <c r="A218" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B218" t="s">
-        <v>228</v>
+        <v>284</v>
       </c>
       <c r="H218">
         <v>1</v>
@@ -40959,10 +41127,10 @@
     </row>
     <row r="219" spans="1:65">
       <c r="A219" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B219" t="s">
-        <v>229</v>
+        <v>285</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -41141,10 +41309,10 @@
     </row>
     <row r="220" spans="1:65">
       <c r="A220" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B220" t="s">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="H220">
         <v>1</v>
@@ -41323,10 +41491,10 @@
     </row>
     <row r="221" spans="1:65">
       <c r="A221" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B221" t="s">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="H221">
         <v>1</v>
@@ -41505,10 +41673,10 @@
     </row>
     <row r="222" spans="1:65">
       <c r="A222" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B222" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="H222">
         <v>1</v>
@@ -41687,10 +41855,10 @@
     </row>
     <row r="223" spans="1:65">
       <c r="A223" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B223" t="s">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="H223">
         <v>1</v>
@@ -41869,10 +42037,10 @@
     </row>
     <row r="224" spans="1:65">
       <c r="A224" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B224" t="s">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="H224">
         <v>1</v>
@@ -42051,10 +42219,10 @@
     </row>
     <row r="225" spans="1:65">
       <c r="A225" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B225" t="s">
-        <v>235</v>
+        <v>291</v>
       </c>
       <c r="H225">
         <v>1</v>
@@ -42233,10 +42401,10 @@
     </row>
     <row r="226" spans="1:65">
       <c r="A226" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B226" t="s">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="H226">
         <v>1</v>
@@ -42451,181 +42619,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>58</v>
@@ -42807,10 +42975,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>58</v>
@@ -42992,10 +43160,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C4">
         <v>59</v>
@@ -43177,10 +43345,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>59</v>
@@ -43362,10 +43530,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>59</v>
@@ -43547,10 +43715,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>59</v>
@@ -43732,10 +43900,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>59</v>
@@ -43917,10 +44085,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -44102,10 +44270,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>60</v>
@@ -44287,10 +44455,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -44472,10 +44640,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -44657,10 +44825,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -44839,10 +45007,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -45021,10 +45189,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -45203,10 +45371,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -45385,10 +45553,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -45567,10 +45735,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -45749,10 +45917,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -45931,10 +46099,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -46113,10 +46281,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -46295,10 +46463,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -46477,10 +46645,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -46659,10 +46827,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C24">
         <v>63</v>
@@ -46844,10 +47012,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="C25">
         <v>63</v>
@@ -47029,10 +47197,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -47211,10 +47379,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -47393,10 +47561,10 @@
     </row>
     <row r="28" spans="1:65">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -47575,10 +47743,10 @@
     </row>
     <row r="29" spans="1:65">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -47757,10 +47925,10 @@
     </row>
     <row r="30" spans="1:65">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -47939,10 +48107,10 @@
     </row>
     <row r="31" spans="1:65">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -48121,10 +48289,10 @@
     </row>
     <row r="32" spans="1:65">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -48303,10 +48471,10 @@
     </row>
     <row r="33" spans="1:65">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -48485,10 +48653,10 @@
     </row>
     <row r="34" spans="1:65">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -48667,10 +48835,10 @@
     </row>
     <row r="35" spans="1:65">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -48849,10 +49017,10 @@
     </row>
     <row r="36" spans="1:65">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -49031,10 +49199,10 @@
     </row>
     <row r="37" spans="1:65">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -49213,10 +49381,10 @@
     </row>
     <row r="38" spans="1:65">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -49431,181 +49599,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>58</v>
@@ -49787,10 +49955,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>58</v>
@@ -49972,10 +50140,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C4">
         <v>59</v>
@@ -50157,10 +50325,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>59</v>
@@ -50342,10 +50510,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>59</v>
@@ -50527,10 +50695,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>59</v>
@@ -50712,10 +50880,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>59</v>
@@ -50897,10 +51065,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -51082,10 +51250,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>60</v>
@@ -51267,10 +51435,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -51452,10 +51620,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -51637,10 +51805,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -51819,10 +51987,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -52001,10 +52169,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -52183,10 +52351,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -52365,10 +52533,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -52547,10 +52715,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C18">
         <v>63</v>
@@ -52732,10 +52900,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="C19">
         <v>63</v>
@@ -52917,10 +53085,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -53099,10 +53267,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -53281,10 +53449,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -53463,10 +53631,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -53645,10 +53813,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -53827,10 +53995,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -54009,10 +54177,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -54191,10 +54359,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -54409,181 +54577,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>58</v>
@@ -54765,10 +54933,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>58</v>
@@ -54950,10 +55118,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C4">
         <v>59</v>
@@ -55135,10 +55303,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>59</v>
@@ -55320,10 +55488,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>59</v>
@@ -55505,10 +55673,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>59</v>
@@ -55690,10 +55858,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>59</v>
@@ -55875,10 +56043,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -56060,10 +56228,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>60</v>
@@ -56245,10 +56413,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -56430,10 +56598,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -56615,10 +56783,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -56797,10 +56965,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -56979,10 +57147,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -57161,10 +57329,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -57343,10 +57511,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -57525,10 +57693,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -57707,10 +57875,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -57889,10 +58057,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -58071,10 +58239,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -58253,10 +58421,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -58435,10 +58603,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -58617,10 +58785,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C24">
         <v>63</v>
@@ -58802,10 +58970,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="C25">
         <v>63</v>
@@ -58987,10 +59155,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -59169,10 +59337,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -59351,10 +59519,10 @@
     </row>
     <row r="28" spans="1:65">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -59533,10 +59701,10 @@
     </row>
     <row r="29" spans="1:65">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -59715,10 +59883,10 @@
     </row>
     <row r="30" spans="1:65">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -59897,10 +60065,10 @@
     </row>
     <row r="31" spans="1:65">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -60079,10 +60247,10 @@
     </row>
     <row r="32" spans="1:65">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -60261,10 +60429,10 @@
     </row>
     <row r="33" spans="1:65">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -60443,10 +60611,10 @@
     </row>
     <row r="34" spans="1:65">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -60625,10 +60793,10 @@
     </row>
     <row r="35" spans="1:65">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -60807,10 +60975,10 @@
     </row>
     <row r="36" spans="1:65">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -60989,10 +61157,10 @@
     </row>
     <row r="37" spans="1:65">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -61171,10 +61339,10 @@
     </row>
     <row r="38" spans="1:65">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -61389,181 +61557,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>58</v>
@@ -61745,10 +61913,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>58</v>
@@ -61930,10 +62098,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C4">
         <v>59</v>
@@ -62115,10 +62283,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>59</v>
@@ -62300,10 +62468,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>59</v>
@@ -62485,10 +62653,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>59</v>
@@ -62670,10 +62838,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>59</v>
@@ -62855,10 +63023,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -63040,10 +63208,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>60</v>
@@ -63225,10 +63393,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -63410,10 +63578,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -63595,10 +63763,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -63777,10 +63945,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -63959,10 +64127,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -64141,10 +64309,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -64323,10 +64491,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -64505,10 +64673,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C18">
         <v>63</v>
@@ -64690,10 +64858,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="C19">
         <v>63</v>
@@ -64875,10 +65043,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -65057,10 +65225,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -65239,10 +65407,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -65421,10 +65589,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -65603,10 +65771,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -65785,10 +65953,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -65967,10 +66135,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H26">
         <v>1</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
@@ -43213,133 +43213,133 @@
         <v>0</v>
       </c>
       <c r="W4">
+        <v>0.002325581395348837</v>
+      </c>
+      <c r="X4">
+        <v>0.004651162790697674</v>
+      </c>
+      <c r="Y4">
         <v>0.006976744186046512</v>
       </c>
-      <c r="X4">
+      <c r="Z4">
+        <v>0.009302325581395349</v>
+      </c>
+      <c r="AA4">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="AB4">
         <v>0.01395348837209302</v>
       </c>
-      <c r="Y4">
-        <v>0.02093023255813953</v>
-      </c>
-      <c r="Z4">
+      <c r="AC4">
+        <v>0.01627906976744186</v>
+      </c>
+      <c r="AD4">
+        <v>0.0186046511627907</v>
+      </c>
+      <c r="AE4">
+        <v>0.02093023255813954</v>
+      </c>
+      <c r="AF4">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="AG4">
+        <v>0.02558139534883721</v>
+      </c>
+      <c r="AH4">
         <v>0.02790697674418605</v>
       </c>
-      <c r="AA4">
+      <c r="AI4">
+        <v>0.03023255813953488</v>
+      </c>
+      <c r="AJ4">
+        <v>0.03255813953488373</v>
+      </c>
+      <c r="AK4">
         <v>0.03488372093023256</v>
       </c>
-      <c r="AB4">
-        <v>0.04186046511627907</v>
-      </c>
-      <c r="AC4">
+      <c r="AL4">
+        <v>0.03720930232558139</v>
+      </c>
+      <c r="AM4">
+        <v>0.03953488372093023</v>
+      </c>
+      <c r="AN4">
+        <v>0.04186046511627908</v>
+      </c>
+      <c r="AO4">
+        <v>0.04418604651162791</v>
+      </c>
+      <c r="AP4">
+        <v>0.04651162790697674</v>
+      </c>
+      <c r="AQ4">
         <v>0.04883720930232558</v>
       </c>
-      <c r="AD4">
+      <c r="AR4">
+        <v>0.05116279069767442</v>
+      </c>
+      <c r="AS4">
+        <v>0.05348837209302326</v>
+      </c>
+      <c r="AT4">
         <v>0.05581395348837209</v>
       </c>
-      <c r="AE4">
+      <c r="AU4">
+        <v>0.05813953488372094</v>
+      </c>
+      <c r="AV4">
+        <v>0.06046511627906977</v>
+      </c>
+      <c r="AW4">
         <v>0.06279069767441861</v>
       </c>
-      <c r="AF4">
+      <c r="AX4">
+        <v>0.06511627906976745</v>
+      </c>
+      <c r="AY4">
+        <v>0.06744186046511629</v>
+      </c>
+      <c r="AZ4">
         <v>0.06976744186046512</v>
       </c>
-      <c r="AG4">
+      <c r="BA4">
+        <v>0.07209302325581395</v>
+      </c>
+      <c r="BB4">
+        <v>0.07441860465116279</v>
+      </c>
+      <c r="BC4">
         <v>0.07674418604651163</v>
       </c>
-      <c r="AH4">
-        <v>0.08372093023255814</v>
-      </c>
-      <c r="AI4">
-        <v>0.09069767441860464</v>
-      </c>
-      <c r="AJ4">
+      <c r="BD4">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="BE4">
+        <v>0.08139534883720931</v>
+      </c>
+      <c r="BF4">
+        <v>0.08372093023255815</v>
+      </c>
+      <c r="BG4">
+        <v>0.08604651162790698</v>
+      </c>
+      <c r="BH4">
+        <v>0.08837209302325583</v>
+      </c>
+      <c r="BI4">
+        <v>0.09069767441860466</v>
+      </c>
+      <c r="BJ4">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="BK4">
+        <v>0.09534883720930233</v>
+      </c>
+      <c r="BL4">
         <v>0.09767441860465116</v>
       </c>
-      <c r="AK4">
-        <v>0.1046511627906977</v>
-      </c>
-      <c r="AL4">
-        <v>0.1116279069767442</v>
-      </c>
-      <c r="AM4">
-        <v>0.1186046511627907</v>
-      </c>
-      <c r="AN4">
-        <v>0.1255813953488372</v>
-      </c>
-      <c r="AO4">
-        <v>0.1325581395348837</v>
-      </c>
-      <c r="AP4">
-        <v>0.1395348837209302</v>
-      </c>
-      <c r="AQ4">
-        <v>0.1465116279069767</v>
-      </c>
-      <c r="AR4">
-        <v>0.1534883720930233</v>
-      </c>
-      <c r="AS4">
-        <v>0.1604651162790698</v>
-      </c>
-      <c r="AT4">
-        <v>0.1674418604651163</v>
-      </c>
-      <c r="AU4">
-        <v>0.1744186046511628</v>
-      </c>
-      <c r="AV4">
-        <v>0.1813953488372093</v>
-      </c>
-      <c r="AW4">
-        <v>0.1883720930232558</v>
-      </c>
-      <c r="AX4">
-        <v>0.1953488372093023</v>
-      </c>
-      <c r="AY4">
-        <v>0.2023255813953488</v>
-      </c>
-      <c r="AZ4">
-        <v>0.2093023255813954</v>
-      </c>
-      <c r="BA4">
-        <v>0.2162790697674419</v>
-      </c>
-      <c r="BB4">
-        <v>0.2232558139534884</v>
-      </c>
-      <c r="BC4">
-        <v>0.2302325581395349</v>
-      </c>
-      <c r="BD4">
-        <v>0.2372093023255814</v>
-      </c>
-      <c r="BE4">
-        <v>0.2441860465116279</v>
-      </c>
-      <c r="BF4">
-        <v>0.2511627906976744</v>
-      </c>
-      <c r="BG4">
-        <v>0.2581395348837209</v>
-      </c>
-      <c r="BH4">
-        <v>0.2651162790697674</v>
-      </c>
-      <c r="BI4">
-        <v>0.2720930232558139</v>
-      </c>
-      <c r="BJ4">
-        <v>0.2790697674418605</v>
-      </c>
-      <c r="BK4">
-        <v>0.286046511627907</v>
-      </c>
-      <c r="BL4">
-        <v>0.2930232558139534</v>
-      </c>
       <c r="BM4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:65">
@@ -43398,133 +43398,133 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.006976744186046512</v>
+        <v>0.01627906976744186</v>
       </c>
       <c r="X5">
-        <v>0.01395348837209302</v>
+        <v>0.03255813953488372</v>
       </c>
       <c r="Y5">
-        <v>0.02093023255813953</v>
+        <v>0.04883720930232558</v>
       </c>
       <c r="Z5">
-        <v>0.02790697674418605</v>
+        <v>0.06511627906976744</v>
       </c>
       <c r="AA5">
-        <v>0.03488372093023256</v>
+        <v>0.08139534883720929</v>
       </c>
       <c r="AB5">
-        <v>0.04186046511627907</v>
+        <v>0.09767441860465116</v>
       </c>
       <c r="AC5">
-        <v>0.04883720930232558</v>
+        <v>0.113953488372093</v>
       </c>
       <c r="AD5">
-        <v>0.05581395348837209</v>
+        <v>0.1302325581395349</v>
       </c>
       <c r="AE5">
-        <v>0.06279069767441861</v>
+        <v>0.1465116279069767</v>
       </c>
       <c r="AF5">
-        <v>0.06976744186046512</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="AG5">
-        <v>0.07674418604651163</v>
+        <v>0.1790697674418605</v>
       </c>
       <c r="AH5">
-        <v>0.08372093023255814</v>
+        <v>0.1953488372093023</v>
       </c>
       <c r="AI5">
-        <v>0.09069767441860464</v>
+        <v>0.2116279069767442</v>
       </c>
       <c r="AJ5">
-        <v>0.09767441860465116</v>
+        <v>0.2279069767441861</v>
       </c>
       <c r="AK5">
-        <v>0.1046511627906977</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="AL5">
-        <v>0.1116279069767442</v>
+        <v>0.2604651162790698</v>
       </c>
       <c r="AM5">
-        <v>0.1186046511627907</v>
+        <v>0.2767441860465116</v>
       </c>
       <c r="AN5">
-        <v>0.1255813953488372</v>
+        <v>0.2930232558139535</v>
       </c>
       <c r="AO5">
-        <v>0.1325581395348837</v>
+        <v>0.3093023255813953</v>
       </c>
       <c r="AP5">
-        <v>0.1395348837209302</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="AQ5">
-        <v>0.1465116279069767</v>
+        <v>0.341860465116279</v>
       </c>
       <c r="AR5">
-        <v>0.1534883720930233</v>
+        <v>0.3581395348837209</v>
       </c>
       <c r="AS5">
-        <v>0.1604651162790698</v>
+        <v>0.3744186046511627</v>
       </c>
       <c r="AT5">
-        <v>0.1674418604651163</v>
+        <v>0.3906976744186046</v>
       </c>
       <c r="AU5">
-        <v>0.1744186046511628</v>
+        <v>0.4069767441860465</v>
       </c>
       <c r="AV5">
-        <v>0.1813953488372093</v>
+        <v>0.4232558139534883</v>
       </c>
       <c r="AW5">
-        <v>0.1883720930232558</v>
+        <v>0.4395348837209302</v>
       </c>
       <c r="AX5">
-        <v>0.1953488372093023</v>
+        <v>0.4558139534883721</v>
       </c>
       <c r="AY5">
-        <v>0.2023255813953488</v>
+        <v>0.4720930232558139</v>
       </c>
       <c r="AZ5">
-        <v>0.2093023255813954</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="BA5">
-        <v>0.2162790697674419</v>
+        <v>0.5046511627906977</v>
       </c>
       <c r="BB5">
-        <v>0.2232558139534884</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="BC5">
-        <v>0.2302325581395349</v>
+        <v>0.5372093023255814</v>
       </c>
       <c r="BD5">
-        <v>0.2372093023255814</v>
+        <v>0.5534883720930232</v>
       </c>
       <c r="BE5">
-        <v>0.2441860465116279</v>
+        <v>0.5697674418604651</v>
       </c>
       <c r="BF5">
-        <v>0.2511627906976744</v>
+        <v>0.586046511627907</v>
       </c>
       <c r="BG5">
-        <v>0.2581395348837209</v>
+        <v>0.6023255813953488</v>
       </c>
       <c r="BH5">
-        <v>0.2651162790697674</v>
+        <v>0.6186046511627906</v>
       </c>
       <c r="BI5">
-        <v>0.2720930232558139</v>
+        <v>0.6348837209302325</v>
       </c>
       <c r="BJ5">
-        <v>0.2790697674418605</v>
+        <v>0.6511627906976744</v>
       </c>
       <c r="BK5">
-        <v>0.286046511627907</v>
+        <v>0.6674418604651162</v>
       </c>
       <c r="BL5">
-        <v>0.2930232558139534</v>
+        <v>0.6837209302325581</v>
       </c>
       <c r="BM5">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="1:65">
@@ -43583,133 +43583,133 @@
         <v>0</v>
       </c>
       <c r="W6">
+        <v>0.002325581395348837</v>
+      </c>
+      <c r="X6">
         <v>0.004651162790697674</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
+        <v>0.006976744186046512</v>
+      </c>
+      <c r="Z6">
         <v>0.009302325581395349</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="AB6">
         <v>0.01395348837209302</v>
       </c>
-      <c r="Z6">
+      <c r="AC6">
+        <v>0.01627906976744186</v>
+      </c>
+      <c r="AD6">
         <v>0.0186046511627907</v>
       </c>
-      <c r="AA6">
+      <c r="AE6">
+        <v>0.02093023255813954</v>
+      </c>
+      <c r="AF6">
         <v>0.02325581395348837</v>
       </c>
-      <c r="AB6">
+      <c r="AG6">
+        <v>0.02558139534883721</v>
+      </c>
+      <c r="AH6">
         <v>0.02790697674418605</v>
       </c>
-      <c r="AC6">
+      <c r="AI6">
+        <v>0.03023255813953488</v>
+      </c>
+      <c r="AJ6">
         <v>0.03255813953488373</v>
       </c>
-      <c r="AD6">
+      <c r="AK6">
+        <v>0.03488372093023256</v>
+      </c>
+      <c r="AL6">
         <v>0.03720930232558139</v>
       </c>
-      <c r="AE6">
+      <c r="AM6">
+        <v>0.03953488372093023</v>
+      </c>
+      <c r="AN6">
         <v>0.04186046511627908</v>
       </c>
-      <c r="AF6">
+      <c r="AO6">
+        <v>0.04418604651162791</v>
+      </c>
+      <c r="AP6">
         <v>0.04651162790697674</v>
       </c>
-      <c r="AG6">
+      <c r="AQ6">
+        <v>0.04883720930232558</v>
+      </c>
+      <c r="AR6">
         <v>0.05116279069767442</v>
       </c>
-      <c r="AH6">
+      <c r="AS6">
+        <v>0.05348837209302326</v>
+      </c>
+      <c r="AT6">
         <v>0.05581395348837209</v>
       </c>
-      <c r="AI6">
+      <c r="AU6">
+        <v>0.05813953488372094</v>
+      </c>
+      <c r="AV6">
         <v>0.06046511627906977</v>
       </c>
-      <c r="AJ6">
+      <c r="AW6">
+        <v>0.06279069767441861</v>
+      </c>
+      <c r="AX6">
         <v>0.06511627906976745</v>
       </c>
-      <c r="AK6">
+      <c r="AY6">
+        <v>0.06744186046511629</v>
+      </c>
+      <c r="AZ6">
         <v>0.06976744186046512</v>
       </c>
-      <c r="AL6">
+      <c r="BA6">
+        <v>0.07209302325581395</v>
+      </c>
+      <c r="BB6">
         <v>0.07441860465116279</v>
       </c>
-      <c r="AM6">
+      <c r="BC6">
+        <v>0.07674418604651163</v>
+      </c>
+      <c r="BD6">
         <v>0.07906976744186046</v>
       </c>
-      <c r="AN6">
+      <c r="BE6">
+        <v>0.08139534883720931</v>
+      </c>
+      <c r="BF6">
         <v>0.08372093023255815</v>
       </c>
-      <c r="AO6">
+      <c r="BG6">
+        <v>0.08604651162790698</v>
+      </c>
+      <c r="BH6">
         <v>0.08837209302325583</v>
       </c>
-      <c r="AP6">
+      <c r="BI6">
+        <v>0.09069767441860466</v>
+      </c>
+      <c r="BJ6">
         <v>0.09302325581395349</v>
       </c>
-      <c r="AQ6">
+      <c r="BK6">
+        <v>0.09534883720930233</v>
+      </c>
+      <c r="BL6">
         <v>0.09767441860465116</v>
       </c>
-      <c r="AR6">
-        <v>0.1023255813953488</v>
-      </c>
-      <c r="AS6">
-        <v>0.1069767441860465</v>
-      </c>
-      <c r="AT6">
-        <v>0.1116279069767442</v>
-      </c>
-      <c r="AU6">
-        <v>0.1162790697674419</v>
-      </c>
-      <c r="AV6">
-        <v>0.1209302325581395</v>
-      </c>
-      <c r="AW6">
-        <v>0.1255813953488372</v>
-      </c>
-      <c r="AX6">
-        <v>0.1302325581395349</v>
-      </c>
-      <c r="AY6">
-        <v>0.1348837209302326</v>
-      </c>
-      <c r="AZ6">
-        <v>0.1395348837209302</v>
-      </c>
-      <c r="BA6">
-        <v>0.1441860465116279</v>
-      </c>
-      <c r="BB6">
-        <v>0.1488372093023256</v>
-      </c>
-      <c r="BC6">
-        <v>0.1534883720930233</v>
-      </c>
-      <c r="BD6">
-        <v>0.1581395348837209</v>
-      </c>
-      <c r="BE6">
-        <v>0.1627906976744186</v>
-      </c>
-      <c r="BF6">
-        <v>0.1674418604651163</v>
-      </c>
-      <c r="BG6">
-        <v>0.172093023255814</v>
-      </c>
-      <c r="BH6">
-        <v>0.1767441860465117</v>
-      </c>
-      <c r="BI6">
-        <v>0.1813953488372093</v>
-      </c>
-      <c r="BJ6">
-        <v>0.186046511627907</v>
-      </c>
-      <c r="BK6">
-        <v>0.1906976744186047</v>
-      </c>
-      <c r="BL6">
-        <v>0.1953488372093023</v>
-      </c>
       <c r="BM6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:65">
@@ -43768,133 +43768,133 @@
         <v>0</v>
       </c>
       <c r="W7">
+        <v>0.002325581395348837</v>
+      </c>
+      <c r="X7">
         <v>0.004651162790697674</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
+        <v>0.006976744186046512</v>
+      </c>
+      <c r="Z7">
         <v>0.009302325581395349</v>
       </c>
-      <c r="Y7">
+      <c r="AA7">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="AB7">
         <v>0.01395348837209302</v>
       </c>
-      <c r="Z7">
+      <c r="AC7">
+        <v>0.01627906976744186</v>
+      </c>
+      <c r="AD7">
         <v>0.0186046511627907</v>
       </c>
-      <c r="AA7">
+      <c r="AE7">
+        <v>0.02093023255813954</v>
+      </c>
+      <c r="AF7">
         <v>0.02325581395348837</v>
       </c>
-      <c r="AB7">
+      <c r="AG7">
+        <v>0.02558139534883721</v>
+      </c>
+      <c r="AH7">
         <v>0.02790697674418605</v>
       </c>
-      <c r="AC7">
+      <c r="AI7">
+        <v>0.03023255813953488</v>
+      </c>
+      <c r="AJ7">
         <v>0.03255813953488373</v>
       </c>
-      <c r="AD7">
+      <c r="AK7">
+        <v>0.03488372093023256</v>
+      </c>
+      <c r="AL7">
         <v>0.03720930232558139</v>
       </c>
-      <c r="AE7">
+      <c r="AM7">
+        <v>0.03953488372093023</v>
+      </c>
+      <c r="AN7">
         <v>0.04186046511627908</v>
       </c>
-      <c r="AF7">
+      <c r="AO7">
+        <v>0.04418604651162791</v>
+      </c>
+      <c r="AP7">
         <v>0.04651162790697674</v>
       </c>
-      <c r="AG7">
+      <c r="AQ7">
+        <v>0.04883720930232558</v>
+      </c>
+      <c r="AR7">
         <v>0.05116279069767442</v>
       </c>
-      <c r="AH7">
+      <c r="AS7">
+        <v>0.05348837209302326</v>
+      </c>
+      <c r="AT7">
         <v>0.05581395348837209</v>
       </c>
-      <c r="AI7">
+      <c r="AU7">
+        <v>0.05813953488372094</v>
+      </c>
+      <c r="AV7">
         <v>0.06046511627906977</v>
       </c>
-      <c r="AJ7">
+      <c r="AW7">
+        <v>0.06279069767441861</v>
+      </c>
+      <c r="AX7">
         <v>0.06511627906976745</v>
       </c>
-      <c r="AK7">
+      <c r="AY7">
+        <v>0.06744186046511629</v>
+      </c>
+      <c r="AZ7">
         <v>0.06976744186046512</v>
       </c>
-      <c r="AL7">
+      <c r="BA7">
+        <v>0.07209302325581395</v>
+      </c>
+      <c r="BB7">
         <v>0.07441860465116279</v>
       </c>
-      <c r="AM7">
+      <c r="BC7">
+        <v>0.07674418604651163</v>
+      </c>
+      <c r="BD7">
         <v>0.07906976744186046</v>
       </c>
-      <c r="AN7">
+      <c r="BE7">
+        <v>0.08139534883720931</v>
+      </c>
+      <c r="BF7">
         <v>0.08372093023255815</v>
       </c>
-      <c r="AO7">
+      <c r="BG7">
+        <v>0.08604651162790698</v>
+      </c>
+      <c r="BH7">
         <v>0.08837209302325583</v>
       </c>
-      <c r="AP7">
+      <c r="BI7">
+        <v>0.09069767441860466</v>
+      </c>
+      <c r="BJ7">
         <v>0.09302325581395349</v>
       </c>
-      <c r="AQ7">
+      <c r="BK7">
+        <v>0.09534883720930233</v>
+      </c>
+      <c r="BL7">
         <v>0.09767441860465116</v>
       </c>
-      <c r="AR7">
-        <v>0.1023255813953488</v>
-      </c>
-      <c r="AS7">
-        <v>0.1069767441860465</v>
-      </c>
-      <c r="AT7">
-        <v>0.1116279069767442</v>
-      </c>
-      <c r="AU7">
-        <v>0.1162790697674419</v>
-      </c>
-      <c r="AV7">
-        <v>0.1209302325581395</v>
-      </c>
-      <c r="AW7">
-        <v>0.1255813953488372</v>
-      </c>
-      <c r="AX7">
-        <v>0.1302325581395349</v>
-      </c>
-      <c r="AY7">
-        <v>0.1348837209302326</v>
-      </c>
-      <c r="AZ7">
-        <v>0.1395348837209302</v>
-      </c>
-      <c r="BA7">
-        <v>0.1441860465116279</v>
-      </c>
-      <c r="BB7">
-        <v>0.1488372093023256</v>
-      </c>
-      <c r="BC7">
-        <v>0.1534883720930233</v>
-      </c>
-      <c r="BD7">
-        <v>0.1581395348837209</v>
-      </c>
-      <c r="BE7">
-        <v>0.1627906976744186</v>
-      </c>
-      <c r="BF7">
-        <v>0.1674418604651163</v>
-      </c>
-      <c r="BG7">
-        <v>0.172093023255814</v>
-      </c>
-      <c r="BH7">
-        <v>0.1767441860465117</v>
-      </c>
-      <c r="BI7">
-        <v>0.1813953488372093</v>
-      </c>
-      <c r="BJ7">
-        <v>0.186046511627907</v>
-      </c>
-      <c r="BK7">
-        <v>0.1906976744186047</v>
-      </c>
-      <c r="BL7">
-        <v>0.1953488372093023</v>
-      </c>
       <c r="BM7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:65">
@@ -44031,31 +44031,31 @@
         <v>0.3953488372093024</v>
       </c>
       <c r="AW8">
-        <v>0.3720930232558139</v>
+        <v>0.372093023255814</v>
       </c>
       <c r="AX8">
-        <v>0.3488372093023255</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="AY8">
-        <v>0.3255813953488372</v>
+        <v>0.3255813953488373</v>
       </c>
       <c r="AZ8">
-        <v>0.3023255813953488</v>
+        <v>0.3023255813953489</v>
       </c>
       <c r="BA8">
-        <v>0.2790697674418605</v>
+        <v>0.2790697674418606</v>
       </c>
       <c r="BB8">
-        <v>0.2558139534883721</v>
+        <v>0.2558139534883722</v>
       </c>
       <c r="BC8">
-        <v>0.2325581395348837</v>
+        <v>0.2325581395348838</v>
       </c>
       <c r="BD8">
-        <v>0.2093023255813954</v>
+        <v>0.2093023255813955</v>
       </c>
       <c r="BE8">
-        <v>0.186046511627907</v>
+        <v>0.1860465116279071</v>
       </c>
       <c r="BF8">
         <v>0.1627906976744186</v>
@@ -44064,22 +44064,22 @@
         <v>0.1395348837209303</v>
       </c>
       <c r="BH8">
-        <v>0.1162790697674418</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="BI8">
-        <v>0.09302325581395354</v>
+        <v>0.09302325581395364</v>
       </c>
       <c r="BJ8">
-        <v>0.06976744186046513</v>
+        <v>0.06976744186046523</v>
       </c>
       <c r="BK8">
-        <v>0.04651162790697672</v>
+        <v>0.04651162790697682</v>
       </c>
       <c r="BL8">
-        <v>0.02325581395348841</v>
+        <v>0.02325581395348852</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.110223024625157E-16</v>
       </c>
     </row>
     <row r="9" spans="1:65">
@@ -46331,133 +46331,133 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="W21">
-        <v>0.09162790697674419</v>
+        <v>0.09046511627906978</v>
       </c>
       <c r="X21">
-        <v>0.1132558139534884</v>
+        <v>0.1109302325581396</v>
       </c>
       <c r="Y21">
-        <v>0.1348837209302325</v>
+        <v>0.1313953488372093</v>
       </c>
       <c r="Z21">
-        <v>0.1565116279069768</v>
+        <v>0.1518604651162791</v>
       </c>
       <c r="AA21">
-        <v>0.1781395348837209</v>
+        <v>0.1723255813953488</v>
       </c>
       <c r="AB21">
-        <v>0.1997674418604651</v>
+        <v>0.1927906976744186</v>
       </c>
       <c r="AC21">
-        <v>0.2213953488372093</v>
+        <v>0.2132558139534884</v>
       </c>
       <c r="AD21">
-        <v>0.2430232558139535</v>
+        <v>0.2337209302325581</v>
       </c>
       <c r="AE21">
-        <v>0.2646511627906977</v>
+        <v>0.2541860465116279</v>
       </c>
       <c r="AF21">
-        <v>0.2862790697674419</v>
+        <v>0.2746511627906977</v>
       </c>
       <c r="AG21">
-        <v>0.307906976744186</v>
+        <v>0.2951162790697675</v>
       </c>
       <c r="AH21">
-        <v>0.3295348837209302</v>
+        <v>0.3155813953488372</v>
       </c>
       <c r="AI21">
-        <v>0.3511627906976744</v>
+        <v>0.3360465116279069</v>
       </c>
       <c r="AJ21">
-        <v>0.3727906976744186</v>
+        <v>0.3565116279069768</v>
       </c>
       <c r="AK21">
-        <v>0.3944186046511628</v>
+        <v>0.3769767441860465</v>
       </c>
       <c r="AL21">
-        <v>0.416046511627907</v>
+        <v>0.3974418604651163</v>
       </c>
       <c r="AM21">
-        <v>0.4376744186046512</v>
+        <v>0.417906976744186</v>
       </c>
       <c r="AN21">
-        <v>0.4593023255813954</v>
+        <v>0.4383720930232559</v>
       </c>
       <c r="AO21">
-        <v>0.4809302325581395</v>
+        <v>0.4588372093023256</v>
       </c>
       <c r="AP21">
-        <v>0.5025581395348837</v>
+        <v>0.4793023255813953</v>
       </c>
       <c r="AQ21">
-        <v>0.5241860465116279</v>
+        <v>0.4997674418604651</v>
       </c>
       <c r="AR21">
-        <v>0.5458139534883721</v>
+        <v>0.5202325581395348</v>
       </c>
       <c r="AS21">
-        <v>0.5674418604651162</v>
+        <v>0.5406976744186046</v>
       </c>
       <c r="AT21">
-        <v>0.5890697674418605</v>
+        <v>0.5611627906976744</v>
       </c>
       <c r="AU21">
-        <v>0.6106976744186047</v>
+        <v>0.5816279069767442</v>
       </c>
       <c r="AV21">
-        <v>0.6323255813953488</v>
+        <v>0.6020930232558138</v>
       </c>
       <c r="AW21">
-        <v>0.653953488372093</v>
+        <v>0.6225581395348837</v>
       </c>
       <c r="AX21">
-        <v>0.6755813953488372</v>
+        <v>0.6430232558139535</v>
       </c>
       <c r="AY21">
-        <v>0.6972093023255814</v>
+        <v>0.6634883720930232</v>
       </c>
       <c r="AZ21">
-        <v>0.7188372093023256</v>
+        <v>0.683953488372093</v>
       </c>
       <c r="BA21">
-        <v>0.7404651162790697</v>
+        <v>0.7044186046511628</v>
       </c>
       <c r="BB21">
-        <v>0.762093023255814</v>
+        <v>0.7248837209302326</v>
       </c>
       <c r="BC21">
-        <v>0.7837209302325582</v>
+        <v>0.7453488372093023</v>
       </c>
       <c r="BD21">
-        <v>0.8053488372093023</v>
+        <v>0.765813953488372</v>
       </c>
       <c r="BE21">
-        <v>0.8269767441860465</v>
+        <v>0.7862790697674418</v>
       </c>
       <c r="BF21">
-        <v>0.8486046511627907</v>
+        <v>0.8067441860465117</v>
       </c>
       <c r="BG21">
-        <v>0.8702325581395348</v>
+        <v>0.8272093023255813</v>
       </c>
       <c r="BH21">
-        <v>0.891860465116279</v>
+        <v>0.8476744186046511</v>
       </c>
       <c r="BI21">
-        <v>0.9134883720930232</v>
+        <v>0.8681395348837209</v>
       </c>
       <c r="BJ21">
-        <v>0.9351162790697675</v>
+        <v>0.8886046511627906</v>
       </c>
       <c r="BK21">
-        <v>0.9567441860465117</v>
+        <v>0.9090697674418605</v>
       </c>
       <c r="BL21">
-        <v>0.9783720930232558</v>
+        <v>0.9295348837209302</v>
       </c>
       <c r="BM21">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="22" spans="1:65">
@@ -46513,133 +46513,133 @@
         <v>0.5</v>
       </c>
       <c r="W22">
-        <v>0.5116279069767442</v>
+        <v>0.5104651162790698</v>
       </c>
       <c r="X22">
-        <v>0.5232558139534884</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="Y22">
-        <v>0.5348837209302325</v>
+        <v>0.5313953488372093</v>
       </c>
       <c r="Z22">
-        <v>0.5465116279069768</v>
+        <v>0.5418604651162791</v>
       </c>
       <c r="AA22">
-        <v>0.5581395348837209</v>
+        <v>0.5523255813953488</v>
       </c>
       <c r="AB22">
-        <v>0.5697674418604651</v>
+        <v>0.5627906976744186</v>
       </c>
       <c r="AC22">
-        <v>0.5813953488372092</v>
+        <v>0.5732558139534883</v>
       </c>
       <c r="AD22">
-        <v>0.5930232558139534</v>
+        <v>0.5837209302325581</v>
       </c>
       <c r="AE22">
+        <v>0.5941860465116279</v>
+      </c>
+      <c r="AF22">
         <v>0.6046511627906976</v>
       </c>
-      <c r="AF22">
-        <v>0.6162790697674418</v>
-      </c>
       <c r="AG22">
-        <v>0.6279069767441861</v>
+        <v>0.6151162790697674</v>
       </c>
       <c r="AH22">
-        <v>0.6395348837209303</v>
+        <v>0.6255813953488372</v>
       </c>
       <c r="AI22">
-        <v>0.6511627906976745</v>
+        <v>0.6360465116279069</v>
       </c>
       <c r="AJ22">
-        <v>0.6627906976744187</v>
+        <v>0.6465116279069767</v>
       </c>
       <c r="AK22">
-        <v>0.6744186046511629</v>
+        <v>0.6569767441860466</v>
       </c>
       <c r="AL22">
-        <v>0.686046511627907</v>
+        <v>0.6674418604651162</v>
       </c>
       <c r="AM22">
-        <v>0.6976744186046511</v>
+        <v>0.677906976744186</v>
       </c>
       <c r="AN22">
+        <v>0.6883720930232557</v>
+      </c>
+      <c r="AO22">
+        <v>0.6988372093023256</v>
+      </c>
+      <c r="AP22">
         <v>0.7093023255813953</v>
       </c>
-      <c r="AO22">
-        <v>0.7209302325581395</v>
-      </c>
-      <c r="AP22">
-        <v>0.7325581395348837</v>
-      </c>
       <c r="AQ22">
-        <v>0.7441860465116279</v>
+        <v>0.7197674418604652</v>
       </c>
       <c r="AR22">
-        <v>0.7558139534883721</v>
+        <v>0.7302325581395348</v>
       </c>
       <c r="AS22">
-        <v>0.7674418604651163</v>
+        <v>0.7406976744186047</v>
       </c>
       <c r="AT22">
-        <v>0.7790697674418605</v>
+        <v>0.7511627906976743</v>
       </c>
       <c r="AU22">
-        <v>0.7906976744186047</v>
+        <v>0.7616279069767442</v>
       </c>
       <c r="AV22">
-        <v>0.8023255813953488</v>
+        <v>0.7720930232558139</v>
       </c>
       <c r="AW22">
-        <v>0.813953488372093</v>
+        <v>0.7825581395348837</v>
       </c>
       <c r="AX22">
-        <v>0.8255813953488372</v>
+        <v>0.7930232558139535</v>
       </c>
       <c r="AY22">
-        <v>0.8372093023255813</v>
+        <v>0.8034883720930233</v>
       </c>
       <c r="AZ22">
-        <v>0.8488372093023255</v>
+        <v>0.8139534883720929</v>
       </c>
       <c r="BA22">
-        <v>0.8604651162790697</v>
+        <v>0.8244186046511628</v>
       </c>
       <c r="BB22">
-        <v>0.8720930232558139</v>
+        <v>0.8348837209302326</v>
       </c>
       <c r="BC22">
-        <v>0.8837209302325582</v>
+        <v>0.8453488372093023</v>
       </c>
       <c r="BD22">
-        <v>0.8953488372093024</v>
+        <v>0.855813953488372</v>
       </c>
       <c r="BE22">
-        <v>0.9069767441860466</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="BF22">
-        <v>0.9186046511627908</v>
+        <v>0.8767441860465117</v>
       </c>
       <c r="BG22">
-        <v>0.9302325581395349</v>
+        <v>0.8872093023255814</v>
       </c>
       <c r="BH22">
-        <v>0.9418604651162791</v>
+        <v>0.8976744186046511</v>
       </c>
       <c r="BI22">
-        <v>0.9534883720930232</v>
+        <v>0.9081395348837209</v>
       </c>
       <c r="BJ22">
-        <v>0.9651162790697674</v>
+        <v>0.9186046511627906</v>
       </c>
       <c r="BK22">
-        <v>0.9767441860465116</v>
+        <v>0.9290697674418604</v>
       </c>
       <c r="BL22">
-        <v>0.9883720930232558</v>
+        <v>0.9395348837209302</v>
       </c>
       <c r="BM22">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="23" spans="1:65">
@@ -48521,133 +48521,133 @@
         <v>0.95</v>
       </c>
       <c r="W33">
-        <v>0.9511627906976744</v>
+        <v>0.95</v>
       </c>
       <c r="X33">
-        <v>0.9523255813953488</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="Y33">
-        <v>0.9534883720930232</v>
+        <v>0.95</v>
       </c>
       <c r="Z33">
-        <v>0.9546511627906977</v>
+        <v>0.95</v>
       </c>
       <c r="AA33">
-        <v>0.9558139534883721</v>
+        <v>0.95</v>
       </c>
       <c r="AB33">
-        <v>0.9569767441860465</v>
+        <v>0.95</v>
       </c>
       <c r="AC33">
-        <v>0.9581395348837209</v>
+        <v>0.95</v>
       </c>
       <c r="AD33">
-        <v>0.9593023255813953</v>
+        <v>0.95</v>
       </c>
       <c r="AE33">
-        <v>0.9604651162790697</v>
+        <v>0.95</v>
       </c>
       <c r="AF33">
-        <v>0.9616279069767442</v>
+        <v>0.95</v>
       </c>
       <c r="AG33">
-        <v>0.9627906976744186</v>
+        <v>0.95</v>
       </c>
       <c r="AH33">
-        <v>0.963953488372093</v>
+        <v>0.95</v>
       </c>
       <c r="AI33">
-        <v>0.9651162790697674</v>
+        <v>0.95</v>
       </c>
       <c r="AJ33">
-        <v>0.9662790697674418</v>
+        <v>0.95</v>
       </c>
       <c r="AK33">
-        <v>0.9674418604651163</v>
+        <v>0.95</v>
       </c>
       <c r="AL33">
-        <v>0.9686046511627907</v>
+        <v>0.95</v>
       </c>
       <c r="AM33">
-        <v>0.9697674418604649</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="AN33">
-        <v>0.9709302325581395</v>
+        <v>0.95</v>
       </c>
       <c r="AO33">
-        <v>0.9720930232558139</v>
+        <v>0.95</v>
       </c>
       <c r="AP33">
-        <v>0.9732558139534884</v>
+        <v>0.95</v>
       </c>
       <c r="AQ33">
-        <v>0.9744186046511627</v>
+        <v>0.95</v>
       </c>
       <c r="AR33">
-        <v>0.9755813953488373</v>
+        <v>0.95</v>
       </c>
       <c r="AS33">
-        <v>0.9767441860465116</v>
+        <v>0.95</v>
       </c>
       <c r="AT33">
-        <v>0.977906976744186</v>
+        <v>0.95</v>
       </c>
       <c r="AU33">
-        <v>0.9790697674418605</v>
+        <v>0.95</v>
       </c>
       <c r="AV33">
-        <v>0.9802325581395348</v>
+        <v>0.95</v>
       </c>
       <c r="AW33">
-        <v>0.9813953488372094</v>
+        <v>0.95</v>
       </c>
       <c r="AX33">
-        <v>0.9825581395348837</v>
+        <v>0.95</v>
       </c>
       <c r="AY33">
-        <v>0.9837209302325581</v>
+        <v>0.95</v>
       </c>
       <c r="AZ33">
-        <v>0.9848837209302326</v>
+        <v>0.95</v>
       </c>
       <c r="BA33">
-        <v>0.9860465116279069</v>
+        <v>0.95</v>
       </c>
       <c r="BB33">
-        <v>0.9872093023255814</v>
+        <v>0.95</v>
       </c>
       <c r="BC33">
-        <v>0.9883720930232558</v>
+        <v>0.95</v>
       </c>
       <c r="BD33">
-        <v>0.9895348837209302</v>
+        <v>0.95</v>
       </c>
       <c r="BE33">
-        <v>0.9906976744186047</v>
+        <v>0.95</v>
       </c>
       <c r="BF33">
-        <v>0.991860465116279</v>
+        <v>0.95</v>
       </c>
       <c r="BG33">
-        <v>0.9930232558139535</v>
+        <v>0.95</v>
       </c>
       <c r="BH33">
-        <v>0.9941860465116279</v>
+        <v>0.95</v>
       </c>
       <c r="BI33">
-        <v>0.9953488372093023</v>
+        <v>0.95</v>
       </c>
       <c r="BJ33">
-        <v>0.9965116279069768</v>
+        <v>0.95</v>
       </c>
       <c r="BK33">
-        <v>0.9976744186046511</v>
+        <v>0.95</v>
       </c>
       <c r="BL33">
-        <v>0.9988372093023256</v>
+        <v>0.95</v>
       </c>
       <c r="BM33">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="34" spans="1:65">

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
@@ -9,20 +9,22 @@
   <sheets>
     <sheet name="strategy_id-0" sheetId="1" r:id="rId1"/>
     <sheet name="strategy_id-6004" sheetId="2" r:id="rId2"/>
-    <sheet name="strategy_id-6007" sheetId="3" r:id="rId3"/>
-    <sheet name="strategy_id-6008" sheetId="4" r:id="rId4"/>
+    <sheet name="strategy_id-6008" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="293">
   <si>
     <t>subsector</t>
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>variable_trajectory_group</t>
   </si>
   <si>
     <t>normalize_group</t>
@@ -32,9 +34,6 @@
   </si>
   <si>
     <t>uniform_scaling_q</t>
-  </si>
-  <si>
-    <t>variable_trajectory_group</t>
   </si>
   <si>
     <t>variable_trajectory_group_trajectory_type</t>
@@ -2188,9 +2187,6 @@
       <c r="B6" t="s">
         <v>72</v>
       </c>
-      <c r="F6">
-        <v>58</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
@@ -2373,9 +2369,6 @@
       <c r="B7" t="s">
         <v>73</v>
       </c>
-      <c r="F7">
-        <v>58</v>
-      </c>
       <c r="H7">
         <v>1</v>
       </c>
@@ -2558,9 +2551,6 @@
       <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="F8">
-        <v>58</v>
-      </c>
       <c r="H8">
         <v>1</v>
       </c>
@@ -2743,9 +2733,6 @@
       <c r="B9" t="s">
         <v>75</v>
       </c>
-      <c r="F9">
-        <v>58</v>
-      </c>
       <c r="H9">
         <v>1</v>
       </c>
@@ -2928,9 +2915,6 @@
       <c r="B10" t="s">
         <v>76</v>
       </c>
-      <c r="F10">
-        <v>58</v>
-      </c>
       <c r="H10">
         <v>1</v>
       </c>
@@ -3113,9 +3097,6 @@
       <c r="B11" t="s">
         <v>77</v>
       </c>
-      <c r="F11">
-        <v>58</v>
-      </c>
       <c r="H11">
         <v>1</v>
       </c>
@@ -3298,9 +3279,6 @@
       <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="F12">
-        <v>58</v>
-      </c>
       <c r="H12">
         <v>1</v>
       </c>
@@ -3483,8 +3461,8 @@
       <c r="B13" t="s">
         <v>79</v>
       </c>
-      <c r="F13">
-        <v>58</v>
+      <c r="C13">
+        <v>51</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -3668,8 +3646,8 @@
       <c r="B14" t="s">
         <v>80</v>
       </c>
-      <c r="F14">
-        <v>58</v>
+      <c r="C14">
+        <v>51</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -3853,9 +3831,6 @@
       <c r="B15" t="s">
         <v>81</v>
       </c>
-      <c r="F15">
-        <v>58</v>
-      </c>
       <c r="H15">
         <v>1</v>
       </c>
@@ -4038,8 +4013,8 @@
       <c r="B16" t="s">
         <v>82</v>
       </c>
-      <c r="F16">
-        <v>59</v>
+      <c r="C16">
+        <v>52</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -4223,8 +4198,8 @@
       <c r="B17" t="s">
         <v>83</v>
       </c>
-      <c r="F17">
-        <v>59</v>
+      <c r="C17">
+        <v>52</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -4408,9 +4383,6 @@
       <c r="B18" t="s">
         <v>84</v>
       </c>
-      <c r="F18">
-        <v>59</v>
-      </c>
       <c r="H18">
         <v>1</v>
       </c>
@@ -4593,9 +4565,6 @@
       <c r="B19" t="s">
         <v>85</v>
       </c>
-      <c r="F19">
-        <v>59</v>
-      </c>
       <c r="H19">
         <v>1</v>
       </c>
@@ -4778,9 +4747,6 @@
       <c r="B20" t="s">
         <v>86</v>
       </c>
-      <c r="F20">
-        <v>59</v>
-      </c>
       <c r="H20">
         <v>1</v>
       </c>
@@ -4963,8 +4929,8 @@
       <c r="B21" t="s">
         <v>87</v>
       </c>
-      <c r="F21">
-        <v>59</v>
+      <c r="C21">
+        <v>52</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -5148,8 +5114,8 @@
       <c r="B22" t="s">
         <v>88</v>
       </c>
-      <c r="F22">
-        <v>59</v>
+      <c r="C22">
+        <v>52</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -5333,9 +5299,6 @@
       <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="F23">
-        <v>59</v>
-      </c>
       <c r="H23">
         <v>1</v>
       </c>
@@ -5518,8 +5481,8 @@
       <c r="B24" t="s">
         <v>90</v>
       </c>
-      <c r="F24">
-        <v>59</v>
+      <c r="C24">
+        <v>52</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -5703,9 +5666,6 @@
       <c r="B25" t="s">
         <v>91</v>
       </c>
-      <c r="F25">
-        <v>59</v>
-      </c>
       <c r="H25">
         <v>1</v>
       </c>
@@ -5888,9 +5848,6 @@
       <c r="B26" t="s">
         <v>92</v>
       </c>
-      <c r="F26">
-        <v>60</v>
-      </c>
       <c r="H26">
         <v>1</v>
       </c>
@@ -6073,8 +6030,8 @@
       <c r="B27" t="s">
         <v>93</v>
       </c>
-      <c r="F27">
-        <v>60</v>
+      <c r="C27">
+        <v>50</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -6258,9 +6215,6 @@
       <c r="B28" t="s">
         <v>94</v>
       </c>
-      <c r="F28">
-        <v>60</v>
-      </c>
       <c r="H28">
         <v>1</v>
       </c>
@@ -6443,9 +6397,6 @@
       <c r="B29" t="s">
         <v>95</v>
       </c>
-      <c r="F29">
-        <v>60</v>
-      </c>
       <c r="H29">
         <v>1</v>
       </c>
@@ -6628,9 +6579,6 @@
       <c r="B30" t="s">
         <v>96</v>
       </c>
-      <c r="F30">
-        <v>60</v>
-      </c>
       <c r="H30">
         <v>1</v>
       </c>
@@ -6813,8 +6761,8 @@
       <c r="B31" t="s">
         <v>97</v>
       </c>
-      <c r="F31">
-        <v>60</v>
+      <c r="C31">
+        <v>50</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -6998,8 +6946,8 @@
       <c r="B32" t="s">
         <v>98</v>
       </c>
-      <c r="F32">
-        <v>60</v>
+      <c r="C32">
+        <v>50</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -7183,9 +7131,6 @@
       <c r="B33" t="s">
         <v>99</v>
       </c>
-      <c r="F33">
-        <v>60</v>
-      </c>
       <c r="H33">
         <v>1</v>
       </c>
@@ -7368,8 +7313,8 @@
       <c r="B34" t="s">
         <v>100</v>
       </c>
-      <c r="F34">
-        <v>60</v>
+      <c r="C34">
+        <v>50</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -7553,9 +7498,6 @@
       <c r="B35" t="s">
         <v>101</v>
       </c>
-      <c r="F35">
-        <v>60</v>
-      </c>
       <c r="H35">
         <v>1</v>
       </c>
@@ -17202,6 +17144,9 @@
       <c r="B88" t="s">
         <v>154</v>
       </c>
+      <c r="C88">
+        <v>53</v>
+      </c>
       <c r="H88">
         <v>1</v>
       </c>
@@ -19386,6 +19331,9 @@
       <c r="B100" t="s">
         <v>166</v>
       </c>
+      <c r="C100">
+        <v>54</v>
+      </c>
       <c r="H100">
         <v>1</v>
       </c>
@@ -19568,6 +19516,9 @@
       <c r="B101" t="s">
         <v>167</v>
       </c>
+      <c r="C101">
+        <v>54</v>
+      </c>
       <c r="H101">
         <v>1</v>
       </c>
@@ -19750,6 +19701,9 @@
       <c r="B102" t="s">
         <v>168</v>
       </c>
+      <c r="C102">
+        <v>54</v>
+      </c>
       <c r="H102">
         <v>1</v>
       </c>
@@ -19932,6 +19886,9 @@
       <c r="B103" t="s">
         <v>169</v>
       </c>
+      <c r="C103">
+        <v>54</v>
+      </c>
       <c r="H103">
         <v>1</v>
       </c>
@@ -20296,6 +20253,9 @@
       <c r="B105" t="s">
         <v>171</v>
       </c>
+      <c r="C105">
+        <v>54</v>
+      </c>
       <c r="H105">
         <v>1</v>
       </c>
@@ -20478,6 +20438,9 @@
       <c r="B106" t="s">
         <v>172</v>
       </c>
+      <c r="C106">
+        <v>54</v>
+      </c>
       <c r="H106">
         <v>1</v>
       </c>
@@ -20660,9 +20623,6 @@
       <c r="B107" t="s">
         <v>173</v>
       </c>
-      <c r="F107">
-        <v>61</v>
-      </c>
       <c r="H107">
         <v>1</v>
       </c>
@@ -20845,9 +20805,6 @@
       <c r="B108" t="s">
         <v>174</v>
       </c>
-      <c r="F108">
-        <v>61</v>
-      </c>
       <c r="H108">
         <v>1</v>
       </c>
@@ -21030,9 +20987,6 @@
       <c r="B109" t="s">
         <v>175</v>
       </c>
-      <c r="F109">
-        <v>61</v>
-      </c>
       <c r="H109">
         <v>1</v>
       </c>
@@ -21215,9 +21169,6 @@
       <c r="B110" t="s">
         <v>176</v>
       </c>
-      <c r="F110">
-        <v>61</v>
-      </c>
       <c r="H110">
         <v>1</v>
       </c>
@@ -21400,9 +21351,6 @@
       <c r="B111" t="s">
         <v>177</v>
       </c>
-      <c r="F111">
-        <v>61</v>
-      </c>
       <c r="H111">
         <v>1</v>
       </c>
@@ -21585,9 +21533,6 @@
       <c r="B112" t="s">
         <v>178</v>
       </c>
-      <c r="F112">
-        <v>61</v>
-      </c>
       <c r="H112">
         <v>1</v>
       </c>
@@ -21770,9 +21715,6 @@
       <c r="B113" t="s">
         <v>179</v>
       </c>
-      <c r="F113">
-        <v>61</v>
-      </c>
       <c r="H113">
         <v>1</v>
       </c>
@@ -21955,9 +21897,6 @@
       <c r="B114" t="s">
         <v>180</v>
       </c>
-      <c r="F114">
-        <v>61</v>
-      </c>
       <c r="H114">
         <v>1</v>
       </c>
@@ -22140,9 +22079,6 @@
       <c r="B115" t="s">
         <v>181</v>
       </c>
-      <c r="F115">
-        <v>61</v>
-      </c>
       <c r="H115">
         <v>1</v>
       </c>
@@ -22325,9 +22261,6 @@
       <c r="B116" t="s">
         <v>182</v>
       </c>
-      <c r="F116">
-        <v>61</v>
-      </c>
       <c r="H116">
         <v>1</v>
       </c>
@@ -22510,9 +22443,6 @@
       <c r="B117" t="s">
         <v>183</v>
       </c>
-      <c r="F117">
-        <v>61</v>
-      </c>
       <c r="H117">
         <v>1</v>
       </c>
@@ -22695,9 +22625,6 @@
       <c r="B118" t="s">
         <v>184</v>
       </c>
-      <c r="F118">
-        <v>61</v>
-      </c>
       <c r="H118">
         <v>1</v>
       </c>
@@ -22880,9 +22807,6 @@
       <c r="B119" t="s">
         <v>185</v>
       </c>
-      <c r="F119">
-        <v>61</v>
-      </c>
       <c r="H119">
         <v>1</v>
       </c>
@@ -23065,9 +22989,6 @@
       <c r="B120" t="s">
         <v>186</v>
       </c>
-      <c r="F120">
-        <v>62</v>
-      </c>
       <c r="H120">
         <v>1</v>
       </c>
@@ -23250,9 +23171,6 @@
       <c r="B121" t="s">
         <v>187</v>
       </c>
-      <c r="F121">
-        <v>62</v>
-      </c>
       <c r="H121">
         <v>1</v>
       </c>
@@ -23435,9 +23353,6 @@
       <c r="B122" t="s">
         <v>188</v>
       </c>
-      <c r="F122">
-        <v>62</v>
-      </c>
       <c r="H122">
         <v>1</v>
       </c>
@@ -23620,9 +23535,6 @@
       <c r="B123" t="s">
         <v>189</v>
       </c>
-      <c r="F123">
-        <v>62</v>
-      </c>
       <c r="H123">
         <v>1</v>
       </c>
@@ -23805,9 +23717,6 @@
       <c r="B124" t="s">
         <v>190</v>
       </c>
-      <c r="F124">
-        <v>62</v>
-      </c>
       <c r="H124">
         <v>1</v>
       </c>
@@ -23990,9 +23899,6 @@
       <c r="B125" t="s">
         <v>191</v>
       </c>
-      <c r="F125">
-        <v>62</v>
-      </c>
       <c r="H125">
         <v>1</v>
       </c>
@@ -24175,9 +24081,6 @@
       <c r="B126" t="s">
         <v>192</v>
       </c>
-      <c r="F126">
-        <v>62</v>
-      </c>
       <c r="H126">
         <v>1</v>
       </c>
@@ -24360,9 +24263,6 @@
       <c r="B127" t="s">
         <v>193</v>
       </c>
-      <c r="F127">
-        <v>62</v>
-      </c>
       <c r="H127">
         <v>1</v>
       </c>
@@ -24545,9 +24445,6 @@
       <c r="B128" t="s">
         <v>194</v>
       </c>
-      <c r="F128">
-        <v>62</v>
-      </c>
       <c r="H128">
         <v>1</v>
       </c>
@@ -24730,9 +24627,6 @@
       <c r="B129" t="s">
         <v>195</v>
       </c>
-      <c r="F129">
-        <v>62</v>
-      </c>
       <c r="H129">
         <v>1</v>
       </c>
@@ -24915,9 +24809,6 @@
       <c r="B130" t="s">
         <v>196</v>
       </c>
-      <c r="F130">
-        <v>62</v>
-      </c>
       <c r="H130">
         <v>1</v>
       </c>
@@ -25100,9 +24991,6 @@
       <c r="B131" t="s">
         <v>197</v>
       </c>
-      <c r="F131">
-        <v>62</v>
-      </c>
       <c r="H131">
         <v>1</v>
       </c>
@@ -25285,9 +25173,6 @@
       <c r="B132" t="s">
         <v>198</v>
       </c>
-      <c r="F132">
-        <v>62</v>
-      </c>
       <c r="H132">
         <v>1</v>
       </c>
@@ -25470,6 +25355,9 @@
       <c r="B133" t="s">
         <v>199</v>
       </c>
+      <c r="C133">
+        <v>57</v>
+      </c>
       <c r="H133">
         <v>1</v>
       </c>
@@ -25652,6 +25540,9 @@
       <c r="B134" t="s">
         <v>200</v>
       </c>
+      <c r="C134">
+        <v>55</v>
+      </c>
       <c r="H134">
         <v>1</v>
       </c>
@@ -25834,6 +25725,9 @@
       <c r="B135" t="s">
         <v>201</v>
       </c>
+      <c r="C135">
+        <v>56</v>
+      </c>
       <c r="H135">
         <v>1</v>
       </c>
@@ -26016,6 +25910,9 @@
       <c r="B136" t="s">
         <v>202</v>
       </c>
+      <c r="C136">
+        <v>57</v>
+      </c>
       <c r="H136">
         <v>1</v>
       </c>
@@ -26198,9 +26095,6 @@
       <c r="B137" t="s">
         <v>203</v>
       </c>
-      <c r="F137">
-        <v>63</v>
-      </c>
       <c r="H137">
         <v>1</v>
       </c>
@@ -26383,8 +26277,8 @@
       <c r="B138" t="s">
         <v>204</v>
       </c>
-      <c r="F138">
-        <v>63</v>
+      <c r="C138">
+        <v>58</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -26568,8 +26462,8 @@
       <c r="B139" t="s">
         <v>205</v>
       </c>
-      <c r="F139">
-        <v>63</v>
+      <c r="C139">
+        <v>58</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -26753,6 +26647,9 @@
       <c r="B140" t="s">
         <v>206</v>
       </c>
+      <c r="C140">
+        <v>59</v>
+      </c>
       <c r="H140">
         <v>1</v>
       </c>
@@ -26935,6 +26832,9 @@
       <c r="B141" t="s">
         <v>207</v>
       </c>
+      <c r="C141">
+        <v>59</v>
+      </c>
       <c r="H141">
         <v>1</v>
       </c>
@@ -27117,6 +27017,9 @@
       <c r="B142" t="s">
         <v>208</v>
       </c>
+      <c r="C142">
+        <v>59</v>
+      </c>
       <c r="H142">
         <v>1</v>
       </c>
@@ -27299,6 +27202,9 @@
       <c r="B143" t="s">
         <v>209</v>
       </c>
+      <c r="C143">
+        <v>59</v>
+      </c>
       <c r="H143">
         <v>1</v>
       </c>
@@ -27481,6 +27387,9 @@
       <c r="B144" t="s">
         <v>210</v>
       </c>
+      <c r="C144">
+        <v>59</v>
+      </c>
       <c r="H144">
         <v>1</v>
       </c>
@@ -27663,6 +27572,9 @@
       <c r="B145" t="s">
         <v>211</v>
       </c>
+      <c r="C145">
+        <v>59</v>
+      </c>
       <c r="H145">
         <v>1</v>
       </c>
@@ -27845,6 +27757,9 @@
       <c r="B146" t="s">
         <v>212</v>
       </c>
+      <c r="C146">
+        <v>59</v>
+      </c>
       <c r="H146">
         <v>1</v>
       </c>
@@ -34033,6 +33948,9 @@
       <c r="B180" t="s">
         <v>246</v>
       </c>
+      <c r="C180">
+        <v>49</v>
+      </c>
       <c r="H180">
         <v>1</v>
       </c>
@@ -39675,6 +39593,9 @@
       <c r="B211" t="s">
         <v>277</v>
       </c>
+      <c r="C211">
+        <v>48</v>
+      </c>
       <c r="H211">
         <v>1</v>
       </c>
@@ -39857,6 +39778,9 @@
       <c r="B212" t="s">
         <v>278</v>
       </c>
+      <c r="C212">
+        <v>48</v>
+      </c>
       <c r="H212">
         <v>1</v>
       </c>
@@ -40039,6 +39963,9 @@
       <c r="B213" t="s">
         <v>279</v>
       </c>
+      <c r="C213">
+        <v>48</v>
+      </c>
       <c r="H213">
         <v>1</v>
       </c>
@@ -40220,6 +40147,9 @@
       </c>
       <c r="B214" t="s">
         <v>280</v>
+      </c>
+      <c r="C214">
+        <v>48</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -42794,8 +42724,8 @@
       <c r="B2" t="s">
         <v>79</v>
       </c>
-      <c r="F2">
-        <v>58</v>
+      <c r="C2">
+        <v>51</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -42979,8 +42909,8 @@
       <c r="B3" t="s">
         <v>80</v>
       </c>
-      <c r="F3">
-        <v>58</v>
+      <c r="C3">
+        <v>51</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -43164,8 +43094,8 @@
       <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="F4">
-        <v>59</v>
+      <c r="C4">
+        <v>52</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -43349,8 +43279,8 @@
       <c r="B5" t="s">
         <v>83</v>
       </c>
-      <c r="F5">
-        <v>59</v>
+      <c r="C5">
+        <v>52</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -43534,8 +43464,8 @@
       <c r="B6" t="s">
         <v>87</v>
       </c>
-      <c r="F6">
-        <v>59</v>
+      <c r="C6">
+        <v>52</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -43719,8 +43649,8 @@
       <c r="B7" t="s">
         <v>88</v>
       </c>
-      <c r="F7">
-        <v>59</v>
+      <c r="C7">
+        <v>52</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -43904,8 +43834,8 @@
       <c r="B8" t="s">
         <v>90</v>
       </c>
-      <c r="F8">
-        <v>59</v>
+      <c r="C8">
+        <v>52</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -44089,8 +44019,8 @@
       <c r="B9" t="s">
         <v>93</v>
       </c>
-      <c r="F9">
-        <v>60</v>
+      <c r="C9">
+        <v>50</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -44274,8 +44204,8 @@
       <c r="B10" t="s">
         <v>97</v>
       </c>
-      <c r="F10">
-        <v>60</v>
+      <c r="C10">
+        <v>50</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -44459,8 +44389,8 @@
       <c r="B11" t="s">
         <v>98</v>
       </c>
-      <c r="F11">
-        <v>60</v>
+      <c r="C11">
+        <v>50</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -44644,8 +44574,8 @@
       <c r="B12" t="s">
         <v>100</v>
       </c>
-      <c r="F12">
-        <v>60</v>
+      <c r="C12">
+        <v>50</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -44829,6 +44759,9 @@
       <c r="B13" t="s">
         <v>154</v>
       </c>
+      <c r="C13">
+        <v>53</v>
+      </c>
       <c r="H13">
         <v>1</v>
       </c>
@@ -45011,6 +44944,9 @@
       <c r="B14" t="s">
         <v>166</v>
       </c>
+      <c r="C14">
+        <v>54</v>
+      </c>
       <c r="H14">
         <v>1</v>
       </c>
@@ -45193,6 +45129,9 @@
       <c r="B15" t="s">
         <v>167</v>
       </c>
+      <c r="C15">
+        <v>54</v>
+      </c>
       <c r="H15">
         <v>1</v>
       </c>
@@ -45375,6 +45314,9 @@
       <c r="B16" t="s">
         <v>168</v>
       </c>
+      <c r="C16">
+        <v>54</v>
+      </c>
       <c r="H16">
         <v>1</v>
       </c>
@@ -45557,6 +45499,9 @@
       <c r="B17" t="s">
         <v>169</v>
       </c>
+      <c r="C17">
+        <v>54</v>
+      </c>
       <c r="H17">
         <v>1</v>
       </c>
@@ -45739,6 +45684,9 @@
       <c r="B18" t="s">
         <v>171</v>
       </c>
+      <c r="C18">
+        <v>54</v>
+      </c>
       <c r="H18">
         <v>1</v>
       </c>
@@ -45921,6 +45869,9 @@
       <c r="B19" t="s">
         <v>172</v>
       </c>
+      <c r="C19">
+        <v>54</v>
+      </c>
       <c r="H19">
         <v>1</v>
       </c>
@@ -46103,6 +46054,9 @@
       <c r="B20" t="s">
         <v>199</v>
       </c>
+      <c r="C20">
+        <v>57</v>
+      </c>
       <c r="H20">
         <v>1</v>
       </c>
@@ -46285,6 +46239,9 @@
       <c r="B21" t="s">
         <v>200</v>
       </c>
+      <c r="C21">
+        <v>55</v>
+      </c>
       <c r="H21">
         <v>1</v>
       </c>
@@ -46467,6 +46424,9 @@
       <c r="B22" t="s">
         <v>201</v>
       </c>
+      <c r="C22">
+        <v>56</v>
+      </c>
       <c r="H22">
         <v>1</v>
       </c>
@@ -46649,6 +46609,9 @@
       <c r="B23" t="s">
         <v>202</v>
       </c>
+      <c r="C23">
+        <v>57</v>
+      </c>
       <c r="H23">
         <v>1</v>
       </c>
@@ -46831,8 +46794,8 @@
       <c r="B24" t="s">
         <v>204</v>
       </c>
-      <c r="F24">
-        <v>63</v>
+      <c r="C24">
+        <v>58</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -47016,8 +46979,8 @@
       <c r="B25" t="s">
         <v>205</v>
       </c>
-      <c r="F25">
-        <v>63</v>
+      <c r="C25">
+        <v>58</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -47201,6 +47164,9 @@
       <c r="B26" t="s">
         <v>206</v>
       </c>
+      <c r="C26">
+        <v>59</v>
+      </c>
       <c r="H26">
         <v>1</v>
       </c>
@@ -47383,6 +47349,9 @@
       <c r="B27" t="s">
         <v>207</v>
       </c>
+      <c r="C27">
+        <v>59</v>
+      </c>
       <c r="H27">
         <v>1</v>
       </c>
@@ -47565,6 +47534,9 @@
       <c r="B28" t="s">
         <v>208</v>
       </c>
+      <c r="C28">
+        <v>59</v>
+      </c>
       <c r="H28">
         <v>1</v>
       </c>
@@ -47747,6 +47719,9 @@
       <c r="B29" t="s">
         <v>209</v>
       </c>
+      <c r="C29">
+        <v>59</v>
+      </c>
       <c r="H29">
         <v>1</v>
       </c>
@@ -47929,6 +47904,9 @@
       <c r="B30" t="s">
         <v>210</v>
       </c>
+      <c r="C30">
+        <v>59</v>
+      </c>
       <c r="H30">
         <v>1</v>
       </c>
@@ -48111,6 +48089,9 @@
       <c r="B31" t="s">
         <v>211</v>
       </c>
+      <c r="C31">
+        <v>59</v>
+      </c>
       <c r="H31">
         <v>1</v>
       </c>
@@ -48293,6 +48274,9 @@
       <c r="B32" t="s">
         <v>212</v>
       </c>
+      <c r="C32">
+        <v>59</v>
+      </c>
       <c r="H32">
         <v>1</v>
       </c>
@@ -48657,6 +48641,9 @@
       <c r="B34" t="s">
         <v>246</v>
       </c>
+      <c r="C34">
+        <v>49</v>
+      </c>
       <c r="H34">
         <v>1</v>
       </c>
@@ -48839,6 +48826,9 @@
       <c r="B35" t="s">
         <v>277</v>
       </c>
+      <c r="C35">
+        <v>48</v>
+      </c>
       <c r="H35">
         <v>1</v>
       </c>
@@ -49021,6 +49011,9 @@
       <c r="B36" t="s">
         <v>278</v>
       </c>
+      <c r="C36">
+        <v>48</v>
+      </c>
       <c r="H36">
         <v>1</v>
       </c>
@@ -49203,6 +49196,9 @@
       <c r="B37" t="s">
         <v>279</v>
       </c>
+      <c r="C37">
+        <v>48</v>
+      </c>
       <c r="H37">
         <v>1</v>
       </c>
@@ -49384,6 +49380,9 @@
       </c>
       <c r="B38" t="s">
         <v>280</v>
+      </c>
+      <c r="C38">
+        <v>48</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -49567,4802 +49566,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BM26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:65">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:65">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2">
-        <v>58</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0.02</v>
-      </c>
-      <c r="Q2">
-        <v>0.04</v>
-      </c>
-      <c r="R2">
-        <v>0.06</v>
-      </c>
-      <c r="S2">
-        <v>0.08</v>
-      </c>
-      <c r="T2">
-        <v>0.1</v>
-      </c>
-      <c r="U2">
-        <v>0.12</v>
-      </c>
-      <c r="V2">
-        <v>0.14</v>
-      </c>
-      <c r="W2">
-        <v>0.16</v>
-      </c>
-      <c r="X2">
-        <v>0.18</v>
-      </c>
-      <c r="Y2">
-        <v>0.2</v>
-      </c>
-      <c r="Z2">
-        <v>0.22</v>
-      </c>
-      <c r="AA2">
-        <v>0.24</v>
-      </c>
-      <c r="AB2">
-        <v>0.26</v>
-      </c>
-      <c r="AC2">
-        <v>0.28</v>
-      </c>
-      <c r="AD2">
-        <v>0.3</v>
-      </c>
-      <c r="AE2">
-        <v>0.32</v>
-      </c>
-      <c r="AF2">
-        <v>0.34</v>
-      </c>
-      <c r="AG2">
-        <v>0.36</v>
-      </c>
-      <c r="AH2">
-        <v>0.38</v>
-      </c>
-      <c r="AI2">
-        <v>0.4</v>
-      </c>
-      <c r="AJ2">
-        <v>0.42</v>
-      </c>
-      <c r="AK2">
-        <v>0.44</v>
-      </c>
-      <c r="AL2">
-        <v>0.46</v>
-      </c>
-      <c r="AM2">
-        <v>0.48</v>
-      </c>
-      <c r="AN2">
-        <v>0.5</v>
-      </c>
-      <c r="AO2">
-        <v>0.52</v>
-      </c>
-      <c r="AP2">
-        <v>0.54</v>
-      </c>
-      <c r="AQ2">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR2">
-        <v>0.58</v>
-      </c>
-      <c r="AS2">
-        <v>0.6</v>
-      </c>
-      <c r="AT2">
-        <v>0.62</v>
-      </c>
-      <c r="AU2">
-        <v>0.64</v>
-      </c>
-      <c r="AV2">
-        <v>0.66</v>
-      </c>
-      <c r="AW2">
-        <v>0.68</v>
-      </c>
-      <c r="AX2">
-        <v>0.7</v>
-      </c>
-      <c r="AY2">
-        <v>0.72</v>
-      </c>
-      <c r="AZ2">
-        <v>0.74</v>
-      </c>
-      <c r="BA2">
-        <v>0.76</v>
-      </c>
-      <c r="BB2">
-        <v>0.78</v>
-      </c>
-      <c r="BC2">
-        <v>0.8</v>
-      </c>
-      <c r="BD2">
-        <v>0.82</v>
-      </c>
-      <c r="BE2">
-        <v>0.84</v>
-      </c>
-      <c r="BF2">
-        <v>0.86</v>
-      </c>
-      <c r="BG2">
-        <v>0.88</v>
-      </c>
-      <c r="BH2">
-        <v>0.9</v>
-      </c>
-      <c r="BI2">
-        <v>0.92</v>
-      </c>
-      <c r="BJ2">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BK2">
-        <v>0.96</v>
-      </c>
-      <c r="BL2">
-        <v>0.98</v>
-      </c>
-      <c r="BM2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:65">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3">
-        <v>58</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0.98</v>
-      </c>
-      <c r="Q3">
-        <v>0.96</v>
-      </c>
-      <c r="R3">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="S3">
-        <v>0.92</v>
-      </c>
-      <c r="T3">
-        <v>0.9</v>
-      </c>
-      <c r="U3">
-        <v>0.88</v>
-      </c>
-      <c r="V3">
-        <v>0.86</v>
-      </c>
-      <c r="W3">
-        <v>0.84</v>
-      </c>
-      <c r="X3">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="Y3">
-        <v>0.8</v>
-      </c>
-      <c r="Z3">
-        <v>0.78</v>
-      </c>
-      <c r="AA3">
-        <v>0.76</v>
-      </c>
-      <c r="AB3">
-        <v>0.74</v>
-      </c>
-      <c r="AC3">
-        <v>0.72</v>
-      </c>
-      <c r="AD3">
-        <v>0.7</v>
-      </c>
-      <c r="AE3">
-        <v>0.6799999999999999</v>
-      </c>
-      <c r="AF3">
-        <v>0.6599999999999999</v>
-      </c>
-      <c r="AG3">
-        <v>0.64</v>
-      </c>
-      <c r="AH3">
-        <v>0.62</v>
-      </c>
-      <c r="AI3">
-        <v>0.6</v>
-      </c>
-      <c r="AJ3">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="AK3">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AL3">
-        <v>0.54</v>
-      </c>
-      <c r="AM3">
-        <v>0.52</v>
-      </c>
-      <c r="AN3">
-        <v>0.5</v>
-      </c>
-      <c r="AO3">
-        <v>0.48</v>
-      </c>
-      <c r="AP3">
-        <v>0.46</v>
-      </c>
-      <c r="AQ3">
-        <v>0.4399999999999999</v>
-      </c>
-      <c r="AR3">
-        <v>0.42</v>
-      </c>
-      <c r="AS3">
-        <v>0.4</v>
-      </c>
-      <c r="AT3">
-        <v>0.38</v>
-      </c>
-      <c r="AU3">
-        <v>0.36</v>
-      </c>
-      <c r="AV3">
-        <v>0.34</v>
-      </c>
-      <c r="AW3">
-        <v>0.32</v>
-      </c>
-      <c r="AX3">
-        <v>0.3</v>
-      </c>
-      <c r="AY3">
-        <v>0.28</v>
-      </c>
-      <c r="AZ3">
-        <v>0.26</v>
-      </c>
-      <c r="BA3">
-        <v>0.24</v>
-      </c>
-      <c r="BB3">
-        <v>0.22</v>
-      </c>
-      <c r="BC3">
-        <v>0.2</v>
-      </c>
-      <c r="BD3">
-        <v>0.18</v>
-      </c>
-      <c r="BE3">
-        <v>0.16</v>
-      </c>
-      <c r="BF3">
-        <v>0.14</v>
-      </c>
-      <c r="BG3">
-        <v>0.12</v>
-      </c>
-      <c r="BH3">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="BI3">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="BJ3">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="BK3">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="BL3">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="BM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:65">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4">
-        <v>59</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0.006</v>
-      </c>
-      <c r="Q4">
-        <v>0.012</v>
-      </c>
-      <c r="R4">
-        <v>0.018</v>
-      </c>
-      <c r="S4">
-        <v>0.024</v>
-      </c>
-      <c r="T4">
-        <v>0.03</v>
-      </c>
-      <c r="U4">
-        <v>0.036</v>
-      </c>
-      <c r="V4">
-        <v>0.042</v>
-      </c>
-      <c r="W4">
-        <v>0.048</v>
-      </c>
-      <c r="X4">
-        <v>0.054</v>
-      </c>
-      <c r="Y4">
-        <v>0.06</v>
-      </c>
-      <c r="Z4">
-        <v>0.066</v>
-      </c>
-      <c r="AA4">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AB4">
-        <v>0.078</v>
-      </c>
-      <c r="AC4">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AD4">
-        <v>0.09</v>
-      </c>
-      <c r="AE4">
-        <v>0.096</v>
-      </c>
-      <c r="AF4">
-        <v>0.102</v>
-      </c>
-      <c r="AG4">
-        <v>0.108</v>
-      </c>
-      <c r="AH4">
-        <v>0.114</v>
-      </c>
-      <c r="AI4">
-        <v>0.12</v>
-      </c>
-      <c r="AJ4">
-        <v>0.126</v>
-      </c>
-      <c r="AK4">
-        <v>0.132</v>
-      </c>
-      <c r="AL4">
-        <v>0.138</v>
-      </c>
-      <c r="AM4">
-        <v>0.144</v>
-      </c>
-      <c r="AN4">
-        <v>0.15</v>
-      </c>
-      <c r="AO4">
-        <v>0.156</v>
-      </c>
-      <c r="AP4">
-        <v>0.162</v>
-      </c>
-      <c r="AQ4">
-        <v>0.168</v>
-      </c>
-      <c r="AR4">
-        <v>0.174</v>
-      </c>
-      <c r="AS4">
-        <v>0.18</v>
-      </c>
-      <c r="AT4">
-        <v>0.186</v>
-      </c>
-      <c r="AU4">
-        <v>0.192</v>
-      </c>
-      <c r="AV4">
-        <v>0.198</v>
-      </c>
-      <c r="AW4">
-        <v>0.204</v>
-      </c>
-      <c r="AX4">
-        <v>0.21</v>
-      </c>
-      <c r="AY4">
-        <v>0.216</v>
-      </c>
-      <c r="AZ4">
-        <v>0.222</v>
-      </c>
-      <c r="BA4">
-        <v>0.228</v>
-      </c>
-      <c r="BB4">
-        <v>0.234</v>
-      </c>
-      <c r="BC4">
-        <v>0.24</v>
-      </c>
-      <c r="BD4">
-        <v>0.246</v>
-      </c>
-      <c r="BE4">
-        <v>0.252</v>
-      </c>
-      <c r="BF4">
-        <v>0.258</v>
-      </c>
-      <c r="BG4">
-        <v>0.264</v>
-      </c>
-      <c r="BH4">
-        <v>0.27</v>
-      </c>
-      <c r="BI4">
-        <v>0.276</v>
-      </c>
-      <c r="BJ4">
-        <v>0.282</v>
-      </c>
-      <c r="BK4">
-        <v>0.288</v>
-      </c>
-      <c r="BL4">
-        <v>0.294</v>
-      </c>
-      <c r="BM4">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:65">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5">
-        <v>59</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0.006</v>
-      </c>
-      <c r="Q5">
-        <v>0.012</v>
-      </c>
-      <c r="R5">
-        <v>0.018</v>
-      </c>
-      <c r="S5">
-        <v>0.024</v>
-      </c>
-      <c r="T5">
-        <v>0.03</v>
-      </c>
-      <c r="U5">
-        <v>0.036</v>
-      </c>
-      <c r="V5">
-        <v>0.042</v>
-      </c>
-      <c r="W5">
-        <v>0.048</v>
-      </c>
-      <c r="X5">
-        <v>0.054</v>
-      </c>
-      <c r="Y5">
-        <v>0.06</v>
-      </c>
-      <c r="Z5">
-        <v>0.066</v>
-      </c>
-      <c r="AA5">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AB5">
-        <v>0.078</v>
-      </c>
-      <c r="AC5">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AD5">
-        <v>0.09</v>
-      </c>
-      <c r="AE5">
-        <v>0.096</v>
-      </c>
-      <c r="AF5">
-        <v>0.102</v>
-      </c>
-      <c r="AG5">
-        <v>0.108</v>
-      </c>
-      <c r="AH5">
-        <v>0.114</v>
-      </c>
-      <c r="AI5">
-        <v>0.12</v>
-      </c>
-      <c r="AJ5">
-        <v>0.126</v>
-      </c>
-      <c r="AK5">
-        <v>0.132</v>
-      </c>
-      <c r="AL5">
-        <v>0.138</v>
-      </c>
-      <c r="AM5">
-        <v>0.144</v>
-      </c>
-      <c r="AN5">
-        <v>0.15</v>
-      </c>
-      <c r="AO5">
-        <v>0.156</v>
-      </c>
-      <c r="AP5">
-        <v>0.162</v>
-      </c>
-      <c r="AQ5">
-        <v>0.168</v>
-      </c>
-      <c r="AR5">
-        <v>0.174</v>
-      </c>
-      <c r="AS5">
-        <v>0.18</v>
-      </c>
-      <c r="AT5">
-        <v>0.186</v>
-      </c>
-      <c r="AU5">
-        <v>0.192</v>
-      </c>
-      <c r="AV5">
-        <v>0.198</v>
-      </c>
-      <c r="AW5">
-        <v>0.204</v>
-      </c>
-      <c r="AX5">
-        <v>0.21</v>
-      </c>
-      <c r="AY5">
-        <v>0.216</v>
-      </c>
-      <c r="AZ5">
-        <v>0.222</v>
-      </c>
-      <c r="BA5">
-        <v>0.228</v>
-      </c>
-      <c r="BB5">
-        <v>0.234</v>
-      </c>
-      <c r="BC5">
-        <v>0.24</v>
-      </c>
-      <c r="BD5">
-        <v>0.246</v>
-      </c>
-      <c r="BE5">
-        <v>0.252</v>
-      </c>
-      <c r="BF5">
-        <v>0.258</v>
-      </c>
-      <c r="BG5">
-        <v>0.264</v>
-      </c>
-      <c r="BH5">
-        <v>0.27</v>
-      </c>
-      <c r="BI5">
-        <v>0.276</v>
-      </c>
-      <c r="BJ5">
-        <v>0.282</v>
-      </c>
-      <c r="BK5">
-        <v>0.288</v>
-      </c>
-      <c r="BL5">
-        <v>0.294</v>
-      </c>
-      <c r="BM5">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:65">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6">
-        <v>59</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0.004</v>
-      </c>
-      <c r="Q6">
-        <v>0.008</v>
-      </c>
-      <c r="R6">
-        <v>0.012</v>
-      </c>
-      <c r="S6">
-        <v>0.016</v>
-      </c>
-      <c r="T6">
-        <v>0.02</v>
-      </c>
-      <c r="U6">
-        <v>0.024</v>
-      </c>
-      <c r="V6">
-        <v>0.028</v>
-      </c>
-      <c r="W6">
-        <v>0.032</v>
-      </c>
-      <c r="X6">
-        <v>0.036</v>
-      </c>
-      <c r="Y6">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="Z6">
-        <v>0.044</v>
-      </c>
-      <c r="AA6">
-        <v>0.048</v>
-      </c>
-      <c r="AB6">
-        <v>0.052</v>
-      </c>
-      <c r="AC6">
-        <v>0.05600000000000001</v>
-      </c>
-      <c r="AD6">
-        <v>0.06</v>
-      </c>
-      <c r="AE6">
-        <v>0.064</v>
-      </c>
-      <c r="AF6">
-        <v>0.068</v>
-      </c>
-      <c r="AG6">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AH6">
-        <v>0.07600000000000001</v>
-      </c>
-      <c r="AI6">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="AJ6">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AK6">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="AL6">
-        <v>0.09200000000000001</v>
-      </c>
-      <c r="AM6">
-        <v>0.096</v>
-      </c>
-      <c r="AN6">
-        <v>0.1</v>
-      </c>
-      <c r="AO6">
-        <v>0.104</v>
-      </c>
-      <c r="AP6">
-        <v>0.108</v>
-      </c>
-      <c r="AQ6">
-        <v>0.112</v>
-      </c>
-      <c r="AR6">
-        <v>0.116</v>
-      </c>
-      <c r="AS6">
-        <v>0.12</v>
-      </c>
-      <c r="AT6">
-        <v>0.124</v>
-      </c>
-      <c r="AU6">
-        <v>0.128</v>
-      </c>
-      <c r="AV6">
-        <v>0.132</v>
-      </c>
-      <c r="AW6">
-        <v>0.136</v>
-      </c>
-      <c r="AX6">
-        <v>0.14</v>
-      </c>
-      <c r="AY6">
-        <v>0.144</v>
-      </c>
-      <c r="AZ6">
-        <v>0.148</v>
-      </c>
-      <c r="BA6">
-        <v>0.152</v>
-      </c>
-      <c r="BB6">
-        <v>0.156</v>
-      </c>
-      <c r="BC6">
-        <v>0.16</v>
-      </c>
-      <c r="BD6">
-        <v>0.164</v>
-      </c>
-      <c r="BE6">
-        <v>0.168</v>
-      </c>
-      <c r="BF6">
-        <v>0.172</v>
-      </c>
-      <c r="BG6">
-        <v>0.176</v>
-      </c>
-      <c r="BH6">
-        <v>0.18</v>
-      </c>
-      <c r="BI6">
-        <v>0.184</v>
-      </c>
-      <c r="BJ6">
-        <v>0.188</v>
-      </c>
-      <c r="BK6">
-        <v>0.192</v>
-      </c>
-      <c r="BL6">
-        <v>0.196</v>
-      </c>
-      <c r="BM6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:65">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7">
-        <v>59</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0.004</v>
-      </c>
-      <c r="Q7">
-        <v>0.008</v>
-      </c>
-      <c r="R7">
-        <v>0.012</v>
-      </c>
-      <c r="S7">
-        <v>0.016</v>
-      </c>
-      <c r="T7">
-        <v>0.02</v>
-      </c>
-      <c r="U7">
-        <v>0.024</v>
-      </c>
-      <c r="V7">
-        <v>0.028</v>
-      </c>
-      <c r="W7">
-        <v>0.032</v>
-      </c>
-      <c r="X7">
-        <v>0.036</v>
-      </c>
-      <c r="Y7">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="Z7">
-        <v>0.044</v>
-      </c>
-      <c r="AA7">
-        <v>0.048</v>
-      </c>
-      <c r="AB7">
-        <v>0.052</v>
-      </c>
-      <c r="AC7">
-        <v>0.05600000000000001</v>
-      </c>
-      <c r="AD7">
-        <v>0.06</v>
-      </c>
-      <c r="AE7">
-        <v>0.064</v>
-      </c>
-      <c r="AF7">
-        <v>0.068</v>
-      </c>
-      <c r="AG7">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AH7">
-        <v>0.07600000000000001</v>
-      </c>
-      <c r="AI7">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="AJ7">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AK7">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="AL7">
-        <v>0.09200000000000001</v>
-      </c>
-      <c r="AM7">
-        <v>0.096</v>
-      </c>
-      <c r="AN7">
-        <v>0.1</v>
-      </c>
-      <c r="AO7">
-        <v>0.104</v>
-      </c>
-      <c r="AP7">
-        <v>0.108</v>
-      </c>
-      <c r="AQ7">
-        <v>0.112</v>
-      </c>
-      <c r="AR7">
-        <v>0.116</v>
-      </c>
-      <c r="AS7">
-        <v>0.12</v>
-      </c>
-      <c r="AT7">
-        <v>0.124</v>
-      </c>
-      <c r="AU7">
-        <v>0.128</v>
-      </c>
-      <c r="AV7">
-        <v>0.132</v>
-      </c>
-      <c r="AW7">
-        <v>0.136</v>
-      </c>
-      <c r="AX7">
-        <v>0.14</v>
-      </c>
-      <c r="AY7">
-        <v>0.144</v>
-      </c>
-      <c r="AZ7">
-        <v>0.148</v>
-      </c>
-      <c r="BA7">
-        <v>0.152</v>
-      </c>
-      <c r="BB7">
-        <v>0.156</v>
-      </c>
-      <c r="BC7">
-        <v>0.16</v>
-      </c>
-      <c r="BD7">
-        <v>0.164</v>
-      </c>
-      <c r="BE7">
-        <v>0.168</v>
-      </c>
-      <c r="BF7">
-        <v>0.172</v>
-      </c>
-      <c r="BG7">
-        <v>0.176</v>
-      </c>
-      <c r="BH7">
-        <v>0.18</v>
-      </c>
-      <c r="BI7">
-        <v>0.184</v>
-      </c>
-      <c r="BJ7">
-        <v>0.188</v>
-      </c>
-      <c r="BK7">
-        <v>0.192</v>
-      </c>
-      <c r="BL7">
-        <v>0.196</v>
-      </c>
-      <c r="BM7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:65">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8">
-        <v>59</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0.98</v>
-      </c>
-      <c r="Q8">
-        <v>0.96</v>
-      </c>
-      <c r="R8">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="S8">
-        <v>0.92</v>
-      </c>
-      <c r="T8">
-        <v>0.9</v>
-      </c>
-      <c r="U8">
-        <v>0.88</v>
-      </c>
-      <c r="V8">
-        <v>0.86</v>
-      </c>
-      <c r="W8">
-        <v>0.84</v>
-      </c>
-      <c r="X8">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="Y8">
-        <v>0.8</v>
-      </c>
-      <c r="Z8">
-        <v>0.78</v>
-      </c>
-      <c r="AA8">
-        <v>0.76</v>
-      </c>
-      <c r="AB8">
-        <v>0.74</v>
-      </c>
-      <c r="AC8">
-        <v>0.72</v>
-      </c>
-      <c r="AD8">
-        <v>0.7</v>
-      </c>
-      <c r="AE8">
-        <v>0.6799999999999999</v>
-      </c>
-      <c r="AF8">
-        <v>0.6599999999999999</v>
-      </c>
-      <c r="AG8">
-        <v>0.64</v>
-      </c>
-      <c r="AH8">
-        <v>0.62</v>
-      </c>
-      <c r="AI8">
-        <v>0.6</v>
-      </c>
-      <c r="AJ8">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="AK8">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AL8">
-        <v>0.54</v>
-      </c>
-      <c r="AM8">
-        <v>0.52</v>
-      </c>
-      <c r="AN8">
-        <v>0.5</v>
-      </c>
-      <c r="AO8">
-        <v>0.48</v>
-      </c>
-      <c r="AP8">
-        <v>0.46</v>
-      </c>
-      <c r="AQ8">
-        <v>0.4399999999999999</v>
-      </c>
-      <c r="AR8">
-        <v>0.42</v>
-      </c>
-      <c r="AS8">
-        <v>0.4</v>
-      </c>
-      <c r="AT8">
-        <v>0.38</v>
-      </c>
-      <c r="AU8">
-        <v>0.36</v>
-      </c>
-      <c r="AV8">
-        <v>0.34</v>
-      </c>
-      <c r="AW8">
-        <v>0.32</v>
-      </c>
-      <c r="AX8">
-        <v>0.3</v>
-      </c>
-      <c r="AY8">
-        <v>0.28</v>
-      </c>
-      <c r="AZ8">
-        <v>0.26</v>
-      </c>
-      <c r="BA8">
-        <v>0.24</v>
-      </c>
-      <c r="BB8">
-        <v>0.22</v>
-      </c>
-      <c r="BC8">
-        <v>0.2</v>
-      </c>
-      <c r="BD8">
-        <v>0.18</v>
-      </c>
-      <c r="BE8">
-        <v>0.16</v>
-      </c>
-      <c r="BF8">
-        <v>0.14</v>
-      </c>
-      <c r="BG8">
-        <v>0.12</v>
-      </c>
-      <c r="BH8">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="BI8">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="BJ8">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="BK8">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="BL8">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="BM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:65">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9">
-        <v>60</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0.016</v>
-      </c>
-      <c r="Q9">
-        <v>0.032</v>
-      </c>
-      <c r="R9">
-        <v>0.048</v>
-      </c>
-      <c r="S9">
-        <v>0.064</v>
-      </c>
-      <c r="T9">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="U9">
-        <v>0.096</v>
-      </c>
-      <c r="V9">
-        <v>0.112</v>
-      </c>
-      <c r="W9">
-        <v>0.128</v>
-      </c>
-      <c r="X9">
-        <v>0.144</v>
-      </c>
-      <c r="Y9">
-        <v>0.16</v>
-      </c>
-      <c r="Z9">
-        <v>0.176</v>
-      </c>
-      <c r="AA9">
-        <v>0.192</v>
-      </c>
-      <c r="AB9">
-        <v>0.208</v>
-      </c>
-      <c r="AC9">
-        <v>0.224</v>
-      </c>
-      <c r="AD9">
-        <v>0.24</v>
-      </c>
-      <c r="AE9">
-        <v>0.256</v>
-      </c>
-      <c r="AF9">
-        <v>0.272</v>
-      </c>
-      <c r="AG9">
-        <v>0.288</v>
-      </c>
-      <c r="AH9">
-        <v>0.304</v>
-      </c>
-      <c r="AI9">
-        <v>0.3200000000000001</v>
-      </c>
-      <c r="AJ9">
-        <v>0.336</v>
-      </c>
-      <c r="AK9">
-        <v>0.352</v>
-      </c>
-      <c r="AL9">
-        <v>0.368</v>
-      </c>
-      <c r="AM9">
-        <v>0.384</v>
-      </c>
-      <c r="AN9">
-        <v>0.4</v>
-      </c>
-      <c r="AO9">
-        <v>0.416</v>
-      </c>
-      <c r="AP9">
-        <v>0.4320000000000001</v>
-      </c>
-      <c r="AQ9">
-        <v>0.4480000000000001</v>
-      </c>
-      <c r="AR9">
-        <v>0.464</v>
-      </c>
-      <c r="AS9">
-        <v>0.48</v>
-      </c>
-      <c r="AT9">
-        <v>0.496</v>
-      </c>
-      <c r="AU9">
-        <v>0.512</v>
-      </c>
-      <c r="AV9">
-        <v>0.528</v>
-      </c>
-      <c r="AW9">
-        <v>0.544</v>
-      </c>
-      <c r="AX9">
-        <v>0.5599999999999999</v>
-      </c>
-      <c r="AY9">
-        <v>0.576</v>
-      </c>
-      <c r="AZ9">
-        <v>0.592</v>
-      </c>
-      <c r="BA9">
-        <v>0.6080000000000001</v>
-      </c>
-      <c r="BB9">
-        <v>0.6240000000000001</v>
-      </c>
-      <c r="BC9">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="BD9">
-        <v>0.656</v>
-      </c>
-      <c r="BE9">
-        <v>0.672</v>
-      </c>
-      <c r="BF9">
-        <v>0.6880000000000001</v>
-      </c>
-      <c r="BG9">
-        <v>0.7040000000000001</v>
-      </c>
-      <c r="BH9">
-        <v>0.7200000000000001</v>
-      </c>
-      <c r="BI9">
-        <v>0.7360000000000001</v>
-      </c>
-      <c r="BJ9">
-        <v>0.752</v>
-      </c>
-      <c r="BK9">
-        <v>0.768</v>
-      </c>
-      <c r="BL9">
-        <v>0.784</v>
-      </c>
-      <c r="BM9">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:65">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10">
-        <v>60</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0.002</v>
-      </c>
-      <c r="Q10">
-        <v>0.004</v>
-      </c>
-      <c r="R10">
-        <v>0.006</v>
-      </c>
-      <c r="S10">
-        <v>0.008</v>
-      </c>
-      <c r="T10">
-        <v>0.01</v>
-      </c>
-      <c r="U10">
-        <v>0.012</v>
-      </c>
-      <c r="V10">
-        <v>0.014</v>
-      </c>
-      <c r="W10">
-        <v>0.016</v>
-      </c>
-      <c r="X10">
-        <v>0.018</v>
-      </c>
-      <c r="Y10">
-        <v>0.02</v>
-      </c>
-      <c r="Z10">
-        <v>0.022</v>
-      </c>
-      <c r="AA10">
-        <v>0.024</v>
-      </c>
-      <c r="AB10">
-        <v>0.026</v>
-      </c>
-      <c r="AC10">
-        <v>0.028</v>
-      </c>
-      <c r="AD10">
-        <v>0.03</v>
-      </c>
-      <c r="AE10">
-        <v>0.032</v>
-      </c>
-      <c r="AF10">
-        <v>0.034</v>
-      </c>
-      <c r="AG10">
-        <v>0.036</v>
-      </c>
-      <c r="AH10">
-        <v>0.03800000000000001</v>
-      </c>
-      <c r="AI10">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="AJ10">
-        <v>0.042</v>
-      </c>
-      <c r="AK10">
-        <v>0.044</v>
-      </c>
-      <c r="AL10">
-        <v>0.04600000000000001</v>
-      </c>
-      <c r="AM10">
-        <v>0.048</v>
-      </c>
-      <c r="AN10">
-        <v>0.05</v>
-      </c>
-      <c r="AO10">
-        <v>0.052</v>
-      </c>
-      <c r="AP10">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="AQ10">
-        <v>0.05600000000000001</v>
-      </c>
-      <c r="AR10">
-        <v>0.058</v>
-      </c>
-      <c r="AS10">
-        <v>0.06</v>
-      </c>
-      <c r="AT10">
-        <v>0.062</v>
-      </c>
-      <c r="AU10">
-        <v>0.064</v>
-      </c>
-      <c r="AV10">
-        <v>0.066</v>
-      </c>
-      <c r="AW10">
-        <v>0.068</v>
-      </c>
-      <c r="AX10">
-        <v>0.06999999999999999</v>
-      </c>
-      <c r="AY10">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AZ10">
-        <v>0.074</v>
-      </c>
-      <c r="BA10">
-        <v>0.07600000000000001</v>
-      </c>
-      <c r="BB10">
-        <v>0.07800000000000001</v>
-      </c>
-      <c r="BC10">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="BD10">
-        <v>0.082</v>
-      </c>
-      <c r="BE10">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="BF10">
-        <v>0.08600000000000001</v>
-      </c>
-      <c r="BG10">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="BH10">
-        <v>0.09000000000000001</v>
-      </c>
-      <c r="BI10">
-        <v>0.09200000000000001</v>
-      </c>
-      <c r="BJ10">
-        <v>0.094</v>
-      </c>
-      <c r="BK10">
-        <v>0.096</v>
-      </c>
-      <c r="BL10">
-        <v>0.098</v>
-      </c>
-      <c r="BM10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:65">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11">
-        <v>60</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0.002</v>
-      </c>
-      <c r="Q11">
-        <v>0.004</v>
-      </c>
-      <c r="R11">
-        <v>0.006</v>
-      </c>
-      <c r="S11">
-        <v>0.008</v>
-      </c>
-      <c r="T11">
-        <v>0.01</v>
-      </c>
-      <c r="U11">
-        <v>0.012</v>
-      </c>
-      <c r="V11">
-        <v>0.014</v>
-      </c>
-      <c r="W11">
-        <v>0.016</v>
-      </c>
-      <c r="X11">
-        <v>0.018</v>
-      </c>
-      <c r="Y11">
-        <v>0.02</v>
-      </c>
-      <c r="Z11">
-        <v>0.022</v>
-      </c>
-      <c r="AA11">
-        <v>0.024</v>
-      </c>
-      <c r="AB11">
-        <v>0.026</v>
-      </c>
-      <c r="AC11">
-        <v>0.028</v>
-      </c>
-      <c r="AD11">
-        <v>0.03</v>
-      </c>
-      <c r="AE11">
-        <v>0.032</v>
-      </c>
-      <c r="AF11">
-        <v>0.034</v>
-      </c>
-      <c r="AG11">
-        <v>0.036</v>
-      </c>
-      <c r="AH11">
-        <v>0.03800000000000001</v>
-      </c>
-      <c r="AI11">
-        <v>0.04000000000000001</v>
-      </c>
-      <c r="AJ11">
-        <v>0.042</v>
-      </c>
-      <c r="AK11">
-        <v>0.044</v>
-      </c>
-      <c r="AL11">
-        <v>0.04600000000000001</v>
-      </c>
-      <c r="AM11">
-        <v>0.048</v>
-      </c>
-      <c r="AN11">
-        <v>0.05</v>
-      </c>
-      <c r="AO11">
-        <v>0.052</v>
-      </c>
-      <c r="AP11">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="AQ11">
-        <v>0.05600000000000001</v>
-      </c>
-      <c r="AR11">
-        <v>0.058</v>
-      </c>
-      <c r="AS11">
-        <v>0.06</v>
-      </c>
-      <c r="AT11">
-        <v>0.062</v>
-      </c>
-      <c r="AU11">
-        <v>0.064</v>
-      </c>
-      <c r="AV11">
-        <v>0.066</v>
-      </c>
-      <c r="AW11">
-        <v>0.068</v>
-      </c>
-      <c r="AX11">
-        <v>0.06999999999999999</v>
-      </c>
-      <c r="AY11">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AZ11">
-        <v>0.074</v>
-      </c>
-      <c r="BA11">
-        <v>0.07600000000000001</v>
-      </c>
-      <c r="BB11">
-        <v>0.07800000000000001</v>
-      </c>
-      <c r="BC11">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="BD11">
-        <v>0.082</v>
-      </c>
-      <c r="BE11">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="BF11">
-        <v>0.08600000000000001</v>
-      </c>
-      <c r="BG11">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="BH11">
-        <v>0.09000000000000001</v>
-      </c>
-      <c r="BI11">
-        <v>0.09200000000000001</v>
-      </c>
-      <c r="BJ11">
-        <v>0.094</v>
-      </c>
-      <c r="BK11">
-        <v>0.096</v>
-      </c>
-      <c r="BL11">
-        <v>0.098</v>
-      </c>
-      <c r="BM11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:65">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12">
-        <v>60</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>0.98</v>
-      </c>
-      <c r="Q12">
-        <v>0.96</v>
-      </c>
-      <c r="R12">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="S12">
-        <v>0.92</v>
-      </c>
-      <c r="T12">
-        <v>0.9</v>
-      </c>
-      <c r="U12">
-        <v>0.88</v>
-      </c>
-      <c r="V12">
-        <v>0.86</v>
-      </c>
-      <c r="W12">
-        <v>0.84</v>
-      </c>
-      <c r="X12">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="Y12">
-        <v>0.8</v>
-      </c>
-      <c r="Z12">
-        <v>0.78</v>
-      </c>
-      <c r="AA12">
-        <v>0.76</v>
-      </c>
-      <c r="AB12">
-        <v>0.74</v>
-      </c>
-      <c r="AC12">
-        <v>0.72</v>
-      </c>
-      <c r="AD12">
-        <v>0.7</v>
-      </c>
-      <c r="AE12">
-        <v>0.6799999999999999</v>
-      </c>
-      <c r="AF12">
-        <v>0.6599999999999999</v>
-      </c>
-      <c r="AG12">
-        <v>0.64</v>
-      </c>
-      <c r="AH12">
-        <v>0.62</v>
-      </c>
-      <c r="AI12">
-        <v>0.6</v>
-      </c>
-      <c r="AJ12">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="AK12">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AL12">
-        <v>0.54</v>
-      </c>
-      <c r="AM12">
-        <v>0.52</v>
-      </c>
-      <c r="AN12">
-        <v>0.5</v>
-      </c>
-      <c r="AO12">
-        <v>0.48</v>
-      </c>
-      <c r="AP12">
-        <v>0.46</v>
-      </c>
-      <c r="AQ12">
-        <v>0.4399999999999999</v>
-      </c>
-      <c r="AR12">
-        <v>0.42</v>
-      </c>
-      <c r="AS12">
-        <v>0.4</v>
-      </c>
-      <c r="AT12">
-        <v>0.38</v>
-      </c>
-      <c r="AU12">
-        <v>0.36</v>
-      </c>
-      <c r="AV12">
-        <v>0.34</v>
-      </c>
-      <c r="AW12">
-        <v>0.32</v>
-      </c>
-      <c r="AX12">
-        <v>0.3</v>
-      </c>
-      <c r="AY12">
-        <v>0.28</v>
-      </c>
-      <c r="AZ12">
-        <v>0.26</v>
-      </c>
-      <c r="BA12">
-        <v>0.24</v>
-      </c>
-      <c r="BB12">
-        <v>0.22</v>
-      </c>
-      <c r="BC12">
-        <v>0.2</v>
-      </c>
-      <c r="BD12">
-        <v>0.18</v>
-      </c>
-      <c r="BE12">
-        <v>0.16</v>
-      </c>
-      <c r="BF12">
-        <v>0.14</v>
-      </c>
-      <c r="BG12">
-        <v>0.12</v>
-      </c>
-      <c r="BH12">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="BI12">
-        <v>0.07999999999999996</v>
-      </c>
-      <c r="BJ12">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="BK12">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="BL12">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="BM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:65">
-      <c r="A13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>0.994</v>
-      </c>
-      <c r="Q13">
-        <v>0.988</v>
-      </c>
-      <c r="R13">
-        <v>0.982</v>
-      </c>
-      <c r="S13">
-        <v>0.976</v>
-      </c>
-      <c r="T13">
-        <v>0.97</v>
-      </c>
-      <c r="U13">
-        <v>0.964</v>
-      </c>
-      <c r="V13">
-        <v>0.958</v>
-      </c>
-      <c r="W13">
-        <v>0.952</v>
-      </c>
-      <c r="X13">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y13">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z13">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA13">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB13">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC13">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD13">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE13">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF13">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG13">
-        <v>0.892</v>
-      </c>
-      <c r="AH13">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI13">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ13">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK13">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL13">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM13">
-        <v>0.856</v>
-      </c>
-      <c r="AN13">
-        <v>0.85</v>
-      </c>
-      <c r="AO13">
-        <v>0.844</v>
-      </c>
-      <c r="AP13">
-        <v>0.838</v>
-      </c>
-      <c r="AQ13">
-        <v>0.832</v>
-      </c>
-      <c r="AR13">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS13">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT13">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU13">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV13">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW13">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX13">
-        <v>0.79</v>
-      </c>
-      <c r="AY13">
-        <v>0.784</v>
-      </c>
-      <c r="AZ13">
-        <v>0.778</v>
-      </c>
-      <c r="BA13">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB13">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC13">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD13">
-        <v>0.754</v>
-      </c>
-      <c r="BE13">
-        <v>0.748</v>
-      </c>
-      <c r="BF13">
-        <v>0.742</v>
-      </c>
-      <c r="BG13">
-        <v>0.736</v>
-      </c>
-      <c r="BH13">
-        <v>0.73</v>
-      </c>
-      <c r="BI13">
-        <v>0.724</v>
-      </c>
-      <c r="BJ13">
-        <v>0.718</v>
-      </c>
-      <c r="BK13">
-        <v>0.712</v>
-      </c>
-      <c r="BL13">
-        <v>0.706</v>
-      </c>
-      <c r="BM13">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:65">
-      <c r="A14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" t="s">
-        <v>199</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>0.041455807</v>
-      </c>
-      <c r="K14">
-        <v>0.041455807</v>
-      </c>
-      <c r="L14">
-        <v>0.041455807</v>
-      </c>
-      <c r="M14">
-        <v>0.041455807</v>
-      </c>
-      <c r="N14">
-        <v>0.041455807</v>
-      </c>
-      <c r="O14">
-        <v>0.041455807</v>
-      </c>
-      <c r="P14">
-        <v>0.05762669086</v>
-      </c>
-      <c r="Q14">
-        <v>0.07379757472000001</v>
-      </c>
-      <c r="R14">
-        <v>0.08996845857999999</v>
-      </c>
-      <c r="S14">
-        <v>0.10613934244</v>
-      </c>
-      <c r="T14">
-        <v>0.1223102263</v>
-      </c>
-      <c r="U14">
-        <v>0.13848111016</v>
-      </c>
-      <c r="V14">
-        <v>0.15465199402</v>
-      </c>
-      <c r="W14">
-        <v>0.17082287788</v>
-      </c>
-      <c r="X14">
-        <v>0.18699376174</v>
-      </c>
-      <c r="Y14">
-        <v>0.2031646456</v>
-      </c>
-      <c r="Z14">
-        <v>0.21933552946</v>
-      </c>
-      <c r="AA14">
-        <v>0.23550641332</v>
-      </c>
-      <c r="AB14">
-        <v>0.25167729718</v>
-      </c>
-      <c r="AC14">
-        <v>0.26784818104</v>
-      </c>
-      <c r="AD14">
-        <v>0.2840190649</v>
-      </c>
-      <c r="AE14">
-        <v>0.30018994876</v>
-      </c>
-      <c r="AF14">
-        <v>0.31636083262</v>
-      </c>
-      <c r="AG14">
-        <v>0.33253171648</v>
-      </c>
-      <c r="AH14">
-        <v>0.34870260034</v>
-      </c>
-      <c r="AI14">
-        <v>0.3648734842</v>
-      </c>
-      <c r="AJ14">
-        <v>0.38104436806</v>
-      </c>
-      <c r="AK14">
-        <v>0.39721525192</v>
-      </c>
-      <c r="AL14">
-        <v>0.41338613578</v>
-      </c>
-      <c r="AM14">
-        <v>0.42955701964</v>
-      </c>
-      <c r="AN14">
-        <v>0.4457279035</v>
-      </c>
-      <c r="AO14">
-        <v>0.46189878736</v>
-      </c>
-      <c r="AP14">
-        <v>0.47806967122</v>
-      </c>
-      <c r="AQ14">
-        <v>0.49424055508</v>
-      </c>
-      <c r="AR14">
-        <v>0.51041143894</v>
-      </c>
-      <c r="AS14">
-        <v>0.5265823228000001</v>
-      </c>
-      <c r="AT14">
-        <v>0.54275320666</v>
-      </c>
-      <c r="AU14">
-        <v>0.55892409052</v>
-      </c>
-      <c r="AV14">
-        <v>0.57509497438</v>
-      </c>
-      <c r="AW14">
-        <v>0.5912658582400001</v>
-      </c>
-      <c r="AX14">
-        <v>0.6074367421</v>
-      </c>
-      <c r="AY14">
-        <v>0.62360762596</v>
-      </c>
-      <c r="AZ14">
-        <v>0.63977850982</v>
-      </c>
-      <c r="BA14">
-        <v>0.65594939368</v>
-      </c>
-      <c r="BB14">
-        <v>0.67212027754</v>
-      </c>
-      <c r="BC14">
-        <v>0.6882911614</v>
-      </c>
-      <c r="BD14">
-        <v>0.70446204526</v>
-      </c>
-      <c r="BE14">
-        <v>0.72063292912</v>
-      </c>
-      <c r="BF14">
-        <v>0.73680381298</v>
-      </c>
-      <c r="BG14">
-        <v>0.75297469684</v>
-      </c>
-      <c r="BH14">
-        <v>0.7691455807000001</v>
-      </c>
-      <c r="BI14">
-        <v>0.78531646456</v>
-      </c>
-      <c r="BJ14">
-        <v>0.8014873484199999</v>
-      </c>
-      <c r="BK14">
-        <v>0.8176582322799999</v>
-      </c>
-      <c r="BL14">
-        <v>0.83382911614</v>
-      </c>
-      <c r="BM14">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:65">
-      <c r="A15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" t="s">
-        <v>200</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K15">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L15">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M15">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="N15">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O15">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="P15">
-        <v>0.08560000000000001</v>
-      </c>
-      <c r="Q15">
-        <v>0.1012</v>
-      </c>
-      <c r="R15">
-        <v>0.1168</v>
-      </c>
-      <c r="S15">
-        <v>0.1324</v>
-      </c>
-      <c r="T15">
-        <v>0.148</v>
-      </c>
-      <c r="U15">
-        <v>0.1636</v>
-      </c>
-      <c r="V15">
-        <v>0.1792</v>
-      </c>
-      <c r="W15">
-        <v>0.1948</v>
-      </c>
-      <c r="X15">
-        <v>0.2104</v>
-      </c>
-      <c r="Y15">
-        <v>0.226</v>
-      </c>
-      <c r="Z15">
-        <v>0.2416</v>
-      </c>
-      <c r="AA15">
-        <v>0.2572</v>
-      </c>
-      <c r="AB15">
-        <v>0.2728</v>
-      </c>
-      <c r="AC15">
-        <v>0.2884</v>
-      </c>
-      <c r="AD15">
-        <v>0.304</v>
-      </c>
-      <c r="AE15">
-        <v>0.3196</v>
-      </c>
-      <c r="AF15">
-        <v>0.3352000000000001</v>
-      </c>
-      <c r="AG15">
-        <v>0.3508</v>
-      </c>
-      <c r="AH15">
-        <v>0.3664</v>
-      </c>
-      <c r="AI15">
-        <v>0.382</v>
-      </c>
-      <c r="AJ15">
-        <v>0.3976</v>
-      </c>
-      <c r="AK15">
-        <v>0.4132</v>
-      </c>
-      <c r="AL15">
-        <v>0.4288</v>
-      </c>
-      <c r="AM15">
-        <v>0.4444</v>
-      </c>
-      <c r="AN15">
-        <v>0.46</v>
-      </c>
-      <c r="AO15">
-        <v>0.4756</v>
-      </c>
-      <c r="AP15">
-        <v>0.4912</v>
-      </c>
-      <c r="AQ15">
-        <v>0.5068</v>
-      </c>
-      <c r="AR15">
-        <v>0.5224</v>
-      </c>
-      <c r="AS15">
-        <v>0.538</v>
-      </c>
-      <c r="AT15">
-        <v>0.5536</v>
-      </c>
-      <c r="AU15">
-        <v>0.5692</v>
-      </c>
-      <c r="AV15">
-        <v>0.5848000000000001</v>
-      </c>
-      <c r="AW15">
-        <v>0.6004</v>
-      </c>
-      <c r="AX15">
-        <v>0.616</v>
-      </c>
-      <c r="AY15">
-        <v>0.6315999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>0.6472</v>
-      </c>
-      <c r="BA15">
-        <v>0.6628000000000001</v>
-      </c>
-      <c r="BB15">
-        <v>0.6784</v>
-      </c>
-      <c r="BC15">
-        <v>0.6940000000000001</v>
-      </c>
-      <c r="BD15">
-        <v>0.7096</v>
-      </c>
-      <c r="BE15">
-        <v>0.7252</v>
-      </c>
-      <c r="BF15">
-        <v>0.7408</v>
-      </c>
-      <c r="BG15">
-        <v>0.7564</v>
-      </c>
-      <c r="BH15">
-        <v>0.772</v>
-      </c>
-      <c r="BI15">
-        <v>0.7876000000000001</v>
-      </c>
-      <c r="BJ15">
-        <v>0.8031999999999999</v>
-      </c>
-      <c r="BK15">
-        <v>0.8188</v>
-      </c>
-      <c r="BL15">
-        <v>0.8343999999999999</v>
-      </c>
-      <c r="BM15">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:65">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>0.5</v>
-      </c>
-      <c r="K16">
-        <v>0.5</v>
-      </c>
-      <c r="L16">
-        <v>0.5</v>
-      </c>
-      <c r="M16">
-        <v>0.5</v>
-      </c>
-      <c r="N16">
-        <v>0.5</v>
-      </c>
-      <c r="O16">
-        <v>0.5</v>
-      </c>
-      <c r="P16">
-        <v>0.507</v>
-      </c>
-      <c r="Q16">
-        <v>0.514</v>
-      </c>
-      <c r="R16">
-        <v>0.521</v>
-      </c>
-      <c r="S16">
-        <v>0.528</v>
-      </c>
-      <c r="T16">
-        <v>0.535</v>
-      </c>
-      <c r="U16">
-        <v>0.542</v>
-      </c>
-      <c r="V16">
-        <v>0.549</v>
-      </c>
-      <c r="W16">
-        <v>0.556</v>
-      </c>
-      <c r="X16">
-        <v>0.5630000000000001</v>
-      </c>
-      <c r="Y16">
-        <v>0.5700000000000001</v>
-      </c>
-      <c r="Z16">
-        <v>0.577</v>
-      </c>
-      <c r="AA16">
-        <v>0.584</v>
-      </c>
-      <c r="AB16">
-        <v>0.591</v>
-      </c>
-      <c r="AC16">
-        <v>0.598</v>
-      </c>
-      <c r="AD16">
-        <v>0.605</v>
-      </c>
-      <c r="AE16">
-        <v>0.612</v>
-      </c>
-      <c r="AF16">
-        <v>0.619</v>
-      </c>
-      <c r="AG16">
-        <v>0.626</v>
-      </c>
-      <c r="AH16">
-        <v>0.633</v>
-      </c>
-      <c r="AI16">
-        <v>0.64</v>
-      </c>
-      <c r="AJ16">
-        <v>0.647</v>
-      </c>
-      <c r="AK16">
-        <v>0.654</v>
-      </c>
-      <c r="AL16">
-        <v>0.661</v>
-      </c>
-      <c r="AM16">
-        <v>0.6679999999999999</v>
-      </c>
-      <c r="AN16">
-        <v>0.675</v>
-      </c>
-      <c r="AO16">
-        <v>0.6819999999999999</v>
-      </c>
-      <c r="AP16">
-        <v>0.6890000000000001</v>
-      </c>
-      <c r="AQ16">
-        <v>0.696</v>
-      </c>
-      <c r="AR16">
-        <v>0.703</v>
-      </c>
-      <c r="AS16">
-        <v>0.71</v>
-      </c>
-      <c r="AT16">
-        <v>0.7170000000000001</v>
-      </c>
-      <c r="AU16">
-        <v>0.724</v>
-      </c>
-      <c r="AV16">
-        <v>0.7310000000000001</v>
-      </c>
-      <c r="AW16">
-        <v>0.738</v>
-      </c>
-      <c r="AX16">
-        <v>0.745</v>
-      </c>
-      <c r="AY16">
-        <v>0.752</v>
-      </c>
-      <c r="AZ16">
-        <v>0.759</v>
-      </c>
-      <c r="BA16">
-        <v>0.766</v>
-      </c>
-      <c r="BB16">
-        <v>0.773</v>
-      </c>
-      <c r="BC16">
-        <v>0.78</v>
-      </c>
-      <c r="BD16">
-        <v>0.7869999999999999</v>
-      </c>
-      <c r="BE16">
-        <v>0.794</v>
-      </c>
-      <c r="BF16">
-        <v>0.8009999999999999</v>
-      </c>
-      <c r="BG16">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="BH16">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="BI16">
-        <v>0.8220000000000001</v>
-      </c>
-      <c r="BJ16">
-        <v>0.829</v>
-      </c>
-      <c r="BK16">
-        <v>0.836</v>
-      </c>
-      <c r="BL16">
-        <v>0.843</v>
-      </c>
-      <c r="BM16">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:65">
-      <c r="A17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" t="s">
-        <v>202</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>0.041455807</v>
-      </c>
-      <c r="K17">
-        <v>0.041455807</v>
-      </c>
-      <c r="L17">
-        <v>0.041455807</v>
-      </c>
-      <c r="M17">
-        <v>0.041455807</v>
-      </c>
-      <c r="N17">
-        <v>0.041455807</v>
-      </c>
-      <c r="O17">
-        <v>0.041455807</v>
-      </c>
-      <c r="P17">
-        <v>0.05762669086</v>
-      </c>
-      <c r="Q17">
-        <v>0.07379757472000001</v>
-      </c>
-      <c r="R17">
-        <v>0.08996845857999999</v>
-      </c>
-      <c r="S17">
-        <v>0.10613934244</v>
-      </c>
-      <c r="T17">
-        <v>0.1223102263</v>
-      </c>
-      <c r="U17">
-        <v>0.13848111016</v>
-      </c>
-      <c r="V17">
-        <v>0.15465199402</v>
-      </c>
-      <c r="W17">
-        <v>0.17082287788</v>
-      </c>
-      <c r="X17">
-        <v>0.18699376174</v>
-      </c>
-      <c r="Y17">
-        <v>0.2031646456</v>
-      </c>
-      <c r="Z17">
-        <v>0.21933552946</v>
-      </c>
-      <c r="AA17">
-        <v>0.23550641332</v>
-      </c>
-      <c r="AB17">
-        <v>0.25167729718</v>
-      </c>
-      <c r="AC17">
-        <v>0.26784818104</v>
-      </c>
-      <c r="AD17">
-        <v>0.2840190649</v>
-      </c>
-      <c r="AE17">
-        <v>0.30018994876</v>
-      </c>
-      <c r="AF17">
-        <v>0.31636083262</v>
-      </c>
-      <c r="AG17">
-        <v>0.33253171648</v>
-      </c>
-      <c r="AH17">
-        <v>0.34870260034</v>
-      </c>
-      <c r="AI17">
-        <v>0.3648734842</v>
-      </c>
-      <c r="AJ17">
-        <v>0.38104436806</v>
-      </c>
-      <c r="AK17">
-        <v>0.39721525192</v>
-      </c>
-      <c r="AL17">
-        <v>0.41338613578</v>
-      </c>
-      <c r="AM17">
-        <v>0.42955701964</v>
-      </c>
-      <c r="AN17">
-        <v>0.4457279035</v>
-      </c>
-      <c r="AO17">
-        <v>0.46189878736</v>
-      </c>
-      <c r="AP17">
-        <v>0.47806967122</v>
-      </c>
-      <c r="AQ17">
-        <v>0.49424055508</v>
-      </c>
-      <c r="AR17">
-        <v>0.51041143894</v>
-      </c>
-      <c r="AS17">
-        <v>0.5265823228000001</v>
-      </c>
-      <c r="AT17">
-        <v>0.54275320666</v>
-      </c>
-      <c r="AU17">
-        <v>0.55892409052</v>
-      </c>
-      <c r="AV17">
-        <v>0.57509497438</v>
-      </c>
-      <c r="AW17">
-        <v>0.5912658582400001</v>
-      </c>
-      <c r="AX17">
-        <v>0.6074367421</v>
-      </c>
-      <c r="AY17">
-        <v>0.62360762596</v>
-      </c>
-      <c r="AZ17">
-        <v>0.63977850982</v>
-      </c>
-      <c r="BA17">
-        <v>0.65594939368</v>
-      </c>
-      <c r="BB17">
-        <v>0.67212027754</v>
-      </c>
-      <c r="BC17">
-        <v>0.6882911614</v>
-      </c>
-      <c r="BD17">
-        <v>0.70446204526</v>
-      </c>
-      <c r="BE17">
-        <v>0.72063292912</v>
-      </c>
-      <c r="BF17">
-        <v>0.73680381298</v>
-      </c>
-      <c r="BG17">
-        <v>0.75297469684</v>
-      </c>
-      <c r="BH17">
-        <v>0.7691455807000001</v>
-      </c>
-      <c r="BI17">
-        <v>0.78531646456</v>
-      </c>
-      <c r="BJ17">
-        <v>0.8014873484199999</v>
-      </c>
-      <c r="BK17">
-        <v>0.8176582322799999</v>
-      </c>
-      <c r="BL17">
-        <v>0.83382911614</v>
-      </c>
-      <c r="BM17">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:65">
-      <c r="A18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18">
-        <v>63</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0.01</v>
-      </c>
-      <c r="Q18">
-        <v>0.02</v>
-      </c>
-      <c r="R18">
-        <v>0.03</v>
-      </c>
-      <c r="S18">
-        <v>0.04</v>
-      </c>
-      <c r="T18">
-        <v>0.05</v>
-      </c>
-      <c r="U18">
-        <v>0.06</v>
-      </c>
-      <c r="V18">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W18">
-        <v>0.08</v>
-      </c>
-      <c r="X18">
-        <v>0.09</v>
-      </c>
-      <c r="Y18">
-        <v>0.1</v>
-      </c>
-      <c r="Z18">
-        <v>0.11</v>
-      </c>
-      <c r="AA18">
-        <v>0.12</v>
-      </c>
-      <c r="AB18">
-        <v>0.13</v>
-      </c>
-      <c r="AC18">
-        <v>0.14</v>
-      </c>
-      <c r="AD18">
-        <v>0.15</v>
-      </c>
-      <c r="AE18">
-        <v>0.16</v>
-      </c>
-      <c r="AF18">
-        <v>0.17</v>
-      </c>
-      <c r="AG18">
-        <v>0.18</v>
-      </c>
-      <c r="AH18">
-        <v>0.19</v>
-      </c>
-      <c r="AI18">
-        <v>0.2</v>
-      </c>
-      <c r="AJ18">
-        <v>0.21</v>
-      </c>
-      <c r="AK18">
-        <v>0.22</v>
-      </c>
-      <c r="AL18">
-        <v>0.23</v>
-      </c>
-      <c r="AM18">
-        <v>0.24</v>
-      </c>
-      <c r="AN18">
-        <v>0.25</v>
-      </c>
-      <c r="AO18">
-        <v>0.26</v>
-      </c>
-      <c r="AP18">
-        <v>0.27</v>
-      </c>
-      <c r="AQ18">
-        <v>0.28</v>
-      </c>
-      <c r="AR18">
-        <v>0.29</v>
-      </c>
-      <c r="AS18">
-        <v>0.3</v>
-      </c>
-      <c r="AT18">
-        <v>0.31</v>
-      </c>
-      <c r="AU18">
-        <v>0.32</v>
-      </c>
-      <c r="AV18">
-        <v>0.33</v>
-      </c>
-      <c r="AW18">
-        <v>0.34</v>
-      </c>
-      <c r="AX18">
-        <v>0.35</v>
-      </c>
-      <c r="AY18">
-        <v>0.36</v>
-      </c>
-      <c r="AZ18">
-        <v>0.37</v>
-      </c>
-      <c r="BA18">
-        <v>0.38</v>
-      </c>
-      <c r="BB18">
-        <v>0.39</v>
-      </c>
-      <c r="BC18">
-        <v>0.4</v>
-      </c>
-      <c r="BD18">
-        <v>0.41</v>
-      </c>
-      <c r="BE18">
-        <v>0.42</v>
-      </c>
-      <c r="BF18">
-        <v>0.43</v>
-      </c>
-      <c r="BG18">
-        <v>0.44</v>
-      </c>
-      <c r="BH18">
-        <v>0.45</v>
-      </c>
-      <c r="BI18">
-        <v>0.46</v>
-      </c>
-      <c r="BJ18">
-        <v>0.47</v>
-      </c>
-      <c r="BK18">
-        <v>0.48</v>
-      </c>
-      <c r="BL18">
-        <v>0.49</v>
-      </c>
-      <c r="BM18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:65">
-      <c r="A19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" t="s">
-        <v>205</v>
-      </c>
-      <c r="F19">
-        <v>63</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>0.85598915</v>
-      </c>
-      <c r="K19">
-        <v>0.85598915</v>
-      </c>
-      <c r="L19">
-        <v>0.85598915</v>
-      </c>
-      <c r="M19">
-        <v>0.85598915</v>
-      </c>
-      <c r="N19">
-        <v>0.85598915</v>
-      </c>
-      <c r="O19">
-        <v>0.85598915</v>
-      </c>
-      <c r="P19">
-        <v>0.84598915</v>
-      </c>
-      <c r="Q19">
-        <v>0.83598915</v>
-      </c>
-      <c r="R19">
-        <v>0.8259891499999999</v>
-      </c>
-      <c r="S19">
-        <v>0.8159891499999999</v>
-      </c>
-      <c r="T19">
-        <v>0.80598915</v>
-      </c>
-      <c r="U19">
-        <v>0.7959891499999999</v>
-      </c>
-      <c r="V19">
-        <v>0.7859891499999999</v>
-      </c>
-      <c r="W19">
-        <v>0.77598915</v>
-      </c>
-      <c r="X19">
-        <v>0.76598915</v>
-      </c>
-      <c r="Y19">
-        <v>0.75598915</v>
-      </c>
-      <c r="Z19">
-        <v>0.74598915</v>
-      </c>
-      <c r="AA19">
-        <v>0.73598915</v>
-      </c>
-      <c r="AB19">
-        <v>0.72598915</v>
-      </c>
-      <c r="AC19">
-        <v>0.71598915</v>
-      </c>
-      <c r="AD19">
-        <v>0.70598915</v>
-      </c>
-      <c r="AE19">
-        <v>0.6959891499999999</v>
-      </c>
-      <c r="AF19">
-        <v>0.6859891499999999</v>
-      </c>
-      <c r="AG19">
-        <v>0.6759891499999999</v>
-      </c>
-      <c r="AH19">
-        <v>0.6659891499999999</v>
-      </c>
-      <c r="AI19">
-        <v>0.65598915</v>
-      </c>
-      <c r="AJ19">
-        <v>0.64598915</v>
-      </c>
-      <c r="AK19">
-        <v>0.63598915</v>
-      </c>
-      <c r="AL19">
-        <v>0.6259891500000001</v>
-      </c>
-      <c r="AM19">
-        <v>0.61598915</v>
-      </c>
-      <c r="AN19">
-        <v>0.60598915</v>
-      </c>
-      <c r="AO19">
-        <v>0.59598915</v>
-      </c>
-      <c r="AP19">
-        <v>0.58598915</v>
-      </c>
-      <c r="AQ19">
-        <v>0.5759891499999999</v>
-      </c>
-      <c r="AR19">
-        <v>0.5659891500000001</v>
-      </c>
-      <c r="AS19">
-        <v>0.5559891499999999</v>
-      </c>
-      <c r="AT19">
-        <v>0.54598915</v>
-      </c>
-      <c r="AU19">
-        <v>0.53598915</v>
-      </c>
-      <c r="AV19">
-        <v>0.52598915</v>
-      </c>
-      <c r="AW19">
-        <v>0.51598915</v>
-      </c>
-      <c r="AX19">
-        <v>0.50598915</v>
-      </c>
-      <c r="AY19">
-        <v>0.49598915</v>
-      </c>
-      <c r="AZ19">
-        <v>0.48598915</v>
-      </c>
-      <c r="BA19">
-        <v>0.47598915</v>
-      </c>
-      <c r="BB19">
-        <v>0.46598915</v>
-      </c>
-      <c r="BC19">
-        <v>0.45598915</v>
-      </c>
-      <c r="BD19">
-        <v>0.44598915</v>
-      </c>
-      <c r="BE19">
-        <v>0.43598915</v>
-      </c>
-      <c r="BF19">
-        <v>0.42598915</v>
-      </c>
-      <c r="BG19">
-        <v>0.41598915</v>
-      </c>
-      <c r="BH19">
-        <v>0.40598915</v>
-      </c>
-      <c r="BI19">
-        <v>0.39598915</v>
-      </c>
-      <c r="BJ19">
-        <v>0.38598915</v>
-      </c>
-      <c r="BK19">
-        <v>0.37598915</v>
-      </c>
-      <c r="BL19">
-        <v>0.36598915</v>
-      </c>
-      <c r="BM19">
-        <v>0.35598915</v>
-      </c>
-    </row>
-    <row r="20" spans="1:65">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s">
-        <v>206</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>0.06</v>
-      </c>
-      <c r="K20">
-        <v>0.06</v>
-      </c>
-      <c r="L20">
-        <v>0.06</v>
-      </c>
-      <c r="M20">
-        <v>0.06</v>
-      </c>
-      <c r="N20">
-        <v>0.06</v>
-      </c>
-      <c r="O20">
-        <v>0.06</v>
-      </c>
-      <c r="P20">
-        <v>0.0683</v>
-      </c>
-      <c r="Q20">
-        <v>0.0766</v>
-      </c>
-      <c r="R20">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S20">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T20">
-        <v>0.1015</v>
-      </c>
-      <c r="U20">
-        <v>0.1098</v>
-      </c>
-      <c r="V20">
-        <v>0.1181</v>
-      </c>
-      <c r="W20">
-        <v>0.1264</v>
-      </c>
-      <c r="X20">
-        <v>0.1347</v>
-      </c>
-      <c r="Y20">
-        <v>0.143</v>
-      </c>
-      <c r="Z20">
-        <v>0.1513</v>
-      </c>
-      <c r="AA20">
-        <v>0.1596</v>
-      </c>
-      <c r="AB20">
-        <v>0.1679</v>
-      </c>
-      <c r="AC20">
-        <v>0.1762</v>
-      </c>
-      <c r="AD20">
-        <v>0.1845</v>
-      </c>
-      <c r="AE20">
-        <v>0.1928</v>
-      </c>
-      <c r="AF20">
-        <v>0.2011</v>
-      </c>
-      <c r="AG20">
-        <v>0.2094</v>
-      </c>
-      <c r="AH20">
-        <v>0.2177</v>
-      </c>
-      <c r="AI20">
-        <v>0.226</v>
-      </c>
-      <c r="AJ20">
-        <v>0.2343</v>
-      </c>
-      <c r="AK20">
-        <v>0.2426</v>
-      </c>
-      <c r="AL20">
-        <v>0.2509</v>
-      </c>
-      <c r="AM20">
-        <v>0.2592</v>
-      </c>
-      <c r="AN20">
-        <v>0.2675</v>
-      </c>
-      <c r="AO20">
-        <v>0.2758</v>
-      </c>
-      <c r="AP20">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ20">
-        <v>0.2924</v>
-      </c>
-      <c r="AR20">
-        <v>0.3007</v>
-      </c>
-      <c r="AS20">
-        <v>0.309</v>
-      </c>
-      <c r="AT20">
-        <v>0.3173</v>
-      </c>
-      <c r="AU20">
-        <v>0.3256</v>
-      </c>
-      <c r="AV20">
-        <v>0.3339</v>
-      </c>
-      <c r="AW20">
-        <v>0.3422</v>
-      </c>
-      <c r="AX20">
-        <v>0.3505</v>
-      </c>
-      <c r="AY20">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ20">
-        <v>0.3671</v>
-      </c>
-      <c r="BA20">
-        <v>0.3754</v>
-      </c>
-      <c r="BB20">
-        <v>0.3837</v>
-      </c>
-      <c r="BC20">
-        <v>0.392</v>
-      </c>
-      <c r="BD20">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE20">
-        <v>0.4086</v>
-      </c>
-      <c r="BF20">
-        <v>0.4169</v>
-      </c>
-      <c r="BG20">
-        <v>0.4252</v>
-      </c>
-      <c r="BH20">
-        <v>0.4335</v>
-      </c>
-      <c r="BI20">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ20">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK20">
-        <v>0.4584</v>
-      </c>
-      <c r="BL20">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM20">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="21" spans="1:65">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
-        <v>207</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>0.06</v>
-      </c>
-      <c r="K21">
-        <v>0.06</v>
-      </c>
-      <c r="L21">
-        <v>0.06</v>
-      </c>
-      <c r="M21">
-        <v>0.06</v>
-      </c>
-      <c r="N21">
-        <v>0.06</v>
-      </c>
-      <c r="O21">
-        <v>0.06</v>
-      </c>
-      <c r="P21">
-        <v>0.0683</v>
-      </c>
-      <c r="Q21">
-        <v>0.0766</v>
-      </c>
-      <c r="R21">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S21">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T21">
-        <v>0.1015</v>
-      </c>
-      <c r="U21">
-        <v>0.1098</v>
-      </c>
-      <c r="V21">
-        <v>0.1181</v>
-      </c>
-      <c r="W21">
-        <v>0.1264</v>
-      </c>
-      <c r="X21">
-        <v>0.1347</v>
-      </c>
-      <c r="Y21">
-        <v>0.143</v>
-      </c>
-      <c r="Z21">
-        <v>0.1513</v>
-      </c>
-      <c r="AA21">
-        <v>0.1596</v>
-      </c>
-      <c r="AB21">
-        <v>0.1679</v>
-      </c>
-      <c r="AC21">
-        <v>0.1762</v>
-      </c>
-      <c r="AD21">
-        <v>0.1845</v>
-      </c>
-      <c r="AE21">
-        <v>0.1928</v>
-      </c>
-      <c r="AF21">
-        <v>0.2011</v>
-      </c>
-      <c r="AG21">
-        <v>0.2094</v>
-      </c>
-      <c r="AH21">
-        <v>0.2177</v>
-      </c>
-      <c r="AI21">
-        <v>0.226</v>
-      </c>
-      <c r="AJ21">
-        <v>0.2343</v>
-      </c>
-      <c r="AK21">
-        <v>0.2426</v>
-      </c>
-      <c r="AL21">
-        <v>0.2509</v>
-      </c>
-      <c r="AM21">
-        <v>0.2592</v>
-      </c>
-      <c r="AN21">
-        <v>0.2675</v>
-      </c>
-      <c r="AO21">
-        <v>0.2758</v>
-      </c>
-      <c r="AP21">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ21">
-        <v>0.2924</v>
-      </c>
-      <c r="AR21">
-        <v>0.3007</v>
-      </c>
-      <c r="AS21">
-        <v>0.309</v>
-      </c>
-      <c r="AT21">
-        <v>0.3173</v>
-      </c>
-      <c r="AU21">
-        <v>0.3256</v>
-      </c>
-      <c r="AV21">
-        <v>0.3339</v>
-      </c>
-      <c r="AW21">
-        <v>0.3422</v>
-      </c>
-      <c r="AX21">
-        <v>0.3505</v>
-      </c>
-      <c r="AY21">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ21">
-        <v>0.3671</v>
-      </c>
-      <c r="BA21">
-        <v>0.3754</v>
-      </c>
-      <c r="BB21">
-        <v>0.3837</v>
-      </c>
-      <c r="BC21">
-        <v>0.392</v>
-      </c>
-      <c r="BD21">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE21">
-        <v>0.4086</v>
-      </c>
-      <c r="BF21">
-        <v>0.4169</v>
-      </c>
-      <c r="BG21">
-        <v>0.4252</v>
-      </c>
-      <c r="BH21">
-        <v>0.4335</v>
-      </c>
-      <c r="BI21">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ21">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK21">
-        <v>0.4584</v>
-      </c>
-      <c r="BL21">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM21">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="22" spans="1:65">
-      <c r="A22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" t="s">
-        <v>208</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>0.06</v>
-      </c>
-      <c r="K22">
-        <v>0.06</v>
-      </c>
-      <c r="L22">
-        <v>0.06</v>
-      </c>
-      <c r="M22">
-        <v>0.06</v>
-      </c>
-      <c r="N22">
-        <v>0.06</v>
-      </c>
-      <c r="O22">
-        <v>0.06</v>
-      </c>
-      <c r="P22">
-        <v>0.0683</v>
-      </c>
-      <c r="Q22">
-        <v>0.0766</v>
-      </c>
-      <c r="R22">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S22">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T22">
-        <v>0.1015</v>
-      </c>
-      <c r="U22">
-        <v>0.1098</v>
-      </c>
-      <c r="V22">
-        <v>0.1181</v>
-      </c>
-      <c r="W22">
-        <v>0.1264</v>
-      </c>
-      <c r="X22">
-        <v>0.1347</v>
-      </c>
-      <c r="Y22">
-        <v>0.143</v>
-      </c>
-      <c r="Z22">
-        <v>0.1513</v>
-      </c>
-      <c r="AA22">
-        <v>0.1596</v>
-      </c>
-      <c r="AB22">
-        <v>0.1679</v>
-      </c>
-      <c r="AC22">
-        <v>0.1762</v>
-      </c>
-      <c r="AD22">
-        <v>0.1845</v>
-      </c>
-      <c r="AE22">
-        <v>0.1928</v>
-      </c>
-      <c r="AF22">
-        <v>0.2011</v>
-      </c>
-      <c r="AG22">
-        <v>0.2094</v>
-      </c>
-      <c r="AH22">
-        <v>0.2177</v>
-      </c>
-      <c r="AI22">
-        <v>0.226</v>
-      </c>
-      <c r="AJ22">
-        <v>0.2343</v>
-      </c>
-      <c r="AK22">
-        <v>0.2426</v>
-      </c>
-      <c r="AL22">
-        <v>0.2509</v>
-      </c>
-      <c r="AM22">
-        <v>0.2592</v>
-      </c>
-      <c r="AN22">
-        <v>0.2675</v>
-      </c>
-      <c r="AO22">
-        <v>0.2758</v>
-      </c>
-      <c r="AP22">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ22">
-        <v>0.2924</v>
-      </c>
-      <c r="AR22">
-        <v>0.3007</v>
-      </c>
-      <c r="AS22">
-        <v>0.309</v>
-      </c>
-      <c r="AT22">
-        <v>0.3173</v>
-      </c>
-      <c r="AU22">
-        <v>0.3256</v>
-      </c>
-      <c r="AV22">
-        <v>0.3339</v>
-      </c>
-      <c r="AW22">
-        <v>0.3422</v>
-      </c>
-      <c r="AX22">
-        <v>0.3505</v>
-      </c>
-      <c r="AY22">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ22">
-        <v>0.3671</v>
-      </c>
-      <c r="BA22">
-        <v>0.3754</v>
-      </c>
-      <c r="BB22">
-        <v>0.3837</v>
-      </c>
-      <c r="BC22">
-        <v>0.392</v>
-      </c>
-      <c r="BD22">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE22">
-        <v>0.4086</v>
-      </c>
-      <c r="BF22">
-        <v>0.4169</v>
-      </c>
-      <c r="BG22">
-        <v>0.4252</v>
-      </c>
-      <c r="BH22">
-        <v>0.4335</v>
-      </c>
-      <c r="BI22">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ22">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK22">
-        <v>0.4584</v>
-      </c>
-      <c r="BL22">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM22">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="23" spans="1:65">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>209</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>0.06</v>
-      </c>
-      <c r="K23">
-        <v>0.06</v>
-      </c>
-      <c r="L23">
-        <v>0.06</v>
-      </c>
-      <c r="M23">
-        <v>0.06</v>
-      </c>
-      <c r="N23">
-        <v>0.06</v>
-      </c>
-      <c r="O23">
-        <v>0.06</v>
-      </c>
-      <c r="P23">
-        <v>0.0683</v>
-      </c>
-      <c r="Q23">
-        <v>0.0766</v>
-      </c>
-      <c r="R23">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S23">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T23">
-        <v>0.1015</v>
-      </c>
-      <c r="U23">
-        <v>0.1098</v>
-      </c>
-      <c r="V23">
-        <v>0.1181</v>
-      </c>
-      <c r="W23">
-        <v>0.1264</v>
-      </c>
-      <c r="X23">
-        <v>0.1347</v>
-      </c>
-      <c r="Y23">
-        <v>0.143</v>
-      </c>
-      <c r="Z23">
-        <v>0.1513</v>
-      </c>
-      <c r="AA23">
-        <v>0.1596</v>
-      </c>
-      <c r="AB23">
-        <v>0.1679</v>
-      </c>
-      <c r="AC23">
-        <v>0.1762</v>
-      </c>
-      <c r="AD23">
-        <v>0.1845</v>
-      </c>
-      <c r="AE23">
-        <v>0.1928</v>
-      </c>
-      <c r="AF23">
-        <v>0.2011</v>
-      </c>
-      <c r="AG23">
-        <v>0.2094</v>
-      </c>
-      <c r="AH23">
-        <v>0.2177</v>
-      </c>
-      <c r="AI23">
-        <v>0.226</v>
-      </c>
-      <c r="AJ23">
-        <v>0.2343</v>
-      </c>
-      <c r="AK23">
-        <v>0.2426</v>
-      </c>
-      <c r="AL23">
-        <v>0.2509</v>
-      </c>
-      <c r="AM23">
-        <v>0.2592</v>
-      </c>
-      <c r="AN23">
-        <v>0.2675</v>
-      </c>
-      <c r="AO23">
-        <v>0.2758</v>
-      </c>
-      <c r="AP23">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ23">
-        <v>0.2924</v>
-      </c>
-      <c r="AR23">
-        <v>0.3007</v>
-      </c>
-      <c r="AS23">
-        <v>0.309</v>
-      </c>
-      <c r="AT23">
-        <v>0.3173</v>
-      </c>
-      <c r="AU23">
-        <v>0.3256</v>
-      </c>
-      <c r="AV23">
-        <v>0.3339</v>
-      </c>
-      <c r="AW23">
-        <v>0.3422</v>
-      </c>
-      <c r="AX23">
-        <v>0.3505</v>
-      </c>
-      <c r="AY23">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ23">
-        <v>0.3671</v>
-      </c>
-      <c r="BA23">
-        <v>0.3754</v>
-      </c>
-      <c r="BB23">
-        <v>0.3837</v>
-      </c>
-      <c r="BC23">
-        <v>0.392</v>
-      </c>
-      <c r="BD23">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE23">
-        <v>0.4086</v>
-      </c>
-      <c r="BF23">
-        <v>0.4169</v>
-      </c>
-      <c r="BG23">
-        <v>0.4252</v>
-      </c>
-      <c r="BH23">
-        <v>0.4335</v>
-      </c>
-      <c r="BI23">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ23">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK23">
-        <v>0.4584</v>
-      </c>
-      <c r="BL23">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM23">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="24" spans="1:65">
-      <c r="A24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" t="s">
-        <v>210</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>0.06</v>
-      </c>
-      <c r="K24">
-        <v>0.06</v>
-      </c>
-      <c r="L24">
-        <v>0.06</v>
-      </c>
-      <c r="M24">
-        <v>0.06</v>
-      </c>
-      <c r="N24">
-        <v>0.06</v>
-      </c>
-      <c r="O24">
-        <v>0.06</v>
-      </c>
-      <c r="P24">
-        <v>0.0683</v>
-      </c>
-      <c r="Q24">
-        <v>0.0766</v>
-      </c>
-      <c r="R24">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S24">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T24">
-        <v>0.1015</v>
-      </c>
-      <c r="U24">
-        <v>0.1098</v>
-      </c>
-      <c r="V24">
-        <v>0.1181</v>
-      </c>
-      <c r="W24">
-        <v>0.1264</v>
-      </c>
-      <c r="X24">
-        <v>0.1347</v>
-      </c>
-      <c r="Y24">
-        <v>0.143</v>
-      </c>
-      <c r="Z24">
-        <v>0.1513</v>
-      </c>
-      <c r="AA24">
-        <v>0.1596</v>
-      </c>
-      <c r="AB24">
-        <v>0.1679</v>
-      </c>
-      <c r="AC24">
-        <v>0.1762</v>
-      </c>
-      <c r="AD24">
-        <v>0.1845</v>
-      </c>
-      <c r="AE24">
-        <v>0.1928</v>
-      </c>
-      <c r="AF24">
-        <v>0.2011</v>
-      </c>
-      <c r="AG24">
-        <v>0.2094</v>
-      </c>
-      <c r="AH24">
-        <v>0.2177</v>
-      </c>
-      <c r="AI24">
-        <v>0.226</v>
-      </c>
-      <c r="AJ24">
-        <v>0.2343</v>
-      </c>
-      <c r="AK24">
-        <v>0.2426</v>
-      </c>
-      <c r="AL24">
-        <v>0.2509</v>
-      </c>
-      <c r="AM24">
-        <v>0.2592</v>
-      </c>
-      <c r="AN24">
-        <v>0.2675</v>
-      </c>
-      <c r="AO24">
-        <v>0.2758</v>
-      </c>
-      <c r="AP24">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ24">
-        <v>0.2924</v>
-      </c>
-      <c r="AR24">
-        <v>0.3007</v>
-      </c>
-      <c r="AS24">
-        <v>0.309</v>
-      </c>
-      <c r="AT24">
-        <v>0.3173</v>
-      </c>
-      <c r="AU24">
-        <v>0.3256</v>
-      </c>
-      <c r="AV24">
-        <v>0.3339</v>
-      </c>
-      <c r="AW24">
-        <v>0.3422</v>
-      </c>
-      <c r="AX24">
-        <v>0.3505</v>
-      </c>
-      <c r="AY24">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ24">
-        <v>0.3671</v>
-      </c>
-      <c r="BA24">
-        <v>0.3754</v>
-      </c>
-      <c r="BB24">
-        <v>0.3837</v>
-      </c>
-      <c r="BC24">
-        <v>0.392</v>
-      </c>
-      <c r="BD24">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE24">
-        <v>0.4086</v>
-      </c>
-      <c r="BF24">
-        <v>0.4169</v>
-      </c>
-      <c r="BG24">
-        <v>0.4252</v>
-      </c>
-      <c r="BH24">
-        <v>0.4335</v>
-      </c>
-      <c r="BI24">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ24">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK24">
-        <v>0.4584</v>
-      </c>
-      <c r="BL24">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM24">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="25" spans="1:65">
-      <c r="A25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" t="s">
-        <v>211</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>0.06</v>
-      </c>
-      <c r="K25">
-        <v>0.06</v>
-      </c>
-      <c r="L25">
-        <v>0.06</v>
-      </c>
-      <c r="M25">
-        <v>0.06</v>
-      </c>
-      <c r="N25">
-        <v>0.06</v>
-      </c>
-      <c r="O25">
-        <v>0.06</v>
-      </c>
-      <c r="P25">
-        <v>0.0683</v>
-      </c>
-      <c r="Q25">
-        <v>0.0766</v>
-      </c>
-      <c r="R25">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S25">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T25">
-        <v>0.1015</v>
-      </c>
-      <c r="U25">
-        <v>0.1098</v>
-      </c>
-      <c r="V25">
-        <v>0.1181</v>
-      </c>
-      <c r="W25">
-        <v>0.1264</v>
-      </c>
-      <c r="X25">
-        <v>0.1347</v>
-      </c>
-      <c r="Y25">
-        <v>0.143</v>
-      </c>
-      <c r="Z25">
-        <v>0.1513</v>
-      </c>
-      <c r="AA25">
-        <v>0.1596</v>
-      </c>
-      <c r="AB25">
-        <v>0.1679</v>
-      </c>
-      <c r="AC25">
-        <v>0.1762</v>
-      </c>
-      <c r="AD25">
-        <v>0.1845</v>
-      </c>
-      <c r="AE25">
-        <v>0.1928</v>
-      </c>
-      <c r="AF25">
-        <v>0.2011</v>
-      </c>
-      <c r="AG25">
-        <v>0.2094</v>
-      </c>
-      <c r="AH25">
-        <v>0.2177</v>
-      </c>
-      <c r="AI25">
-        <v>0.226</v>
-      </c>
-      <c r="AJ25">
-        <v>0.2343</v>
-      </c>
-      <c r="AK25">
-        <v>0.2426</v>
-      </c>
-      <c r="AL25">
-        <v>0.2509</v>
-      </c>
-      <c r="AM25">
-        <v>0.2592</v>
-      </c>
-      <c r="AN25">
-        <v>0.2675</v>
-      </c>
-      <c r="AO25">
-        <v>0.2758</v>
-      </c>
-      <c r="AP25">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ25">
-        <v>0.2924</v>
-      </c>
-      <c r="AR25">
-        <v>0.3007</v>
-      </c>
-      <c r="AS25">
-        <v>0.309</v>
-      </c>
-      <c r="AT25">
-        <v>0.3173</v>
-      </c>
-      <c r="AU25">
-        <v>0.3256</v>
-      </c>
-      <c r="AV25">
-        <v>0.3339</v>
-      </c>
-      <c r="AW25">
-        <v>0.3422</v>
-      </c>
-      <c r="AX25">
-        <v>0.3505</v>
-      </c>
-      <c r="AY25">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ25">
-        <v>0.3671</v>
-      </c>
-      <c r="BA25">
-        <v>0.3754</v>
-      </c>
-      <c r="BB25">
-        <v>0.3837</v>
-      </c>
-      <c r="BC25">
-        <v>0.392</v>
-      </c>
-      <c r="BD25">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE25">
-        <v>0.4086</v>
-      </c>
-      <c r="BF25">
-        <v>0.4169</v>
-      </c>
-      <c r="BG25">
-        <v>0.4252</v>
-      </c>
-      <c r="BH25">
-        <v>0.4335</v>
-      </c>
-      <c r="BI25">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ25">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK25">
-        <v>0.4584</v>
-      </c>
-      <c r="BL25">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM25">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="26" spans="1:65">
-      <c r="A26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" t="s">
-        <v>212</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>0.06</v>
-      </c>
-      <c r="K26">
-        <v>0.06</v>
-      </c>
-      <c r="L26">
-        <v>0.06</v>
-      </c>
-      <c r="M26">
-        <v>0.06</v>
-      </c>
-      <c r="N26">
-        <v>0.06</v>
-      </c>
-      <c r="O26">
-        <v>0.06</v>
-      </c>
-      <c r="P26">
-        <v>0.0683</v>
-      </c>
-      <c r="Q26">
-        <v>0.0766</v>
-      </c>
-      <c r="R26">
-        <v>0.08489999999999999</v>
-      </c>
-      <c r="S26">
-        <v>0.09320000000000001</v>
-      </c>
-      <c r="T26">
-        <v>0.1015</v>
-      </c>
-      <c r="U26">
-        <v>0.1098</v>
-      </c>
-      <c r="V26">
-        <v>0.1181</v>
-      </c>
-      <c r="W26">
-        <v>0.1264</v>
-      </c>
-      <c r="X26">
-        <v>0.1347</v>
-      </c>
-      <c r="Y26">
-        <v>0.143</v>
-      </c>
-      <c r="Z26">
-        <v>0.1513</v>
-      </c>
-      <c r="AA26">
-        <v>0.1596</v>
-      </c>
-      <c r="AB26">
-        <v>0.1679</v>
-      </c>
-      <c r="AC26">
-        <v>0.1762</v>
-      </c>
-      <c r="AD26">
-        <v>0.1845</v>
-      </c>
-      <c r="AE26">
-        <v>0.1928</v>
-      </c>
-      <c r="AF26">
-        <v>0.2011</v>
-      </c>
-      <c r="AG26">
-        <v>0.2094</v>
-      </c>
-      <c r="AH26">
-        <v>0.2177</v>
-      </c>
-      <c r="AI26">
-        <v>0.226</v>
-      </c>
-      <c r="AJ26">
-        <v>0.2343</v>
-      </c>
-      <c r="AK26">
-        <v>0.2426</v>
-      </c>
-      <c r="AL26">
-        <v>0.2509</v>
-      </c>
-      <c r="AM26">
-        <v>0.2592</v>
-      </c>
-      <c r="AN26">
-        <v>0.2675</v>
-      </c>
-      <c r="AO26">
-        <v>0.2758</v>
-      </c>
-      <c r="AP26">
-        <v>0.2841</v>
-      </c>
-      <c r="AQ26">
-        <v>0.2924</v>
-      </c>
-      <c r="AR26">
-        <v>0.3007</v>
-      </c>
-      <c r="AS26">
-        <v>0.309</v>
-      </c>
-      <c r="AT26">
-        <v>0.3173</v>
-      </c>
-      <c r="AU26">
-        <v>0.3256</v>
-      </c>
-      <c r="AV26">
-        <v>0.3339</v>
-      </c>
-      <c r="AW26">
-        <v>0.3422</v>
-      </c>
-      <c r="AX26">
-        <v>0.3505</v>
-      </c>
-      <c r="AY26">
-        <v>0.3588</v>
-      </c>
-      <c r="AZ26">
-        <v>0.3671</v>
-      </c>
-      <c r="BA26">
-        <v>0.3754</v>
-      </c>
-      <c r="BB26">
-        <v>0.3837</v>
-      </c>
-      <c r="BC26">
-        <v>0.392</v>
-      </c>
-      <c r="BD26">
-        <v>0.4002999999999999</v>
-      </c>
-      <c r="BE26">
-        <v>0.4086</v>
-      </c>
-      <c r="BF26">
-        <v>0.4169</v>
-      </c>
-      <c r="BG26">
-        <v>0.4252</v>
-      </c>
-      <c r="BH26">
-        <v>0.4335</v>
-      </c>
-      <c r="BI26">
-        <v>0.4418</v>
-      </c>
-      <c r="BJ26">
-        <v>0.4500999999999999</v>
-      </c>
-      <c r="BK26">
-        <v>0.4584</v>
-      </c>
-      <c r="BL26">
-        <v>0.4666999999999999</v>
-      </c>
-      <c r="BM26">
-        <v>0.475</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BM30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -54570,8 +49773,8 @@
       <c r="B2" t="s">
         <v>79</v>
       </c>
-      <c r="F2">
-        <v>58</v>
+      <c r="C2">
+        <v>51</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -54755,8 +49958,8 @@
       <c r="B3" t="s">
         <v>80</v>
       </c>
-      <c r="F3">
-        <v>58</v>
+      <c r="C3">
+        <v>51</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -54940,8 +50143,8 @@
       <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="F4">
-        <v>59</v>
+      <c r="C4">
+        <v>52</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -55125,8 +50328,8 @@
       <c r="B5" t="s">
         <v>83</v>
       </c>
-      <c r="F5">
-        <v>59</v>
+      <c r="C5">
+        <v>52</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -55310,8 +50513,8 @@
       <c r="B6" t="s">
         <v>87</v>
       </c>
-      <c r="F6">
-        <v>59</v>
+      <c r="C6">
+        <v>52</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -55495,8 +50698,8 @@
       <c r="B7" t="s">
         <v>88</v>
       </c>
-      <c r="F7">
-        <v>59</v>
+      <c r="C7">
+        <v>52</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -55680,8 +50883,8 @@
       <c r="B8" t="s">
         <v>90</v>
       </c>
-      <c r="F8">
-        <v>59</v>
+      <c r="C8">
+        <v>52</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -55865,8 +51068,8 @@
       <c r="B9" t="s">
         <v>93</v>
       </c>
-      <c r="F9">
-        <v>60</v>
+      <c r="C9">
+        <v>50</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -56050,8 +51253,8 @@
       <c r="B10" t="s">
         <v>97</v>
       </c>
-      <c r="F10">
-        <v>60</v>
+      <c r="C10">
+        <v>50</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -56235,8 +51438,8 @@
       <c r="B11" t="s">
         <v>98</v>
       </c>
-      <c r="F11">
-        <v>60</v>
+      <c r="C11">
+        <v>50</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -56420,8 +51623,8 @@
       <c r="B12" t="s">
         <v>100</v>
       </c>
-      <c r="F12">
-        <v>60</v>
+      <c r="C12">
+        <v>50</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -56605,6 +51808,9 @@
       <c r="B13" t="s">
         <v>154</v>
       </c>
+      <c r="C13">
+        <v>53</v>
+      </c>
       <c r="H13">
         <v>1</v>
       </c>
@@ -56787,6 +51993,9 @@
       <c r="B14" t="s">
         <v>166</v>
       </c>
+      <c r="C14">
+        <v>54</v>
+      </c>
       <c r="H14">
         <v>1</v>
       </c>
@@ -56969,6 +52178,9 @@
       <c r="B15" t="s">
         <v>167</v>
       </c>
+      <c r="C15">
+        <v>54</v>
+      </c>
       <c r="H15">
         <v>1</v>
       </c>
@@ -57151,6 +52363,9 @@
       <c r="B16" t="s">
         <v>168</v>
       </c>
+      <c r="C16">
+        <v>54</v>
+      </c>
       <c r="H16">
         <v>1</v>
       </c>
@@ -57333,6 +52548,9 @@
       <c r="B17" t="s">
         <v>169</v>
       </c>
+      <c r="C17">
+        <v>54</v>
+      </c>
       <c r="H17">
         <v>1</v>
       </c>
@@ -57515,6 +52733,9 @@
       <c r="B18" t="s">
         <v>171</v>
       </c>
+      <c r="C18">
+        <v>54</v>
+      </c>
       <c r="H18">
         <v>1</v>
       </c>
@@ -57697,6 +52918,9 @@
       <c r="B19" t="s">
         <v>172</v>
       </c>
+      <c r="C19">
+        <v>54</v>
+      </c>
       <c r="H19">
         <v>1</v>
       </c>
@@ -57879,6 +53103,9 @@
       <c r="B20" t="s">
         <v>200</v>
       </c>
+      <c r="C20">
+        <v>55</v>
+      </c>
       <c r="H20">
         <v>1</v>
       </c>
@@ -58061,8 +53288,8 @@
       <c r="B21" t="s">
         <v>204</v>
       </c>
-      <c r="F21">
-        <v>63</v>
+      <c r="C21">
+        <v>58</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -58246,8 +53473,8 @@
       <c r="B22" t="s">
         <v>205</v>
       </c>
-      <c r="F22">
-        <v>63</v>
+      <c r="C22">
+        <v>58</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -58431,6 +53658,9 @@
       <c r="B23" t="s">
         <v>206</v>
       </c>
+      <c r="C23">
+        <v>59</v>
+      </c>
       <c r="H23">
         <v>1</v>
       </c>
@@ -58613,6 +53843,9 @@
       <c r="B24" t="s">
         <v>207</v>
       </c>
+      <c r="C24">
+        <v>59</v>
+      </c>
       <c r="H24">
         <v>1</v>
       </c>
@@ -58795,6 +54028,9 @@
       <c r="B25" t="s">
         <v>208</v>
       </c>
+      <c r="C25">
+        <v>59</v>
+      </c>
       <c r="H25">
         <v>1</v>
       </c>
@@ -58977,6 +54213,9 @@
       <c r="B26" t="s">
         <v>209</v>
       </c>
+      <c r="C26">
+        <v>59</v>
+      </c>
       <c r="H26">
         <v>1</v>
       </c>
@@ -59159,6 +54398,9 @@
       <c r="B27" t="s">
         <v>210</v>
       </c>
+      <c r="C27">
+        <v>59</v>
+      </c>
       <c r="H27">
         <v>1</v>
       </c>
@@ -59341,6 +54583,9 @@
       <c r="B28" t="s">
         <v>211</v>
       </c>
+      <c r="C28">
+        <v>59</v>
+      </c>
       <c r="H28">
         <v>1</v>
       </c>
@@ -59523,6 +54768,9 @@
       <c r="B29" t="s">
         <v>212</v>
       </c>
+      <c r="C29">
+        <v>59</v>
+      </c>
       <c r="H29">
         <v>1</v>
       </c>
@@ -59704,6 +54952,9 @@
       </c>
       <c r="B30" t="s">
         <v>246</v>
+      </c>
+      <c r="C30">
+        <v>49</v>
       </c>
       <c r="H30">
         <v>1</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
@@ -19357,172 +19357,172 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="W100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="X100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Y100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Z100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AA100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AB100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AC100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AD100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AE100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AF100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AG100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AH100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AI100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AJ100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AK100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AL100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AM100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AN100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AO100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AP100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AQ100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AR100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AS100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AT100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AU100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AV100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AW100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AX100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AY100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AZ100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BA100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BB100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BC100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BD100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BE100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BF100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BG100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BH100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BI100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BJ100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BK100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BL100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BM100">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
     </row>
     <row r="101" spans="1:65">
@@ -19542,172 +19542,172 @@
         <v>1</v>
       </c>
       <c r="J101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="W101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="X101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Y101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Z101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AA101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AB101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AC101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AD101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AE101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AF101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AG101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AH101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AI101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AJ101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AK101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AL101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AM101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AN101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AO101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AP101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AQ101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AR101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AS101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AT101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AU101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AV101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AW101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AX101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AY101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AZ101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BA101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BB101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BC101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BD101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BE101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BF101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BG101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BH101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BI101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BJ101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BK101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BL101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BM101">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
     </row>
     <row r="102" spans="1:65">
@@ -19727,172 +19727,172 @@
         <v>1</v>
       </c>
       <c r="J102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="W102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="X102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Y102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Z102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AA102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AB102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AC102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AD102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AE102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AF102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AG102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AH102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AI102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AJ102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AK102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AL102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AM102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AN102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AO102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AP102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AQ102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AR102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AS102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AT102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AU102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AV102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AW102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AX102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AY102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="AZ102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BA102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BB102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BC102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BD102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BE102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BF102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BG102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BH102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BI102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BJ102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BK102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BL102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="BM102">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
     </row>
     <row r="103" spans="1:65">
@@ -19912,172 +19912,172 @@
         <v>1</v>
       </c>
       <c r="J103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="W103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="X103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Y103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Z103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AA103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AB103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AC103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AD103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AE103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AF103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AG103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AH103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AI103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AJ103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AK103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AL103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AM103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AN103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AO103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AP103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AQ103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AR103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AS103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AT103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AU103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AV103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AW103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AX103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AY103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AZ103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BA103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BB103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BC103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BD103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BE103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BF103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BG103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BH103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BI103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BJ103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BK103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BL103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BM103">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
     </row>
     <row r="104" spans="1:65">
@@ -20094,172 +20094,172 @@
         <v>1</v>
       </c>
       <c r="J104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="L104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="M104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AB104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AC104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AH104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AI104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AJ104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AL104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AM104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AN104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AO104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AP104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AQ104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AR104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AS104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AT104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AU104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AV104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AW104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AX104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AY104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="AZ104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BA104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BB104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BC104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BD104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BE104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BF104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BG104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BH104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BI104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BJ104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BK104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BL104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
       <c r="BM104">
-        <v>0.005851456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:65">
@@ -20279,172 +20279,172 @@
         <v>1</v>
       </c>
       <c r="J105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="W105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="X105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Y105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Z105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AA105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AB105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AC105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AD105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AE105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AF105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AG105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AH105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AI105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AJ105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AK105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AL105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AM105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AN105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AO105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AP105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AQ105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AR105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AS105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AT105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AU105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AV105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AW105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AX105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AY105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AZ105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BA105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BB105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BC105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BD105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BE105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BF105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BG105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BH105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BI105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BJ105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BK105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BL105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BM105">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
     </row>
     <row r="106" spans="1:65">
@@ -20464,172 +20464,172 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="W106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="X106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Y106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Z106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AA106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AB106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AC106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AD106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AE106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AF106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AG106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AH106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AI106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AJ106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AK106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AL106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AM106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AN106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AO106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AP106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AQ106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AR106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AS106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AT106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AU106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AV106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AW106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AX106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AY106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="AZ106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BA106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BB106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BC106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BD106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BE106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BF106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BG106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BH106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BI106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BJ106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BK106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BL106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="BM106">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
     </row>
     <row r="107" spans="1:65">
@@ -26118,172 +26118,172 @@
         <v>1</v>
       </c>
       <c r="J137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="K137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="L137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="M137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="N137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="O137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="P137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="Q137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="R137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="S137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="T137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="U137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="V137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="W137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="X137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="Y137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="Z137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AA137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AB137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AC137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AD137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AE137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AF137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AG137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AH137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AI137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AJ137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AK137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AL137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AM137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AN137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AO137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AP137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AQ137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AR137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AS137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AT137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AU137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AV137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AW137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AX137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AY137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="AZ137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BA137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BB137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BC137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BD137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BE137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BF137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BG137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BH137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BI137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BJ137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BK137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BL137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
       <c r="BM137">
-        <v>0.14401085</v>
+        <v>0.001765668679445968</v>
       </c>
     </row>
     <row r="138" spans="1:65">
@@ -26303,172 +26303,172 @@
         <v>1</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="L138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="M138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AH138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AI138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AL138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AM138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AN138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AO138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AP138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AQ138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AR138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AS138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AT138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AU138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AV138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AW138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AX138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AY138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="AZ138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BA138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BB138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BC138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BD138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BE138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BF138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BG138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BH138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BI138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BJ138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BK138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BL138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="BM138">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
     </row>
     <row r="139" spans="1:65">
@@ -26488,172 +26488,172 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="K139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="L139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="M139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="N139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="O139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="P139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="Q139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="R139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="S139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="T139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="U139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="V139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="W139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="X139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="Y139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="Z139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AA139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AB139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AC139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AD139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AE139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AF139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AG139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AH139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AI139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AJ139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AK139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AL139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AM139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AN139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AO139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AP139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AQ139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AR139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AS139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AT139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AU139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AV139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AW139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AX139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AY139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="AZ139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BA139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BB139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BC139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BD139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BE139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BF139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BG139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BH139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BI139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BJ139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BK139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BL139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="BM139">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
     </row>
     <row r="140" spans="1:65">
@@ -28693,172 +28693,172 @@
         <v>1</v>
       </c>
       <c r="J151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="K151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="L151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="M151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="N151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="O151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="P151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="Q151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="R151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="S151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="T151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="U151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="V151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="W151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="X151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="Y151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="Z151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AA151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AB151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AC151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AD151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AE151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AF151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AG151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AH151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AI151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AJ151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AK151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AL151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AM151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AN151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AO151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AP151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AQ151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AR151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AS151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AT151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AU151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AV151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AW151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AX151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AY151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="AZ151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BA151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BB151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BC151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BD151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BE151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BF151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BG151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BH151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BI151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BJ151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BK151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BL151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
       <c r="BM151">
-        <v>0.5</v>
+        <v>0.2547310323529962</v>
       </c>
     </row>
     <row r="152" spans="1:65">
@@ -31787,172 +31787,172 @@
         <v>1</v>
       </c>
       <c r="J168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="K168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="L168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="M168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="N168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="O168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="P168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="Q168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="R168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="S168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="T168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="U168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="V168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="W168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="X168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="Y168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="Z168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AA168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AB168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AC168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AD168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AE168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AF168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AG168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AH168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AI168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AJ168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AK168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AL168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AM168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AN168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AO168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AP168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AQ168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AR168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AS168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AT168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AU168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AV168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AW168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AX168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AY168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="AZ168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BA168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BB168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BC168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BD168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BE168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BF168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BG168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BH168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BI168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BJ168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BK168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BL168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
       <c r="BM168">
-        <v>0.355</v>
+        <v>0.20454</v>
       </c>
     </row>
     <row r="169" spans="1:65">
@@ -45895,169 +45895,169 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="W19">
-        <v>0.03058139534883721</v>
+        <v>0.127507734020138</v>
       </c>
       <c r="X19">
-        <v>0.04116279069767442</v>
+        <v>0.1357813594006109</v>
       </c>
       <c r="Y19">
-        <v>0.05174418604651163</v>
+        <v>0.1440549847810838</v>
       </c>
       <c r="Z19">
-        <v>0.06232558139534884</v>
+        <v>0.1523286101615567</v>
       </c>
       <c r="AA19">
-        <v>0.07290697674418604</v>
+        <v>0.1606022355420296</v>
       </c>
       <c r="AB19">
-        <v>0.08348837209302325</v>
+        <v>0.1688758609225025</v>
       </c>
       <c r="AC19">
-        <v>0.09406976744186046</v>
+        <v>0.1771494863029754</v>
       </c>
       <c r="AD19">
-        <v>0.1046511627906977</v>
+        <v>0.1854231116834483</v>
       </c>
       <c r="AE19">
-        <v>0.1152325581395349</v>
+        <v>0.1936967370639212</v>
       </c>
       <c r="AF19">
-        <v>0.1258139534883721</v>
+        <v>0.2019703624443941</v>
       </c>
       <c r="AG19">
-        <v>0.1363953488372093</v>
+        <v>0.210243987824867</v>
       </c>
       <c r="AH19">
-        <v>0.1469767441860465</v>
+        <v>0.2185176132053399</v>
       </c>
       <c r="AI19">
-        <v>0.1575581395348837</v>
+        <v>0.2267912385858128</v>
       </c>
       <c r="AJ19">
-        <v>0.1681395348837209</v>
+        <v>0.2350648639662857</v>
       </c>
       <c r="AK19">
-        <v>0.1787209302325581</v>
+        <v>0.2433384893467586</v>
       </c>
       <c r="AL19">
-        <v>0.1893023255813953</v>
+        <v>0.2516121147272316</v>
       </c>
       <c r="AM19">
-        <v>0.1998837209302325</v>
+        <v>0.2598857401077044</v>
       </c>
       <c r="AN19">
-        <v>0.2104651162790698</v>
+        <v>0.2681593654881774</v>
       </c>
       <c r="AO19">
-        <v>0.221046511627907</v>
+        <v>0.2764329908686503</v>
       </c>
       <c r="AP19">
-        <v>0.2316279069767442</v>
+        <v>0.2847066162491232</v>
       </c>
       <c r="AQ19">
-        <v>0.2422093023255814</v>
+        <v>0.2929802416295961</v>
       </c>
       <c r="AR19">
-        <v>0.2527906976744186</v>
+        <v>0.301253867010069</v>
       </c>
       <c r="AS19">
-        <v>0.2633720930232558</v>
+        <v>0.3095274923905419</v>
       </c>
       <c r="AT19">
-        <v>0.273953488372093</v>
+        <v>0.3178011177710148</v>
       </c>
       <c r="AU19">
-        <v>0.2845348837209302</v>
+        <v>0.3260747431514877</v>
       </c>
       <c r="AV19">
-        <v>0.2951162790697674</v>
+        <v>0.3343483685319605</v>
       </c>
       <c r="AW19">
-        <v>0.3056976744186047</v>
+        <v>0.3426219939124335</v>
       </c>
       <c r="AX19">
-        <v>0.3162790697674419</v>
+        <v>0.3508956192929064</v>
       </c>
       <c r="AY19">
-        <v>0.326860465116279</v>
+        <v>0.3591692446733793</v>
       </c>
       <c r="AZ19">
-        <v>0.3374418604651163</v>
+        <v>0.3674428700538522</v>
       </c>
       <c r="BA19">
-        <v>0.3480232558139535</v>
+        <v>0.3757164954343251</v>
       </c>
       <c r="BB19">
-        <v>0.3586046511627907</v>
+        <v>0.3839901208147981</v>
       </c>
       <c r="BC19">
-        <v>0.3691860465116279</v>
+        <v>0.3922637461952709</v>
       </c>
       <c r="BD19">
-        <v>0.3797674418604651</v>
+        <v>0.4005373715757438</v>
       </c>
       <c r="BE19">
-        <v>0.3903488372093023</v>
+        <v>0.4088109969562167</v>
       </c>
       <c r="BF19">
-        <v>0.4009302325581396</v>
+        <v>0.4170846223366897</v>
       </c>
       <c r="BG19">
-        <v>0.4115116279069767</v>
+        <v>0.4253582477171626</v>
       </c>
       <c r="BH19">
-        <v>0.4220930232558139</v>
+        <v>0.4336318730976355</v>
       </c>
       <c r="BI19">
-        <v>0.4326744186046511</v>
+        <v>0.4419054984781083</v>
       </c>
       <c r="BJ19">
-        <v>0.4432558139534883</v>
+        <v>0.4501791238585812</v>
       </c>
       <c r="BK19">
-        <v>0.4538372093023256</v>
+        <v>0.4584527492390542</v>
       </c>
       <c r="BL19">
-        <v>0.4644186046511627</v>
+        <v>0.4667263746195271</v>
       </c>
       <c r="BM19">
         <v>0.475</v>
@@ -46080,169 +46080,169 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="W20">
-        <v>0.4017441860465116</v>
+        <v>0.127507734020138</v>
       </c>
       <c r="X20">
-        <v>0.4034883720930233</v>
+        <v>0.1357813594006109</v>
       </c>
       <c r="Y20">
-        <v>0.4052325581395348</v>
+        <v>0.1440549847810838</v>
       </c>
       <c r="Z20">
-        <v>0.4069767441860465</v>
+        <v>0.1523286101615567</v>
       </c>
       <c r="AA20">
-        <v>0.4087209302325582</v>
+        <v>0.1606022355420296</v>
       </c>
       <c r="AB20">
-        <v>0.4104651162790698</v>
+        <v>0.1688758609225025</v>
       </c>
       <c r="AC20">
-        <v>0.4122093023255814</v>
+        <v>0.1771494863029754</v>
       </c>
       <c r="AD20">
-        <v>0.4139534883720931</v>
+        <v>0.1854231116834483</v>
       </c>
       <c r="AE20">
-        <v>0.4156976744186047</v>
+        <v>0.1936967370639212</v>
       </c>
       <c r="AF20">
-        <v>0.4174418604651163</v>
+        <v>0.2019703624443941</v>
       </c>
       <c r="AG20">
-        <v>0.4191860465116279</v>
+        <v>0.210243987824867</v>
       </c>
       <c r="AH20">
-        <v>0.4209302325581395</v>
+        <v>0.2185176132053399</v>
       </c>
       <c r="AI20">
-        <v>0.4226744186046512</v>
+        <v>0.2267912385858128</v>
       </c>
       <c r="AJ20">
-        <v>0.4244186046511628</v>
+        <v>0.2350648639662857</v>
       </c>
       <c r="AK20">
-        <v>0.4261627906976745</v>
+        <v>0.2433384893467586</v>
       </c>
       <c r="AL20">
-        <v>0.4279069767441861</v>
+        <v>0.2516121147272316</v>
       </c>
       <c r="AM20">
-        <v>0.4296511627906976</v>
+        <v>0.2598857401077044</v>
       </c>
       <c r="AN20">
-        <v>0.4313953488372093</v>
+        <v>0.2681593654881774</v>
       </c>
       <c r="AO20">
-        <v>0.4331395348837209</v>
+        <v>0.2764329908686503</v>
       </c>
       <c r="AP20">
-        <v>0.4348837209302325</v>
+        <v>0.2847066162491232</v>
       </c>
       <c r="AQ20">
-        <v>0.4366279069767442</v>
+        <v>0.2929802416295961</v>
       </c>
       <c r="AR20">
-        <v>0.4383720930232558</v>
+        <v>0.301253867010069</v>
       </c>
       <c r="AS20">
-        <v>0.4401162790697675</v>
+        <v>0.3095274923905419</v>
       </c>
       <c r="AT20">
-        <v>0.4418604651162791</v>
+        <v>0.3178011177710148</v>
       </c>
       <c r="AU20">
-        <v>0.4436046511627907</v>
+        <v>0.3260747431514877</v>
       </c>
       <c r="AV20">
-        <v>0.4453488372093023</v>
+        <v>0.3343483685319605</v>
       </c>
       <c r="AW20">
-        <v>0.447093023255814</v>
+        <v>0.3426219939124335</v>
       </c>
       <c r="AX20">
-        <v>0.4488372093023256</v>
+        <v>0.3508956192929064</v>
       </c>
       <c r="AY20">
-        <v>0.4505813953488372</v>
+        <v>0.3591692446733793</v>
       </c>
       <c r="AZ20">
-        <v>0.4523255813953488</v>
+        <v>0.3674428700538522</v>
       </c>
       <c r="BA20">
-        <v>0.4540697674418605</v>
+        <v>0.3757164954343251</v>
       </c>
       <c r="BB20">
-        <v>0.4558139534883721</v>
+        <v>0.3839901208147981</v>
       </c>
       <c r="BC20">
-        <v>0.4575581395348837</v>
+        <v>0.3922637461952709</v>
       </c>
       <c r="BD20">
-        <v>0.4593023255813953</v>
+        <v>0.4005373715757438</v>
       </c>
       <c r="BE20">
-        <v>0.4610465116279069</v>
+        <v>0.4088109969562167</v>
       </c>
       <c r="BF20">
-        <v>0.4627906976744186</v>
+        <v>0.4170846223366897</v>
       </c>
       <c r="BG20">
-        <v>0.4645348837209302</v>
+        <v>0.4253582477171626</v>
       </c>
       <c r="BH20">
-        <v>0.4662790697674418</v>
+        <v>0.4336318730976355</v>
       </c>
       <c r="BI20">
-        <v>0.4680232558139534</v>
+        <v>0.4419054984781083</v>
       </c>
       <c r="BJ20">
-        <v>0.4697674418604651</v>
+        <v>0.4501791238585812</v>
       </c>
       <c r="BK20">
-        <v>0.4715116279069768</v>
+        <v>0.4584527492390542</v>
       </c>
       <c r="BL20">
-        <v>0.4732558139534884</v>
+        <v>0.4667263746195271</v>
       </c>
       <c r="BM20">
         <v>0.475</v>
@@ -46265,169 +46265,169 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="W21">
-        <v>0.03058139534883721</v>
+        <v>0.127507734020138</v>
       </c>
       <c r="X21">
-        <v>0.04116279069767442</v>
+        <v>0.1357813594006109</v>
       </c>
       <c r="Y21">
-        <v>0.05174418604651163</v>
+        <v>0.1440549847810838</v>
       </c>
       <c r="Z21">
-        <v>0.06232558139534884</v>
+        <v>0.1523286101615567</v>
       </c>
       <c r="AA21">
-        <v>0.07290697674418604</v>
+        <v>0.1606022355420296</v>
       </c>
       <c r="AB21">
-        <v>0.08348837209302325</v>
+        <v>0.1688758609225025</v>
       </c>
       <c r="AC21">
-        <v>0.09406976744186046</v>
+        <v>0.1771494863029754</v>
       </c>
       <c r="AD21">
-        <v>0.1046511627906977</v>
+        <v>0.1854231116834483</v>
       </c>
       <c r="AE21">
-        <v>0.1152325581395349</v>
+        <v>0.1936967370639212</v>
       </c>
       <c r="AF21">
-        <v>0.1258139534883721</v>
+        <v>0.2019703624443941</v>
       </c>
       <c r="AG21">
-        <v>0.1363953488372093</v>
+        <v>0.210243987824867</v>
       </c>
       <c r="AH21">
-        <v>0.1469767441860465</v>
+        <v>0.2185176132053399</v>
       </c>
       <c r="AI21">
-        <v>0.1575581395348837</v>
+        <v>0.2267912385858128</v>
       </c>
       <c r="AJ21">
-        <v>0.1681395348837209</v>
+        <v>0.2350648639662857</v>
       </c>
       <c r="AK21">
-        <v>0.1787209302325581</v>
+        <v>0.2433384893467586</v>
       </c>
       <c r="AL21">
-        <v>0.1893023255813953</v>
+        <v>0.2516121147272316</v>
       </c>
       <c r="AM21">
-        <v>0.1998837209302325</v>
+        <v>0.2598857401077044</v>
       </c>
       <c r="AN21">
-        <v>0.2104651162790698</v>
+        <v>0.2681593654881774</v>
       </c>
       <c r="AO21">
-        <v>0.221046511627907</v>
+        <v>0.2764329908686503</v>
       </c>
       <c r="AP21">
-        <v>0.2316279069767442</v>
+        <v>0.2847066162491232</v>
       </c>
       <c r="AQ21">
-        <v>0.2422093023255814</v>
+        <v>0.2929802416295961</v>
       </c>
       <c r="AR21">
-        <v>0.2527906976744186</v>
+        <v>0.301253867010069</v>
       </c>
       <c r="AS21">
-        <v>0.2633720930232558</v>
+        <v>0.3095274923905419</v>
       </c>
       <c r="AT21">
-        <v>0.273953488372093</v>
+        <v>0.3178011177710148</v>
       </c>
       <c r="AU21">
-        <v>0.2845348837209302</v>
+        <v>0.3260747431514877</v>
       </c>
       <c r="AV21">
-        <v>0.2951162790697674</v>
+        <v>0.3343483685319605</v>
       </c>
       <c r="AW21">
-        <v>0.3056976744186047</v>
+        <v>0.3426219939124335</v>
       </c>
       <c r="AX21">
-        <v>0.3162790697674419</v>
+        <v>0.3508956192929064</v>
       </c>
       <c r="AY21">
-        <v>0.326860465116279</v>
+        <v>0.3591692446733793</v>
       </c>
       <c r="AZ21">
-        <v>0.3374418604651163</v>
+        <v>0.3674428700538522</v>
       </c>
       <c r="BA21">
-        <v>0.3480232558139535</v>
+        <v>0.3757164954343251</v>
       </c>
       <c r="BB21">
-        <v>0.3586046511627907</v>
+        <v>0.3839901208147981</v>
       </c>
       <c r="BC21">
-        <v>0.3691860465116279</v>
+        <v>0.3922637461952709</v>
       </c>
       <c r="BD21">
-        <v>0.3797674418604651</v>
+        <v>0.4005373715757438</v>
       </c>
       <c r="BE21">
-        <v>0.3903488372093023</v>
+        <v>0.4088109969562167</v>
       </c>
       <c r="BF21">
-        <v>0.4009302325581396</v>
+        <v>0.4170846223366897</v>
       </c>
       <c r="BG21">
-        <v>0.4115116279069767</v>
+        <v>0.4253582477171626</v>
       </c>
       <c r="BH21">
-        <v>0.4220930232558139</v>
+        <v>0.4336318730976355</v>
       </c>
       <c r="BI21">
-        <v>0.4326744186046511</v>
+        <v>0.4419054984781083</v>
       </c>
       <c r="BJ21">
-        <v>0.4432558139534883</v>
+        <v>0.4501791238585812</v>
       </c>
       <c r="BK21">
-        <v>0.4538372093023256</v>
+        <v>0.4584527492390542</v>
       </c>
       <c r="BL21">
-        <v>0.4644186046511627</v>
+        <v>0.4667263746195271</v>
       </c>
       <c r="BM21">
         <v>0.475</v>
@@ -46450,169 +46450,169 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="W22">
-        <v>0.01676188725581395</v>
+        <v>0.06295407685271286</v>
       </c>
       <c r="X22">
-        <v>0.02767231851162791</v>
+        <v>0.07276469407050541</v>
       </c>
       <c r="Y22">
-        <v>0.03858274976744186</v>
+        <v>0.08257531128829795</v>
       </c>
       <c r="Z22">
-        <v>0.04949318102325581</v>
+        <v>0.09238592850609051</v>
       </c>
       <c r="AA22">
-        <v>0.06040361227906976</v>
+        <v>0.1021965457238831</v>
       </c>
       <c r="AB22">
-        <v>0.07131404353488371</v>
+        <v>0.1120071629416756</v>
       </c>
       <c r="AC22">
-        <v>0.08222447479069768</v>
+        <v>0.1218177801594682</v>
       </c>
       <c r="AD22">
-        <v>0.09313490604651163</v>
+        <v>0.1316283973772607</v>
       </c>
       <c r="AE22">
-        <v>0.1040453373023256</v>
+        <v>0.1414390145950533</v>
       </c>
       <c r="AF22">
-        <v>0.1149557685581395</v>
+        <v>0.1512496318128458</v>
       </c>
       <c r="AG22">
-        <v>0.1258661998139535</v>
+        <v>0.1610602490306384</v>
       </c>
       <c r="AH22">
-        <v>0.1367766310697674</v>
+        <v>0.1708708662484309</v>
       </c>
       <c r="AI22">
-        <v>0.1476870623255814</v>
+        <v>0.1806814834662235</v>
       </c>
       <c r="AJ22">
-        <v>0.1585974935813954</v>
+        <v>0.190492100684016</v>
       </c>
       <c r="AK22">
-        <v>0.1695079248372093</v>
+        <v>0.2003027179018086</v>
       </c>
       <c r="AL22">
-        <v>0.1804183560930233</v>
+        <v>0.2101133351196011</v>
       </c>
       <c r="AM22">
-        <v>0.1913287873488372</v>
+        <v>0.2199239523373936</v>
       </c>
       <c r="AN22">
-        <v>0.2022392186046512</v>
+        <v>0.2297345695551862</v>
       </c>
       <c r="AO22">
-        <v>0.2131496498604651</v>
+        <v>0.2395451867729788</v>
       </c>
       <c r="AP22">
-        <v>0.224060081116279</v>
+        <v>0.2493558039907713</v>
       </c>
       <c r="AQ22">
-        <v>0.234970512372093</v>
+        <v>0.2591664212085639</v>
       </c>
       <c r="AR22">
-        <v>0.245880943627907</v>
+        <v>0.2689770384263564</v>
       </c>
       <c r="AS22">
-        <v>0.2567913748837209</v>
+        <v>0.278787655644149</v>
       </c>
       <c r="AT22">
-        <v>0.2677018061395349</v>
+        <v>0.2885982728619415</v>
       </c>
       <c r="AU22">
-        <v>0.2786122373953488</v>
+        <v>0.2984088900797341</v>
       </c>
       <c r="AV22">
-        <v>0.2895226686511627</v>
+        <v>0.3082195072975266</v>
       </c>
       <c r="AW22">
-        <v>0.3004330999069768</v>
+        <v>0.3180301245153192</v>
       </c>
       <c r="AX22">
-        <v>0.3113435311627907</v>
+        <v>0.3278407417331117</v>
       </c>
       <c r="AY22">
-        <v>0.3222539624186046</v>
+        <v>0.3376513589509043</v>
       </c>
       <c r="AZ22">
-        <v>0.3331643936744186</v>
+        <v>0.3474619761686968</v>
       </c>
       <c r="BA22">
-        <v>0.3440748249302326</v>
+        <v>0.3572725933864894</v>
       </c>
       <c r="BB22">
-        <v>0.3549852561860465</v>
+        <v>0.367083210604282</v>
       </c>
       <c r="BC22">
-        <v>0.3658956874418605</v>
+        <v>0.3768938278220745</v>
       </c>
       <c r="BD22">
-        <v>0.3768061186976744</v>
+        <v>0.386704445039867</v>
       </c>
       <c r="BE22">
-        <v>0.3877165499534883</v>
+        <v>0.3965150622576595</v>
       </c>
       <c r="BF22">
-        <v>0.3986269812093023</v>
+        <v>0.4063256794754522</v>
       </c>
       <c r="BG22">
-        <v>0.4095374124651163</v>
+        <v>0.4161362966932447</v>
       </c>
       <c r="BH22">
-        <v>0.4204478437209302</v>
+        <v>0.4259469139110372</v>
       </c>
       <c r="BI22">
-        <v>0.4313582749767441</v>
+        <v>0.4357575311288298</v>
       </c>
       <c r="BJ22">
-        <v>0.4422687062325581</v>
+        <v>0.4455681483466223</v>
       </c>
       <c r="BK22">
-        <v>0.4531791374883721</v>
+        <v>0.4553787655644149</v>
       </c>
       <c r="BL22">
-        <v>0.464089568744186</v>
+        <v>0.4651893827822074</v>
       </c>
       <c r="BM22">
         <v>0.475</v>
@@ -46635,169 +46635,169 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="W23">
-        <v>0.01676188725581395</v>
+        <v>0.06295407685271286</v>
       </c>
       <c r="X23">
-        <v>0.02767231851162791</v>
+        <v>0.07276469407050541</v>
       </c>
       <c r="Y23">
-        <v>0.03858274976744186</v>
+        <v>0.08257531128829795</v>
       </c>
       <c r="Z23">
-        <v>0.04949318102325581</v>
+        <v>0.09238592850609051</v>
       </c>
       <c r="AA23">
-        <v>0.06040361227906976</v>
+        <v>0.1021965457238831</v>
       </c>
       <c r="AB23">
-        <v>0.07131404353488371</v>
+        <v>0.1120071629416756</v>
       </c>
       <c r="AC23">
-        <v>0.08222447479069768</v>
+        <v>0.1218177801594682</v>
       </c>
       <c r="AD23">
-        <v>0.09313490604651163</v>
+        <v>0.1316283973772607</v>
       </c>
       <c r="AE23">
-        <v>0.1040453373023256</v>
+        <v>0.1414390145950533</v>
       </c>
       <c r="AF23">
-        <v>0.1149557685581395</v>
+        <v>0.1512496318128458</v>
       </c>
       <c r="AG23">
-        <v>0.1258661998139535</v>
+        <v>0.1610602490306384</v>
       </c>
       <c r="AH23">
-        <v>0.1367766310697674</v>
+        <v>0.1708708662484309</v>
       </c>
       <c r="AI23">
-        <v>0.1476870623255814</v>
+        <v>0.1806814834662235</v>
       </c>
       <c r="AJ23">
-        <v>0.1585974935813954</v>
+        <v>0.190492100684016</v>
       </c>
       <c r="AK23">
-        <v>0.1695079248372093</v>
+        <v>0.2003027179018086</v>
       </c>
       <c r="AL23">
-        <v>0.1804183560930233</v>
+        <v>0.2101133351196011</v>
       </c>
       <c r="AM23">
-        <v>0.1913287873488372</v>
+        <v>0.2199239523373936</v>
       </c>
       <c r="AN23">
-        <v>0.2022392186046512</v>
+        <v>0.2297345695551862</v>
       </c>
       <c r="AO23">
-        <v>0.2131496498604651</v>
+        <v>0.2395451867729788</v>
       </c>
       <c r="AP23">
-        <v>0.224060081116279</v>
+        <v>0.2493558039907713</v>
       </c>
       <c r="AQ23">
-        <v>0.234970512372093</v>
+        <v>0.2591664212085639</v>
       </c>
       <c r="AR23">
-        <v>0.245880943627907</v>
+        <v>0.2689770384263564</v>
       </c>
       <c r="AS23">
-        <v>0.2567913748837209</v>
+        <v>0.278787655644149</v>
       </c>
       <c r="AT23">
-        <v>0.2677018061395349</v>
+        <v>0.2885982728619415</v>
       </c>
       <c r="AU23">
-        <v>0.2786122373953488</v>
+        <v>0.2984088900797341</v>
       </c>
       <c r="AV23">
-        <v>0.2895226686511627</v>
+        <v>0.3082195072975266</v>
       </c>
       <c r="AW23">
-        <v>0.3004330999069768</v>
+        <v>0.3180301245153192</v>
       </c>
       <c r="AX23">
-        <v>0.3113435311627907</v>
+        <v>0.3278407417331117</v>
       </c>
       <c r="AY23">
-        <v>0.3222539624186046</v>
+        <v>0.3376513589509043</v>
       </c>
       <c r="AZ23">
-        <v>0.3331643936744186</v>
+        <v>0.3474619761686968</v>
       </c>
       <c r="BA23">
-        <v>0.3440748249302326</v>
+        <v>0.3572725933864894</v>
       </c>
       <c r="BB23">
-        <v>0.3549852561860465</v>
+        <v>0.367083210604282</v>
       </c>
       <c r="BC23">
-        <v>0.3658956874418605</v>
+        <v>0.3768938278220745</v>
       </c>
       <c r="BD23">
-        <v>0.3768061186976744</v>
+        <v>0.386704445039867</v>
       </c>
       <c r="BE23">
-        <v>0.3877165499534883</v>
+        <v>0.3965150622576595</v>
       </c>
       <c r="BF23">
-        <v>0.3986269812093023</v>
+        <v>0.4063256794754522</v>
       </c>
       <c r="BG23">
-        <v>0.4095374124651163</v>
+        <v>0.4161362966932447</v>
       </c>
       <c r="BH23">
-        <v>0.4204478437209302</v>
+        <v>0.4259469139110372</v>
       </c>
       <c r="BI23">
-        <v>0.4313582749767441</v>
+        <v>0.4357575311288298</v>
       </c>
       <c r="BJ23">
-        <v>0.4422687062325581</v>
+        <v>0.4455681483466223</v>
       </c>
       <c r="BK23">
-        <v>0.4531791374883721</v>
+        <v>0.4553787655644149</v>
       </c>
       <c r="BL23">
-        <v>0.464089568744186</v>
+        <v>0.4651893827822074</v>
       </c>
       <c r="BM23">
         <v>0.475</v>
@@ -46820,169 +46820,169 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="W24">
-        <v>0.01676188725581395</v>
+        <v>0.06295407685271286</v>
       </c>
       <c r="X24">
-        <v>0.02767231851162791</v>
+        <v>0.07276469407050541</v>
       </c>
       <c r="Y24">
-        <v>0.03858274976744186</v>
+        <v>0.08257531128829795</v>
       </c>
       <c r="Z24">
-        <v>0.04949318102325581</v>
+        <v>0.09238592850609051</v>
       </c>
       <c r="AA24">
-        <v>0.06040361227906976</v>
+        <v>0.1021965457238831</v>
       </c>
       <c r="AB24">
-        <v>0.07131404353488371</v>
+        <v>0.1120071629416756</v>
       </c>
       <c r="AC24">
-        <v>0.08222447479069768</v>
+        <v>0.1218177801594682</v>
       </c>
       <c r="AD24">
-        <v>0.09313490604651163</v>
+        <v>0.1316283973772607</v>
       </c>
       <c r="AE24">
-        <v>0.1040453373023256</v>
+        <v>0.1414390145950533</v>
       </c>
       <c r="AF24">
-        <v>0.1149557685581395</v>
+        <v>0.1512496318128458</v>
       </c>
       <c r="AG24">
-        <v>0.1258661998139535</v>
+        <v>0.1610602490306384</v>
       </c>
       <c r="AH24">
-        <v>0.1367766310697674</v>
+        <v>0.1708708662484309</v>
       </c>
       <c r="AI24">
-        <v>0.1476870623255814</v>
+        <v>0.1806814834662235</v>
       </c>
       <c r="AJ24">
-        <v>0.1585974935813954</v>
+        <v>0.190492100684016</v>
       </c>
       <c r="AK24">
-        <v>0.1695079248372093</v>
+        <v>0.2003027179018086</v>
       </c>
       <c r="AL24">
-        <v>0.1804183560930233</v>
+        <v>0.2101133351196011</v>
       </c>
       <c r="AM24">
-        <v>0.1913287873488372</v>
+        <v>0.2199239523373936</v>
       </c>
       <c r="AN24">
-        <v>0.2022392186046512</v>
+        <v>0.2297345695551862</v>
       </c>
       <c r="AO24">
-        <v>0.2131496498604651</v>
+        <v>0.2395451867729788</v>
       </c>
       <c r="AP24">
-        <v>0.224060081116279</v>
+        <v>0.2493558039907713</v>
       </c>
       <c r="AQ24">
-        <v>0.234970512372093</v>
+        <v>0.2591664212085639</v>
       </c>
       <c r="AR24">
-        <v>0.245880943627907</v>
+        <v>0.2689770384263564</v>
       </c>
       <c r="AS24">
-        <v>0.2567913748837209</v>
+        <v>0.278787655644149</v>
       </c>
       <c r="AT24">
-        <v>0.2677018061395349</v>
+        <v>0.2885982728619415</v>
       </c>
       <c r="AU24">
-        <v>0.2786122373953488</v>
+        <v>0.2984088900797341</v>
       </c>
       <c r="AV24">
-        <v>0.2895226686511627</v>
+        <v>0.3082195072975266</v>
       </c>
       <c r="AW24">
-        <v>0.3004330999069768</v>
+        <v>0.3180301245153192</v>
       </c>
       <c r="AX24">
-        <v>0.3113435311627907</v>
+        <v>0.3278407417331117</v>
       </c>
       <c r="AY24">
-        <v>0.3222539624186046</v>
+        <v>0.3376513589509043</v>
       </c>
       <c r="AZ24">
-        <v>0.3331643936744186</v>
+        <v>0.3474619761686968</v>
       </c>
       <c r="BA24">
-        <v>0.3440748249302326</v>
+        <v>0.3572725933864894</v>
       </c>
       <c r="BB24">
-        <v>0.3549852561860465</v>
+        <v>0.367083210604282</v>
       </c>
       <c r="BC24">
-        <v>0.3658956874418605</v>
+        <v>0.3768938278220745</v>
       </c>
       <c r="BD24">
-        <v>0.3768061186976744</v>
+        <v>0.386704445039867</v>
       </c>
       <c r="BE24">
-        <v>0.3877165499534883</v>
+        <v>0.3965150622576595</v>
       </c>
       <c r="BF24">
-        <v>0.3986269812093023</v>
+        <v>0.4063256794754522</v>
       </c>
       <c r="BG24">
-        <v>0.4095374124651163</v>
+        <v>0.4161362966932447</v>
       </c>
       <c r="BH24">
-        <v>0.4204478437209302</v>
+        <v>0.4259469139110372</v>
       </c>
       <c r="BI24">
-        <v>0.4313582749767441</v>
+        <v>0.4357575311288298</v>
       </c>
       <c r="BJ24">
-        <v>0.4422687062325581</v>
+        <v>0.4455681483466223</v>
       </c>
       <c r="BK24">
-        <v>0.4531791374883721</v>
+        <v>0.4553787655644149</v>
       </c>
       <c r="BL24">
-        <v>0.464089568744186</v>
+        <v>0.4651893827822074</v>
       </c>
       <c r="BM24">
         <v>0.475</v>
@@ -47745,172 +47745,172 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="W29">
-        <v>0.01990672441860465</v>
+        <v>0.3487997850716117</v>
       </c>
       <c r="X29">
-        <v>0.0398134488372093</v>
+        <v>0.3642625123632532</v>
       </c>
       <c r="Y29">
-        <v>0.05972017325581395</v>
+        <v>0.3797252396548947</v>
       </c>
       <c r="Z29">
-        <v>0.07962689767441861</v>
+        <v>0.3951879669465362</v>
       </c>
       <c r="AA29">
-        <v>0.09953362209302326</v>
+        <v>0.4106506942381777</v>
       </c>
       <c r="AB29">
-        <v>0.1194403465116279</v>
+        <v>0.4261134215298191</v>
       </c>
       <c r="AC29">
-        <v>0.1393470709302326</v>
+        <v>0.4415761488214607</v>
       </c>
       <c r="AD29">
-        <v>0.1592537953488372</v>
+        <v>0.4570388761131021</v>
       </c>
       <c r="AE29">
-        <v>0.1791605197674419</v>
+        <v>0.4725016034047436</v>
       </c>
       <c r="AF29">
-        <v>0.1990672441860465</v>
+        <v>0.4879643306963851</v>
       </c>
       <c r="AG29">
-        <v>0.2189739686046512</v>
+        <v>0.5034270579880266</v>
       </c>
       <c r="AH29">
-        <v>0.2388806930232558</v>
+        <v>0.518889785279668</v>
       </c>
       <c r="AI29">
-        <v>0.2587874174418605</v>
+        <v>0.5343525125713096</v>
       </c>
       <c r="AJ29">
-        <v>0.2786941418604651</v>
+        <v>0.549815239862951</v>
       </c>
       <c r="AK29">
-        <v>0.2986008662790698</v>
+        <v>0.5652779671545926</v>
       </c>
       <c r="AL29">
-        <v>0.3185075906976744</v>
+        <v>0.580740694446234</v>
       </c>
       <c r="AM29">
-        <v>0.3384143151162791</v>
+        <v>0.5962034217378754</v>
       </c>
       <c r="AN29">
-        <v>0.3583210395348838</v>
+        <v>0.611666149029517</v>
       </c>
       <c r="AO29">
-        <v>0.3782277639534884</v>
+        <v>0.6271288763211584</v>
       </c>
       <c r="AP29">
-        <v>0.398134488372093</v>
+        <v>0.6425916036127999</v>
       </c>
       <c r="AQ29">
-        <v>0.4180412127906977</v>
+        <v>0.6580543309044414</v>
       </c>
       <c r="AR29">
-        <v>0.4379479372093023</v>
+        <v>0.6735170581960829</v>
       </c>
       <c r="AS29">
-        <v>0.4578546616279069</v>
+        <v>0.6889797854877243</v>
       </c>
       <c r="AT29">
-        <v>0.4777613860465116</v>
+        <v>0.7044425127793659</v>
       </c>
       <c r="AU29">
-        <v>0.4976681104651163</v>
+        <v>0.7199052400710074</v>
       </c>
       <c r="AV29">
-        <v>0.5175748348837209</v>
+        <v>0.7353679673626489</v>
       </c>
       <c r="AW29">
-        <v>0.5374815593023256</v>
+        <v>0.7508306946542903</v>
       </c>
       <c r="AX29">
-        <v>0.5573882837209303</v>
+        <v>0.7662934219459319</v>
       </c>
       <c r="AY29">
-        <v>0.5772950081395348</v>
+        <v>0.7817561492375733</v>
       </c>
       <c r="AZ29">
-        <v>0.5972017325581396</v>
+        <v>0.7972188765292149</v>
       </c>
       <c r="BA29">
-        <v>0.6171084569767441</v>
+        <v>0.8126816038208563</v>
       </c>
       <c r="BB29">
-        <v>0.6370151813953489</v>
+        <v>0.8281443311124977</v>
       </c>
       <c r="BC29">
-        <v>0.6569219058139535</v>
+        <v>0.8436070584041392</v>
       </c>
       <c r="BD29">
-        <v>0.6768286302325581</v>
+        <v>0.8590697856957806</v>
       </c>
       <c r="BE29">
-        <v>0.6967353546511628</v>
+        <v>0.8745325129874222</v>
       </c>
       <c r="BF29">
-        <v>0.7166420790697675</v>
+        <v>0.8899952402790636</v>
       </c>
       <c r="BG29">
-        <v>0.736548803488372</v>
+        <v>0.9054579675707051</v>
       </c>
       <c r="BH29">
-        <v>0.7564555279069768</v>
+        <v>0.9209206948623466</v>
       </c>
       <c r="BI29">
-        <v>0.7763622523255813</v>
+        <v>0.9363834221539881</v>
       </c>
       <c r="BJ29">
-        <v>0.7962689767441861</v>
+        <v>0.9518461494456296</v>
       </c>
       <c r="BK29">
-        <v>0.8161757011627907</v>
+        <v>0.9673088767372711</v>
       </c>
       <c r="BL29">
-        <v>0.8360824255813953</v>
+        <v>0.9827716040289125</v>
       </c>
       <c r="BM29">
-        <v>0.85598915</v>
+        <v>0.9982343313205541</v>
       </c>
     </row>
     <row r="30" spans="1:65">
@@ -47930,169 +47930,169 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="K30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="L30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="M30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="N30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="O30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="P30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="Q30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="R30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="S30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="T30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="U30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="V30">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="W30">
-        <v>0.8360824255813953</v>
+        <v>0.6494345462489423</v>
       </c>
       <c r="X30">
-        <v>0.8161757011627907</v>
+        <v>0.6339718189573008</v>
       </c>
       <c r="Y30">
-        <v>0.7962689767441861</v>
+        <v>0.6185090916656594</v>
       </c>
       <c r="Z30">
-        <v>0.7763622523255814</v>
+        <v>0.6030463643740179</v>
       </c>
       <c r="AA30">
-        <v>0.7564555279069768</v>
+        <v>0.5875836370823764</v>
       </c>
       <c r="AB30">
-        <v>0.736548803488372</v>
+        <v>0.5721209097907349</v>
       </c>
       <c r="AC30">
-        <v>0.7166420790697674</v>
+        <v>0.5566581824990934</v>
       </c>
       <c r="AD30">
-        <v>0.6967353546511628</v>
+        <v>0.5411954552074519</v>
       </c>
       <c r="AE30">
-        <v>0.6768286302325581</v>
+        <v>0.5257327279158104</v>
       </c>
       <c r="AF30">
-        <v>0.6569219058139535</v>
+        <v>0.5102700006241689</v>
       </c>
       <c r="AG30">
-        <v>0.6370151813953489</v>
+        <v>0.4948072733325275</v>
       </c>
       <c r="AH30">
-        <v>0.6171084569767441</v>
+        <v>0.4793445460408859</v>
       </c>
       <c r="AI30">
-        <v>0.5972017325581396</v>
+        <v>0.4638818187492446</v>
       </c>
       <c r="AJ30">
-        <v>0.5772950081395348</v>
+        <v>0.448419091457603</v>
       </c>
       <c r="AK30">
-        <v>0.5573882837209303</v>
+        <v>0.4329563641659616</v>
       </c>
       <c r="AL30">
-        <v>0.5374815593023256</v>
+        <v>0.4174936368743201</v>
       </c>
       <c r="AM30">
-        <v>0.5175748348837209</v>
+        <v>0.4020309095826786</v>
       </c>
       <c r="AN30">
-        <v>0.4976681104651162</v>
+        <v>0.3865681822910371</v>
       </c>
       <c r="AO30">
-        <v>0.4777613860465116</v>
+        <v>0.3711054549993956</v>
       </c>
       <c r="AP30">
-        <v>0.457854661627907</v>
+        <v>0.3556427277077542</v>
       </c>
       <c r="AQ30">
-        <v>0.4379479372093023</v>
+        <v>0.3401800004161127</v>
       </c>
       <c r="AR30">
-        <v>0.4180412127906977</v>
+        <v>0.3247172731244711</v>
       </c>
       <c r="AS30">
-        <v>0.398134488372093</v>
+        <v>0.3092545458328297</v>
       </c>
       <c r="AT30">
-        <v>0.3782277639534884</v>
+        <v>0.2937918185411882</v>
       </c>
       <c r="AU30">
-        <v>0.3583210395348837</v>
+        <v>0.2783290912495467</v>
       </c>
       <c r="AV30">
-        <v>0.3384143151162791</v>
+        <v>0.2628663639579052</v>
       </c>
       <c r="AW30">
-        <v>0.3185075906976744</v>
+        <v>0.2474036366662637</v>
       </c>
       <c r="AX30">
-        <v>0.2986008662790697</v>
+        <v>0.2319409093746222</v>
       </c>
       <c r="AY30">
-        <v>0.2786941418604651</v>
+        <v>0.2164781820829808</v>
       </c>
       <c r="AZ30">
-        <v>0.2587874174418605</v>
+        <v>0.2010154547913393</v>
       </c>
       <c r="BA30">
-        <v>0.2388806930232558</v>
+        <v>0.1855527274996978</v>
       </c>
       <c r="BB30">
-        <v>0.2189739686046512</v>
+        <v>0.1700900002080563</v>
       </c>
       <c r="BC30">
-        <v>0.1990672441860465</v>
+        <v>0.1546272729164148</v>
       </c>
       <c r="BD30">
-        <v>0.1791605197674419</v>
+        <v>0.1391645456247734</v>
       </c>
       <c r="BE30">
-        <v>0.1592537953488372</v>
+        <v>0.1237018183331319</v>
       </c>
       <c r="BF30">
-        <v>0.1393470709302325</v>
+        <v>0.1082390910414904</v>
       </c>
       <c r="BG30">
-        <v>0.1194403465116279</v>
+        <v>0.09277636374984892</v>
       </c>
       <c r="BH30">
-        <v>0.09953362209302324</v>
+        <v>0.07731363645820741</v>
       </c>
       <c r="BI30">
-        <v>0.07962689767441865</v>
+        <v>0.06185090916656597</v>
       </c>
       <c r="BJ30">
-        <v>0.05972017325581396</v>
+        <v>0.04638818187492446</v>
       </c>
       <c r="BK30">
-        <v>0.03981344883720928</v>
+        <v>0.03092545458328295</v>
       </c>
       <c r="BL30">
-        <v>0.01990672441860469</v>
+        <v>0.01546272729164151</v>
       </c>
       <c r="BM30">
         <v>0</v>
@@ -53869,169 +53869,169 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P19">
-        <v>0.0291</v>
+        <v>0.1263494264668718</v>
       </c>
       <c r="Q19">
-        <v>0.0382</v>
+        <v>0.1334647442940785</v>
       </c>
       <c r="R19">
-        <v>0.04729999999999999</v>
+        <v>0.1405800621212852</v>
       </c>
       <c r="S19">
-        <v>0.0564</v>
+        <v>0.1476953799484919</v>
       </c>
       <c r="T19">
-        <v>0.0655</v>
+        <v>0.1548106977756986</v>
       </c>
       <c r="U19">
-        <v>0.0746</v>
+        <v>0.1619260156029053</v>
       </c>
       <c r="V19">
-        <v>0.0837</v>
+        <v>0.169041333430112</v>
       </c>
       <c r="W19">
-        <v>0.09279999999999999</v>
+        <v>0.1761566512573187</v>
       </c>
       <c r="X19">
-        <v>0.1019</v>
+        <v>0.1832719690845254</v>
       </c>
       <c r="Y19">
-        <v>0.111</v>
+        <v>0.1903872869117321</v>
       </c>
       <c r="Z19">
-        <v>0.1201</v>
+        <v>0.1975026047389387</v>
       </c>
       <c r="AA19">
-        <v>0.1292</v>
+        <v>0.2046179225661454</v>
       </c>
       <c r="AB19">
-        <v>0.1383</v>
+        <v>0.2117332403933521</v>
       </c>
       <c r="AC19">
-        <v>0.1474</v>
+        <v>0.2188485582205588</v>
       </c>
       <c r="AD19">
-        <v>0.1565</v>
+        <v>0.2259638760477655</v>
       </c>
       <c r="AE19">
-        <v>0.1656</v>
+        <v>0.2330791938749722</v>
       </c>
       <c r="AF19">
-        <v>0.1747</v>
+        <v>0.2401945117021789</v>
       </c>
       <c r="AG19">
-        <v>0.1838</v>
+        <v>0.2473098295293856</v>
       </c>
       <c r="AH19">
-        <v>0.1929</v>
+        <v>0.2544251473565923</v>
       </c>
       <c r="AI19">
-        <v>0.202</v>
+        <v>0.261540465183799</v>
       </c>
       <c r="AJ19">
-        <v>0.2111</v>
+        <v>0.2686557830110057</v>
       </c>
       <c r="AK19">
-        <v>0.2202</v>
+        <v>0.2757711008382124</v>
       </c>
       <c r="AL19">
-        <v>0.2293</v>
+        <v>0.2828864186654191</v>
       </c>
       <c r="AM19">
-        <v>0.2384</v>
+        <v>0.2900017364926258</v>
       </c>
       <c r="AN19">
-        <v>0.2475</v>
+        <v>0.2971170543198325</v>
       </c>
       <c r="AO19">
-        <v>0.2566</v>
+        <v>0.3042323721470392</v>
       </c>
       <c r="AP19">
-        <v>0.2657</v>
+        <v>0.3113476899742459</v>
       </c>
       <c r="AQ19">
-        <v>0.2748</v>
+        <v>0.3184630078014526</v>
       </c>
       <c r="AR19">
-        <v>0.2839</v>
+        <v>0.3255783256286593</v>
       </c>
       <c r="AS19">
-        <v>0.293</v>
+        <v>0.332693643455866</v>
       </c>
       <c r="AT19">
-        <v>0.3021</v>
+        <v>0.3398089612830727</v>
       </c>
       <c r="AU19">
-        <v>0.3112</v>
+        <v>0.3469242791102794</v>
       </c>
       <c r="AV19">
-        <v>0.3203</v>
+        <v>0.3540395969374861</v>
       </c>
       <c r="AW19">
-        <v>0.3294</v>
+        <v>0.3611549147646928</v>
       </c>
       <c r="AX19">
-        <v>0.3385</v>
+        <v>0.3682702325918995</v>
       </c>
       <c r="AY19">
-        <v>0.3476</v>
+        <v>0.3753855504191062</v>
       </c>
       <c r="AZ19">
-        <v>0.3567</v>
+        <v>0.3825008682463129</v>
       </c>
       <c r="BA19">
-        <v>0.3658</v>
+        <v>0.3896161860735196</v>
       </c>
       <c r="BB19">
-        <v>0.3749</v>
+        <v>0.3967315039007263</v>
       </c>
       <c r="BC19">
-        <v>0.384</v>
+        <v>0.403846821727933</v>
       </c>
       <c r="BD19">
-        <v>0.3930999999999999</v>
+        <v>0.4109621395551397</v>
       </c>
       <c r="BE19">
-        <v>0.4021999999999999</v>
+        <v>0.4180774573823464</v>
       </c>
       <c r="BF19">
-        <v>0.4113</v>
+        <v>0.4251927752095531</v>
       </c>
       <c r="BG19">
-        <v>0.4204</v>
+        <v>0.4323080930367598</v>
       </c>
       <c r="BH19">
-        <v>0.4295</v>
+        <v>0.4394234108639665</v>
       </c>
       <c r="BI19">
-        <v>0.4386</v>
+        <v>0.4465387286911732</v>
       </c>
       <c r="BJ19">
-        <v>0.4476999999999999</v>
+        <v>0.4536540465183799</v>
       </c>
       <c r="BK19">
-        <v>0.4568</v>
+        <v>0.4607693643455866</v>
       </c>
       <c r="BL19">
-        <v>0.4659</v>
+        <v>0.4678846821727933</v>
       </c>
       <c r="BM19">
         <v>0.475</v>
@@ -54054,169 +54054,169 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P20">
-        <v>0.4015</v>
+        <v>0.1263494264668718</v>
       </c>
       <c r="Q20">
-        <v>0.403</v>
+        <v>0.1334647442940785</v>
       </c>
       <c r="R20">
-        <v>0.4045</v>
+        <v>0.1405800621212852</v>
       </c>
       <c r="S20">
-        <v>0.406</v>
+        <v>0.1476953799484919</v>
       </c>
       <c r="T20">
-        <v>0.4075</v>
+        <v>0.1548106977756986</v>
       </c>
       <c r="U20">
-        <v>0.409</v>
+        <v>0.1619260156029053</v>
       </c>
       <c r="V20">
-        <v>0.4105</v>
+        <v>0.169041333430112</v>
       </c>
       <c r="W20">
-        <v>0.412</v>
+        <v>0.1761566512573187</v>
       </c>
       <c r="X20">
-        <v>0.4135000000000001</v>
+        <v>0.1832719690845254</v>
       </c>
       <c r="Y20">
-        <v>0.415</v>
+        <v>0.1903872869117321</v>
       </c>
       <c r="Z20">
-        <v>0.4165</v>
+        <v>0.1975026047389387</v>
       </c>
       <c r="AA20">
-        <v>0.418</v>
+        <v>0.2046179225661454</v>
       </c>
       <c r="AB20">
-        <v>0.4195</v>
+        <v>0.2117332403933521</v>
       </c>
       <c r="AC20">
-        <v>0.421</v>
+        <v>0.2188485582205588</v>
       </c>
       <c r="AD20">
-        <v>0.4225</v>
+        <v>0.2259638760477655</v>
       </c>
       <c r="AE20">
-        <v>0.4239999999999999</v>
+        <v>0.2330791938749722</v>
       </c>
       <c r="AF20">
-        <v>0.4255</v>
+        <v>0.2401945117021789</v>
       </c>
       <c r="AG20">
-        <v>0.427</v>
+        <v>0.2473098295293856</v>
       </c>
       <c r="AH20">
-        <v>0.4285</v>
+        <v>0.2544251473565923</v>
       </c>
       <c r="AI20">
-        <v>0.43</v>
+        <v>0.261540465183799</v>
       </c>
       <c r="AJ20">
-        <v>0.4315</v>
+        <v>0.2686557830110057</v>
       </c>
       <c r="AK20">
-        <v>0.4330000000000001</v>
+        <v>0.2757711008382124</v>
       </c>
       <c r="AL20">
-        <v>0.4345</v>
+        <v>0.2828864186654191</v>
       </c>
       <c r="AM20">
-        <v>0.436</v>
+        <v>0.2900017364926258</v>
       </c>
       <c r="AN20">
-        <v>0.4375</v>
+        <v>0.2971170543198325</v>
       </c>
       <c r="AO20">
-        <v>0.439</v>
+        <v>0.3042323721470392</v>
       </c>
       <c r="AP20">
-        <v>0.4405</v>
+        <v>0.3113476899742459</v>
       </c>
       <c r="AQ20">
-        <v>0.442</v>
+        <v>0.3184630078014526</v>
       </c>
       <c r="AR20">
-        <v>0.4435</v>
+        <v>0.3255783256286593</v>
       </c>
       <c r="AS20">
-        <v>0.445</v>
+        <v>0.332693643455866</v>
       </c>
       <c r="AT20">
-        <v>0.4465</v>
+        <v>0.3398089612830727</v>
       </c>
       <c r="AU20">
-        <v>0.448</v>
+        <v>0.3469242791102794</v>
       </c>
       <c r="AV20">
-        <v>0.4495</v>
+        <v>0.3540395969374861</v>
       </c>
       <c r="AW20">
-        <v>0.451</v>
+        <v>0.3611549147646928</v>
       </c>
       <c r="AX20">
-        <v>0.4525</v>
+        <v>0.3682702325918995</v>
       </c>
       <c r="AY20">
-        <v>0.454</v>
+        <v>0.3753855504191062</v>
       </c>
       <c r="AZ20">
-        <v>0.4555</v>
+        <v>0.3825008682463129</v>
       </c>
       <c r="BA20">
-        <v>0.457</v>
+        <v>0.3896161860735196</v>
       </c>
       <c r="BB20">
-        <v>0.4585</v>
+        <v>0.3967315039007263</v>
       </c>
       <c r="BC20">
-        <v>0.46</v>
+        <v>0.403846821727933</v>
       </c>
       <c r="BD20">
-        <v>0.4615</v>
+        <v>0.4109621395551397</v>
       </c>
       <c r="BE20">
-        <v>0.463</v>
+        <v>0.4180774573823464</v>
       </c>
       <c r="BF20">
-        <v>0.4645</v>
+        <v>0.4251927752095531</v>
       </c>
       <c r="BG20">
-        <v>0.466</v>
+        <v>0.4323080930367598</v>
       </c>
       <c r="BH20">
-        <v>0.4675</v>
+        <v>0.4394234108639665</v>
       </c>
       <c r="BI20">
-        <v>0.469</v>
+        <v>0.4465387286911732</v>
       </c>
       <c r="BJ20">
-        <v>0.4705</v>
+        <v>0.4536540465183799</v>
       </c>
       <c r="BK20">
-        <v>0.472</v>
+        <v>0.4607693643455866</v>
       </c>
       <c r="BL20">
-        <v>0.4735</v>
+        <v>0.4678846821727933</v>
       </c>
       <c r="BM20">
         <v>0.475</v>
@@ -54239,169 +54239,169 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P21">
-        <v>0.0291</v>
+        <v>0.1263494264668718</v>
       </c>
       <c r="Q21">
-        <v>0.0382</v>
+        <v>0.1334647442940785</v>
       </c>
       <c r="R21">
-        <v>0.04729999999999999</v>
+        <v>0.1405800621212852</v>
       </c>
       <c r="S21">
-        <v>0.0564</v>
+        <v>0.1476953799484919</v>
       </c>
       <c r="T21">
-        <v>0.0655</v>
+        <v>0.1548106977756986</v>
       </c>
       <c r="U21">
-        <v>0.0746</v>
+        <v>0.1619260156029053</v>
       </c>
       <c r="V21">
-        <v>0.0837</v>
+        <v>0.169041333430112</v>
       </c>
       <c r="W21">
-        <v>0.09279999999999999</v>
+        <v>0.1761566512573187</v>
       </c>
       <c r="X21">
-        <v>0.1019</v>
+        <v>0.1832719690845254</v>
       </c>
       <c r="Y21">
-        <v>0.111</v>
+        <v>0.1903872869117321</v>
       </c>
       <c r="Z21">
-        <v>0.1201</v>
+        <v>0.1975026047389387</v>
       </c>
       <c r="AA21">
-        <v>0.1292</v>
+        <v>0.2046179225661454</v>
       </c>
       <c r="AB21">
-        <v>0.1383</v>
+        <v>0.2117332403933521</v>
       </c>
       <c r="AC21">
-        <v>0.1474</v>
+        <v>0.2188485582205588</v>
       </c>
       <c r="AD21">
-        <v>0.1565</v>
+        <v>0.2259638760477655</v>
       </c>
       <c r="AE21">
-        <v>0.1656</v>
+        <v>0.2330791938749722</v>
       </c>
       <c r="AF21">
-        <v>0.1747</v>
+        <v>0.2401945117021789</v>
       </c>
       <c r="AG21">
-        <v>0.1838</v>
+        <v>0.2473098295293856</v>
       </c>
       <c r="AH21">
-        <v>0.1929</v>
+        <v>0.2544251473565923</v>
       </c>
       <c r="AI21">
-        <v>0.202</v>
+        <v>0.261540465183799</v>
       </c>
       <c r="AJ21">
-        <v>0.2111</v>
+        <v>0.2686557830110057</v>
       </c>
       <c r="AK21">
-        <v>0.2202</v>
+        <v>0.2757711008382124</v>
       </c>
       <c r="AL21">
-        <v>0.2293</v>
+        <v>0.2828864186654191</v>
       </c>
       <c r="AM21">
-        <v>0.2384</v>
+        <v>0.2900017364926258</v>
       </c>
       <c r="AN21">
-        <v>0.2475</v>
+        <v>0.2971170543198325</v>
       </c>
       <c r="AO21">
-        <v>0.2566</v>
+        <v>0.3042323721470392</v>
       </c>
       <c r="AP21">
-        <v>0.2657</v>
+        <v>0.3113476899742459</v>
       </c>
       <c r="AQ21">
-        <v>0.2748</v>
+        <v>0.3184630078014526</v>
       </c>
       <c r="AR21">
-        <v>0.2839</v>
+        <v>0.3255783256286593</v>
       </c>
       <c r="AS21">
-        <v>0.293</v>
+        <v>0.332693643455866</v>
       </c>
       <c r="AT21">
-        <v>0.3021</v>
+        <v>0.3398089612830727</v>
       </c>
       <c r="AU21">
-        <v>0.3112</v>
+        <v>0.3469242791102794</v>
       </c>
       <c r="AV21">
-        <v>0.3203</v>
+        <v>0.3540395969374861</v>
       </c>
       <c r="AW21">
-        <v>0.3294</v>
+        <v>0.3611549147646928</v>
       </c>
       <c r="AX21">
-        <v>0.3385</v>
+        <v>0.3682702325918995</v>
       </c>
       <c r="AY21">
-        <v>0.3476</v>
+        <v>0.3753855504191062</v>
       </c>
       <c r="AZ21">
-        <v>0.3567</v>
+        <v>0.3825008682463129</v>
       </c>
       <c r="BA21">
-        <v>0.3658</v>
+        <v>0.3896161860735196</v>
       </c>
       <c r="BB21">
-        <v>0.3749</v>
+        <v>0.3967315039007263</v>
       </c>
       <c r="BC21">
-        <v>0.384</v>
+        <v>0.403846821727933</v>
       </c>
       <c r="BD21">
-        <v>0.3930999999999999</v>
+        <v>0.4109621395551397</v>
       </c>
       <c r="BE21">
-        <v>0.4021999999999999</v>
+        <v>0.4180774573823464</v>
       </c>
       <c r="BF21">
-        <v>0.4113</v>
+        <v>0.4251927752095531</v>
       </c>
       <c r="BG21">
-        <v>0.4204</v>
+        <v>0.4323080930367598</v>
       </c>
       <c r="BH21">
-        <v>0.4295</v>
+        <v>0.4394234108639665</v>
       </c>
       <c r="BI21">
-        <v>0.4386</v>
+        <v>0.4465387286911732</v>
       </c>
       <c r="BJ21">
-        <v>0.4476999999999999</v>
+        <v>0.4536540465183799</v>
       </c>
       <c r="BK21">
-        <v>0.4568</v>
+        <v>0.4607693643455866</v>
       </c>
       <c r="BL21">
-        <v>0.4659</v>
+        <v>0.4678846821727933</v>
       </c>
       <c r="BM21">
         <v>0.475</v>
@@ -54424,169 +54424,169 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P22">
-        <v>0.01523442688</v>
+        <v>0.0615805904422219</v>
       </c>
       <c r="Q22">
-        <v>0.02461739776</v>
+        <v>0.07001772124952349</v>
       </c>
       <c r="R22">
-        <v>0.03400036864</v>
+        <v>0.07845485205682509</v>
       </c>
       <c r="S22">
-        <v>0.04338333952</v>
+        <v>0.08689198286412669</v>
       </c>
       <c r="T22">
-        <v>0.0527663104</v>
+        <v>0.09532911367142828</v>
       </c>
       <c r="U22">
-        <v>0.06214928128</v>
+        <v>0.1037662444787299</v>
       </c>
       <c r="V22">
-        <v>0.07153225216</v>
+        <v>0.1122033752860315</v>
       </c>
       <c r="W22">
-        <v>0.08091522304</v>
+        <v>0.1206405060933331</v>
       </c>
       <c r="X22">
-        <v>0.09029819391999999</v>
+        <v>0.1290776369006346</v>
       </c>
       <c r="Y22">
-        <v>0.0996811648</v>
+        <v>0.1375147677079362</v>
       </c>
       <c r="Z22">
-        <v>0.10906413568</v>
+        <v>0.1459518985152378</v>
       </c>
       <c r="AA22">
-        <v>0.11844710656</v>
+        <v>0.1543890293225394</v>
       </c>
       <c r="AB22">
-        <v>0.12783007744</v>
+        <v>0.162826160129841</v>
       </c>
       <c r="AC22">
-        <v>0.13721304832</v>
+        <v>0.1712632909371426</v>
       </c>
       <c r="AD22">
-        <v>0.1465960192</v>
+        <v>0.1797004217444442</v>
       </c>
       <c r="AE22">
-        <v>0.15597899008</v>
+        <v>0.1881375525517458</v>
       </c>
       <c r="AF22">
-        <v>0.16536196096</v>
+        <v>0.1965746833590474</v>
       </c>
       <c r="AG22">
-        <v>0.17474493184</v>
+        <v>0.205011814166349</v>
       </c>
       <c r="AH22">
-        <v>0.18412790272</v>
+        <v>0.2134489449736506</v>
       </c>
       <c r="AI22">
-        <v>0.1935108736</v>
+        <v>0.2218860757809522</v>
       </c>
       <c r="AJ22">
-        <v>0.20289384448</v>
+        <v>0.2303232065882538</v>
       </c>
       <c r="AK22">
-        <v>0.21227681536</v>
+        <v>0.2387603373955554</v>
       </c>
       <c r="AL22">
-        <v>0.22165978624</v>
+        <v>0.247197468202857</v>
       </c>
       <c r="AM22">
-        <v>0.23104275712</v>
+        <v>0.2556345990101586</v>
       </c>
       <c r="AN22">
-        <v>0.240425728</v>
+        <v>0.2640717298174601</v>
       </c>
       <c r="AO22">
-        <v>0.24980869888</v>
+        <v>0.2725088606247618</v>
       </c>
       <c r="AP22">
-        <v>0.25919166976</v>
+        <v>0.2809459914320633</v>
       </c>
       <c r="AQ22">
-        <v>0.26857464064</v>
+        <v>0.289383122239365</v>
       </c>
       <c r="AR22">
-        <v>0.27795761152</v>
+        <v>0.2978202530466665</v>
       </c>
       <c r="AS22">
-        <v>0.2873405824</v>
+        <v>0.3062573838539681</v>
       </c>
       <c r="AT22">
-        <v>0.29672355328</v>
+        <v>0.3146945146612697</v>
       </c>
       <c r="AU22">
-        <v>0.30610652416</v>
+        <v>0.3231316454685713</v>
       </c>
       <c r="AV22">
-        <v>0.31548949504</v>
+        <v>0.3315687762758729</v>
       </c>
       <c r="AW22">
-        <v>0.32487246592</v>
+        <v>0.3400059070831745</v>
       </c>
       <c r="AX22">
-        <v>0.3342554368</v>
+        <v>0.348443037890476</v>
       </c>
       <c r="AY22">
-        <v>0.34363840768</v>
+        <v>0.3568801686977777</v>
       </c>
       <c r="AZ22">
-        <v>0.35302137856</v>
+        <v>0.3653172995050792</v>
       </c>
       <c r="BA22">
-        <v>0.36240434944</v>
+        <v>0.3737544303123809</v>
       </c>
       <c r="BB22">
-        <v>0.37178732032</v>
+        <v>0.3821915611196824</v>
       </c>
       <c r="BC22">
-        <v>0.3811702912</v>
+        <v>0.3906286919269841</v>
       </c>
       <c r="BD22">
-        <v>0.39055326208</v>
+        <v>0.3990658227342856</v>
       </c>
       <c r="BE22">
-        <v>0.39993623296</v>
+        <v>0.4075029535415872</v>
       </c>
       <c r="BF22">
-        <v>0.40931920384</v>
+        <v>0.4159400843488888</v>
       </c>
       <c r="BG22">
-        <v>0.41870217472</v>
+        <v>0.4243772151561904</v>
       </c>
       <c r="BH22">
-        <v>0.4280851456</v>
+        <v>0.432814345963492</v>
       </c>
       <c r="BI22">
-        <v>0.43746811648</v>
+        <v>0.4412514767707936</v>
       </c>
       <c r="BJ22">
-        <v>0.44685108736</v>
+        <v>0.4496886075780952</v>
       </c>
       <c r="BK22">
-        <v>0.45623405824</v>
+        <v>0.4581257383853968</v>
       </c>
       <c r="BL22">
-        <v>0.46561702912</v>
+        <v>0.4665628691926984</v>
       </c>
       <c r="BM22">
         <v>0.475</v>
@@ -54609,169 +54609,169 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P23">
-        <v>0.01523442688</v>
+        <v>0.0615805904422219</v>
       </c>
       <c r="Q23">
-        <v>0.02461739776</v>
+        <v>0.07001772124952349</v>
       </c>
       <c r="R23">
-        <v>0.03400036864</v>
+        <v>0.07845485205682509</v>
       </c>
       <c r="S23">
-        <v>0.04338333952</v>
+        <v>0.08689198286412669</v>
       </c>
       <c r="T23">
-        <v>0.0527663104</v>
+        <v>0.09532911367142828</v>
       </c>
       <c r="U23">
-        <v>0.06214928128</v>
+        <v>0.1037662444787299</v>
       </c>
       <c r="V23">
-        <v>0.07153225216</v>
+        <v>0.1122033752860315</v>
       </c>
       <c r="W23">
-        <v>0.08091522304</v>
+        <v>0.1206405060933331</v>
       </c>
       <c r="X23">
-        <v>0.09029819391999999</v>
+        <v>0.1290776369006346</v>
       </c>
       <c r="Y23">
-        <v>0.0996811648</v>
+        <v>0.1375147677079362</v>
       </c>
       <c r="Z23">
-        <v>0.10906413568</v>
+        <v>0.1459518985152378</v>
       </c>
       <c r="AA23">
-        <v>0.11844710656</v>
+        <v>0.1543890293225394</v>
       </c>
       <c r="AB23">
-        <v>0.12783007744</v>
+        <v>0.162826160129841</v>
       </c>
       <c r="AC23">
-        <v>0.13721304832</v>
+        <v>0.1712632909371426</v>
       </c>
       <c r="AD23">
-        <v>0.1465960192</v>
+        <v>0.1797004217444442</v>
       </c>
       <c r="AE23">
-        <v>0.15597899008</v>
+        <v>0.1881375525517458</v>
       </c>
       <c r="AF23">
-        <v>0.16536196096</v>
+        <v>0.1965746833590474</v>
       </c>
       <c r="AG23">
-        <v>0.17474493184</v>
+        <v>0.205011814166349</v>
       </c>
       <c r="AH23">
-        <v>0.18412790272</v>
+        <v>0.2134489449736506</v>
       </c>
       <c r="AI23">
-        <v>0.1935108736</v>
+        <v>0.2218860757809522</v>
       </c>
       <c r="AJ23">
-        <v>0.20289384448</v>
+        <v>0.2303232065882538</v>
       </c>
       <c r="AK23">
-        <v>0.21227681536</v>
+        <v>0.2387603373955554</v>
       </c>
       <c r="AL23">
-        <v>0.22165978624</v>
+        <v>0.247197468202857</v>
       </c>
       <c r="AM23">
-        <v>0.23104275712</v>
+        <v>0.2556345990101586</v>
       </c>
       <c r="AN23">
-        <v>0.240425728</v>
+        <v>0.2640717298174601</v>
       </c>
       <c r="AO23">
-        <v>0.24980869888</v>
+        <v>0.2725088606247618</v>
       </c>
       <c r="AP23">
-        <v>0.25919166976</v>
+        <v>0.2809459914320633</v>
       </c>
       <c r="AQ23">
-        <v>0.26857464064</v>
+        <v>0.289383122239365</v>
       </c>
       <c r="AR23">
-        <v>0.27795761152</v>
+        <v>0.2978202530466665</v>
       </c>
       <c r="AS23">
-        <v>0.2873405824</v>
+        <v>0.3062573838539681</v>
       </c>
       <c r="AT23">
-        <v>0.29672355328</v>
+        <v>0.3146945146612697</v>
       </c>
       <c r="AU23">
-        <v>0.30610652416</v>
+        <v>0.3231316454685713</v>
       </c>
       <c r="AV23">
-        <v>0.31548949504</v>
+        <v>0.3315687762758729</v>
       </c>
       <c r="AW23">
-        <v>0.32487246592</v>
+        <v>0.3400059070831745</v>
       </c>
       <c r="AX23">
-        <v>0.3342554368</v>
+        <v>0.348443037890476</v>
       </c>
       <c r="AY23">
-        <v>0.34363840768</v>
+        <v>0.3568801686977777</v>
       </c>
       <c r="AZ23">
-        <v>0.35302137856</v>
+        <v>0.3653172995050792</v>
       </c>
       <c r="BA23">
-        <v>0.36240434944</v>
+        <v>0.3737544303123809</v>
       </c>
       <c r="BB23">
-        <v>0.37178732032</v>
+        <v>0.3821915611196824</v>
       </c>
       <c r="BC23">
-        <v>0.3811702912</v>
+        <v>0.3906286919269841</v>
       </c>
       <c r="BD23">
-        <v>0.39055326208</v>
+        <v>0.3990658227342856</v>
       </c>
       <c r="BE23">
-        <v>0.39993623296</v>
+        <v>0.4075029535415872</v>
       </c>
       <c r="BF23">
-        <v>0.40931920384</v>
+        <v>0.4159400843488888</v>
       </c>
       <c r="BG23">
-        <v>0.41870217472</v>
+        <v>0.4243772151561904</v>
       </c>
       <c r="BH23">
-        <v>0.4280851456</v>
+        <v>0.432814345963492</v>
       </c>
       <c r="BI23">
-        <v>0.43746811648</v>
+        <v>0.4412514767707936</v>
       </c>
       <c r="BJ23">
-        <v>0.44685108736</v>
+        <v>0.4496886075780952</v>
       </c>
       <c r="BK23">
-        <v>0.45623405824</v>
+        <v>0.4581257383853968</v>
       </c>
       <c r="BL23">
-        <v>0.46561702912</v>
+        <v>0.4665628691926984</v>
       </c>
       <c r="BM23">
         <v>0.475</v>
@@ -54794,169 +54794,169 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P24">
-        <v>0.01523442688</v>
+        <v>0.0615805904422219</v>
       </c>
       <c r="Q24">
-        <v>0.02461739776</v>
+        <v>0.07001772124952349</v>
       </c>
       <c r="R24">
-        <v>0.03400036864</v>
+        <v>0.07845485205682509</v>
       </c>
       <c r="S24">
-        <v>0.04338333952</v>
+        <v>0.08689198286412669</v>
       </c>
       <c r="T24">
-        <v>0.0527663104</v>
+        <v>0.09532911367142828</v>
       </c>
       <c r="U24">
-        <v>0.06214928128</v>
+        <v>0.1037662444787299</v>
       </c>
       <c r="V24">
-        <v>0.07153225216</v>
+        <v>0.1122033752860315</v>
       </c>
       <c r="W24">
-        <v>0.08091522304</v>
+        <v>0.1206405060933331</v>
       </c>
       <c r="X24">
-        <v>0.09029819391999999</v>
+        <v>0.1290776369006346</v>
       </c>
       <c r="Y24">
-        <v>0.0996811648</v>
+        <v>0.1375147677079362</v>
       </c>
       <c r="Z24">
-        <v>0.10906413568</v>
+        <v>0.1459518985152378</v>
       </c>
       <c r="AA24">
-        <v>0.11844710656</v>
+        <v>0.1543890293225394</v>
       </c>
       <c r="AB24">
-        <v>0.12783007744</v>
+        <v>0.162826160129841</v>
       </c>
       <c r="AC24">
-        <v>0.13721304832</v>
+        <v>0.1712632909371426</v>
       </c>
       <c r="AD24">
-        <v>0.1465960192</v>
+        <v>0.1797004217444442</v>
       </c>
       <c r="AE24">
-        <v>0.15597899008</v>
+        <v>0.1881375525517458</v>
       </c>
       <c r="AF24">
-        <v>0.16536196096</v>
+        <v>0.1965746833590474</v>
       </c>
       <c r="AG24">
-        <v>0.17474493184</v>
+        <v>0.205011814166349</v>
       </c>
       <c r="AH24">
-        <v>0.18412790272</v>
+        <v>0.2134489449736506</v>
       </c>
       <c r="AI24">
-        <v>0.1935108736</v>
+        <v>0.2218860757809522</v>
       </c>
       <c r="AJ24">
-        <v>0.20289384448</v>
+        <v>0.2303232065882538</v>
       </c>
       <c r="AK24">
-        <v>0.21227681536</v>
+        <v>0.2387603373955554</v>
       </c>
       <c r="AL24">
-        <v>0.22165978624</v>
+        <v>0.247197468202857</v>
       </c>
       <c r="AM24">
-        <v>0.23104275712</v>
+        <v>0.2556345990101586</v>
       </c>
       <c r="AN24">
-        <v>0.240425728</v>
+        <v>0.2640717298174601</v>
       </c>
       <c r="AO24">
-        <v>0.24980869888</v>
+        <v>0.2725088606247618</v>
       </c>
       <c r="AP24">
-        <v>0.25919166976</v>
+        <v>0.2809459914320633</v>
       </c>
       <c r="AQ24">
-        <v>0.26857464064</v>
+        <v>0.289383122239365</v>
       </c>
       <c r="AR24">
-        <v>0.27795761152</v>
+        <v>0.2978202530466665</v>
       </c>
       <c r="AS24">
-        <v>0.2873405824</v>
+        <v>0.3062573838539681</v>
       </c>
       <c r="AT24">
-        <v>0.29672355328</v>
+        <v>0.3146945146612697</v>
       </c>
       <c r="AU24">
-        <v>0.30610652416</v>
+        <v>0.3231316454685713</v>
       </c>
       <c r="AV24">
-        <v>0.31548949504</v>
+        <v>0.3315687762758729</v>
       </c>
       <c r="AW24">
-        <v>0.32487246592</v>
+        <v>0.3400059070831745</v>
       </c>
       <c r="AX24">
-        <v>0.3342554368</v>
+        <v>0.348443037890476</v>
       </c>
       <c r="AY24">
-        <v>0.34363840768</v>
+        <v>0.3568801686977777</v>
       </c>
       <c r="AZ24">
-        <v>0.35302137856</v>
+        <v>0.3653172995050792</v>
       </c>
       <c r="BA24">
-        <v>0.36240434944</v>
+        <v>0.3737544303123809</v>
       </c>
       <c r="BB24">
-        <v>0.37178732032</v>
+        <v>0.3821915611196824</v>
       </c>
       <c r="BC24">
-        <v>0.3811702912</v>
+        <v>0.3906286919269841</v>
       </c>
       <c r="BD24">
-        <v>0.39055326208</v>
+        <v>0.3990658227342856</v>
       </c>
       <c r="BE24">
-        <v>0.39993623296</v>
+        <v>0.4075029535415872</v>
       </c>
       <c r="BF24">
-        <v>0.40931920384</v>
+        <v>0.4159400843488888</v>
       </c>
       <c r="BG24">
-        <v>0.41870217472</v>
+        <v>0.4243772151561904</v>
       </c>
       <c r="BH24">
-        <v>0.4280851456</v>
+        <v>0.432814345963492</v>
       </c>
       <c r="BI24">
-        <v>0.43746811648</v>
+        <v>0.4412514767707936</v>
       </c>
       <c r="BJ24">
-        <v>0.44685108736</v>
+        <v>0.4496886075780952</v>
       </c>
       <c r="BK24">
-        <v>0.45623405824</v>
+        <v>0.4581257383853968</v>
       </c>
       <c r="BL24">
-        <v>0.46561702912</v>
+        <v>0.4665628691926984</v>
       </c>
       <c r="BM24">
         <v>0.475</v>
@@ -55164,172 +55164,172 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="P26">
-        <v>0.017119783</v>
+        <v>0.3466350032507819</v>
       </c>
       <c r="Q26">
-        <v>0.034239566</v>
+        <v>0.3599329487215936</v>
       </c>
       <c r="R26">
-        <v>0.051359349</v>
+        <v>0.3732308941924052</v>
       </c>
       <c r="S26">
-        <v>0.068479132</v>
+        <v>0.386528839663217</v>
       </c>
       <c r="T26">
-        <v>0.085598915</v>
+        <v>0.3998267851340287</v>
       </c>
       <c r="U26">
-        <v>0.102718698</v>
+        <v>0.4131247306048403</v>
       </c>
       <c r="V26">
-        <v>0.119838481</v>
+        <v>0.426422676075652</v>
       </c>
       <c r="W26">
-        <v>0.136958264</v>
+        <v>0.4397206215464636</v>
       </c>
       <c r="X26">
-        <v>0.154078047</v>
+        <v>0.4530185670172753</v>
       </c>
       <c r="Y26">
-        <v>0.17119783</v>
+        <v>0.466316512488087</v>
       </c>
       <c r="Z26">
-        <v>0.188317613</v>
+        <v>0.4796144579588987</v>
       </c>
       <c r="AA26">
-        <v>0.205437396</v>
+        <v>0.4929124034297104</v>
       </c>
       <c r="AB26">
-        <v>0.222557179</v>
+        <v>0.5062103489005221</v>
       </c>
       <c r="AC26">
-        <v>0.239676962</v>
+        <v>0.5195082943713337</v>
       </c>
       <c r="AD26">
-        <v>0.256796745</v>
+        <v>0.5328062398421454</v>
       </c>
       <c r="AE26">
-        <v>0.273916528</v>
+        <v>0.546104185312957</v>
       </c>
       <c r="AF26">
-        <v>0.291036311</v>
+        <v>0.5594021307837688</v>
       </c>
       <c r="AG26">
-        <v>0.308156094</v>
+        <v>0.5727000762545804</v>
       </c>
       <c r="AH26">
-        <v>0.325275877</v>
+        <v>0.5859980217253921</v>
       </c>
       <c r="AI26">
-        <v>0.34239566</v>
+        <v>0.5992959671962038</v>
       </c>
       <c r="AJ26">
-        <v>0.359515443</v>
+        <v>0.6125939126670155</v>
       </c>
       <c r="AK26">
-        <v>0.376635226</v>
+        <v>0.6258918581378271</v>
       </c>
       <c r="AL26">
-        <v>0.393755009</v>
+        <v>0.6391898036086389</v>
       </c>
       <c r="AM26">
-        <v>0.410874792</v>
+        <v>0.6524877490794505</v>
       </c>
       <c r="AN26">
-        <v>0.427994575</v>
+        <v>0.6657856945502622</v>
       </c>
       <c r="AO26">
-        <v>0.445114358</v>
+        <v>0.6790836400210738</v>
       </c>
       <c r="AP26">
-        <v>0.462234141</v>
+        <v>0.6923815854918854</v>
       </c>
       <c r="AQ26">
-        <v>0.479353924</v>
+        <v>0.7056795309626972</v>
       </c>
       <c r="AR26">
-        <v>0.4964737069999999</v>
+        <v>0.7189774764335088</v>
       </c>
       <c r="AS26">
-        <v>0.51359349</v>
+        <v>0.7322754219043205</v>
       </c>
       <c r="AT26">
-        <v>0.5307132729999999</v>
+        <v>0.7455733673751322</v>
       </c>
       <c r="AU26">
-        <v>0.547833056</v>
+        <v>0.7588713128459439</v>
       </c>
       <c r="AV26">
-        <v>0.564952839</v>
+        <v>0.7721692583167555</v>
       </c>
       <c r="AW26">
-        <v>0.582072622</v>
+        <v>0.7854672037875673</v>
       </c>
       <c r="AX26">
-        <v>0.5991924049999999</v>
+        <v>0.7987651492583789</v>
       </c>
       <c r="AY26">
-        <v>0.616312188</v>
+        <v>0.8120630947291906</v>
       </c>
       <c r="AZ26">
-        <v>0.6334319709999999</v>
+        <v>0.8253610402000023</v>
       </c>
       <c r="BA26">
-        <v>0.650551754</v>
+        <v>0.838658985670814</v>
       </c>
       <c r="BB26">
-        <v>0.667671537</v>
+        <v>0.8519569311416256</v>
       </c>
       <c r="BC26">
-        <v>0.68479132</v>
+        <v>0.8652548766124373</v>
       </c>
       <c r="BD26">
-        <v>0.7019111029999999</v>
+        <v>0.878552822083249</v>
       </c>
       <c r="BE26">
-        <v>0.719030886</v>
+        <v>0.8918507675540607</v>
       </c>
       <c r="BF26">
-        <v>0.7361506689999999</v>
+        <v>0.9051487130248723</v>
       </c>
       <c r="BG26">
-        <v>0.753270452</v>
+        <v>0.918446658495684</v>
       </c>
       <c r="BH26">
-        <v>0.770390235</v>
+        <v>0.9317446039664956</v>
       </c>
       <c r="BI26">
-        <v>0.787510018</v>
+        <v>0.9450425494373074</v>
       </c>
       <c r="BJ26">
-        <v>0.8046298009999999</v>
+        <v>0.958340494908119</v>
       </c>
       <c r="BK26">
-        <v>0.821749584</v>
+        <v>0.9716384403789307</v>
       </c>
       <c r="BL26">
-        <v>0.8388693669999999</v>
+        <v>0.9849363858497424</v>
       </c>
       <c r="BM26">
-        <v>0.85598915</v>
+        <v>0.9982343313205541</v>
       </c>
     </row>
     <row r="27" spans="1:65">
@@ -55349,169 +55349,169 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="K27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="L27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="M27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="N27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="O27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="P27">
-        <v>0.8388693669999999</v>
+        <v>0.6515993280697722</v>
       </c>
       <c r="Q27">
-        <v>0.821749584</v>
+        <v>0.6383013825989604</v>
       </c>
       <c r="R27">
-        <v>0.8046298009999999</v>
+        <v>0.6250034371281488</v>
       </c>
       <c r="S27">
-        <v>0.787510018</v>
+        <v>0.6117054916573371</v>
       </c>
       <c r="T27">
-        <v>0.770390235</v>
+        <v>0.5984075461865255</v>
       </c>
       <c r="U27">
-        <v>0.753270452</v>
+        <v>0.5851096007157137</v>
       </c>
       <c r="V27">
-        <v>0.7361506689999999</v>
+        <v>0.5718116552449021</v>
       </c>
       <c r="W27">
-        <v>0.719030886</v>
+        <v>0.5585137097740904</v>
       </c>
       <c r="X27">
-        <v>0.701911103</v>
+        <v>0.5452157643032788</v>
       </c>
       <c r="Y27">
-        <v>0.68479132</v>
+        <v>0.531917818832467</v>
       </c>
       <c r="Z27">
-        <v>0.667671537</v>
+        <v>0.5186198733616554</v>
       </c>
       <c r="AA27">
-        <v>0.650551754</v>
+        <v>0.5053219278908437</v>
       </c>
       <c r="AB27">
-        <v>0.6334319709999999</v>
+        <v>0.492023982420032</v>
       </c>
       <c r="AC27">
-        <v>0.616312188</v>
+        <v>0.4787260369492203</v>
       </c>
       <c r="AD27">
-        <v>0.5991924049999999</v>
+        <v>0.4654280914784086</v>
       </c>
       <c r="AE27">
-        <v>0.582072622</v>
+        <v>0.4521301460075969</v>
       </c>
       <c r="AF27">
-        <v>0.5649528389999999</v>
+        <v>0.4388322005367853</v>
       </c>
       <c r="AG27">
-        <v>0.547833056</v>
+        <v>0.4255342550659736</v>
       </c>
       <c r="AH27">
-        <v>0.5307132729999999</v>
+        <v>0.4122363095951619</v>
       </c>
       <c r="AI27">
-        <v>0.51359349</v>
+        <v>0.3989383641243503</v>
       </c>
       <c r="AJ27">
-        <v>0.496473707</v>
+        <v>0.3856404186535387</v>
       </c>
       <c r="AK27">
-        <v>0.479353924</v>
+        <v>0.372342473182727</v>
       </c>
       <c r="AL27">
-        <v>0.462234141</v>
+        <v>0.3590445277119153</v>
       </c>
       <c r="AM27">
-        <v>0.445114358</v>
+        <v>0.3457465822411036</v>
       </c>
       <c r="AN27">
-        <v>0.427994575</v>
+        <v>0.3324486367702919</v>
       </c>
       <c r="AO27">
-        <v>0.410874792</v>
+        <v>0.3191506912994802</v>
       </c>
       <c r="AP27">
-        <v>0.3937550089999999</v>
+        <v>0.3058527458286685</v>
       </c>
       <c r="AQ27">
-        <v>0.3766352259999999</v>
+        <v>0.2925548003578569</v>
       </c>
       <c r="AR27">
-        <v>0.359515443</v>
+        <v>0.2792568548870452</v>
       </c>
       <c r="AS27">
-        <v>0.34239566</v>
+        <v>0.2659589094162335</v>
       </c>
       <c r="AT27">
-        <v>0.325275877</v>
+        <v>0.2526609639454219</v>
       </c>
       <c r="AU27">
-        <v>0.308156094</v>
+        <v>0.2393630184746102</v>
       </c>
       <c r="AV27">
-        <v>0.291036311</v>
+        <v>0.2260650730037985</v>
       </c>
       <c r="AW27">
-        <v>0.2739165279999999</v>
+        <v>0.2127671275329868</v>
       </c>
       <c r="AX27">
-        <v>0.256796745</v>
+        <v>0.1994691820621752</v>
       </c>
       <c r="AY27">
-        <v>0.239676962</v>
+        <v>0.1861712365913635</v>
       </c>
       <c r="AZ27">
-        <v>0.222557179</v>
+        <v>0.1728732911205518</v>
       </c>
       <c r="BA27">
-        <v>0.205437396</v>
+        <v>0.1595753456497401</v>
       </c>
       <c r="BB27">
-        <v>0.188317613</v>
+        <v>0.1462774001789284</v>
       </c>
       <c r="BC27">
-        <v>0.17119783</v>
+        <v>0.1329794547081167</v>
       </c>
       <c r="BD27">
-        <v>0.1540780470000001</v>
+        <v>0.1196815092373051</v>
       </c>
       <c r="BE27">
-        <v>0.136958264</v>
+        <v>0.1063835637664934</v>
       </c>
       <c r="BF27">
-        <v>0.119838481</v>
+        <v>0.09308561829568174</v>
       </c>
       <c r="BG27">
-        <v>0.102718698</v>
+        <v>0.07978767282487005</v>
       </c>
       <c r="BH27">
-        <v>0.08559891499999998</v>
+        <v>0.06648972735405836</v>
       </c>
       <c r="BI27">
-        <v>0.06847913199999997</v>
+        <v>0.05319178188324668</v>
       </c>
       <c r="BJ27">
-        <v>0.05135934900000005</v>
+        <v>0.03989383641243507</v>
       </c>
       <c r="BK27">
-        <v>0.03423956600000003</v>
+        <v>0.02659589094162338</v>
       </c>
       <c r="BL27">
-        <v>0.01711978300000001</v>
+        <v>0.01329794547081169</v>
       </c>
       <c r="BM27">
         <v>0</v>
@@ -60366,169 +60366,169 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U19">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V19">
-        <v>0.03034090909090909</v>
+        <v>0.1273196970796727</v>
       </c>
       <c r="W19">
-        <v>0.04068181818181818</v>
+        <v>0.1354052855196803</v>
       </c>
       <c r="X19">
-        <v>0.05102272727272727</v>
+        <v>0.1434908739596879</v>
       </c>
       <c r="Y19">
-        <v>0.06136363636363636</v>
+        <v>0.1515764623996955</v>
       </c>
       <c r="Z19">
-        <v>0.07170454545454545</v>
+        <v>0.1596620508397031</v>
       </c>
       <c r="AA19">
-        <v>0.08204545454545453</v>
+        <v>0.1677476392797107</v>
       </c>
       <c r="AB19">
-        <v>0.09238636363636363</v>
+        <v>0.1758332277197183</v>
       </c>
       <c r="AC19">
-        <v>0.1027272727272727</v>
+        <v>0.1839188161597259</v>
       </c>
       <c r="AD19">
-        <v>0.1130681818181818</v>
+        <v>0.1920044045997336</v>
       </c>
       <c r="AE19">
-        <v>0.1234090909090909</v>
+        <v>0.2000899930397412</v>
       </c>
       <c r="AF19">
-        <v>0.13375</v>
+        <v>0.2081755814797488</v>
       </c>
       <c r="AG19">
-        <v>0.1440909090909091</v>
+        <v>0.2162611699197564</v>
       </c>
       <c r="AH19">
-        <v>0.1544318181818182</v>
+        <v>0.224346758359764</v>
       </c>
       <c r="AI19">
-        <v>0.1647727272727273</v>
+        <v>0.2324323467997716</v>
       </c>
       <c r="AJ19">
-        <v>0.1751136363636363</v>
+        <v>0.2405179352397792</v>
       </c>
       <c r="AK19">
-        <v>0.1854545454545455</v>
+        <v>0.2486035236797869</v>
       </c>
       <c r="AL19">
-        <v>0.1957954545454545</v>
+        <v>0.2566891121197944</v>
       </c>
       <c r="AM19">
-        <v>0.2061363636363636</v>
+        <v>0.2647747005598021</v>
       </c>
       <c r="AN19">
-        <v>0.2164772727272727</v>
+        <v>0.2728602889998097</v>
       </c>
       <c r="AO19">
-        <v>0.2268181818181818</v>
+        <v>0.2809458774398172</v>
       </c>
       <c r="AP19">
-        <v>0.2371590909090909</v>
+        <v>0.2890314658798249</v>
       </c>
       <c r="AQ19">
-        <v>0.2475</v>
+        <v>0.2971170543198325</v>
       </c>
       <c r="AR19">
-        <v>0.2578409090909091</v>
+        <v>0.3052026427598401</v>
       </c>
       <c r="AS19">
-        <v>0.2681818181818181</v>
+        <v>0.3132882311998477</v>
       </c>
       <c r="AT19">
-        <v>0.2785227272727273</v>
+        <v>0.3213738196398554</v>
       </c>
       <c r="AU19">
-        <v>0.2888636363636364</v>
+        <v>0.329459408079863</v>
       </c>
       <c r="AV19">
-        <v>0.2992045454545454</v>
+        <v>0.3375449965198706</v>
       </c>
       <c r="AW19">
-        <v>0.3095454545454545</v>
+        <v>0.3456305849598782</v>
       </c>
       <c r="AX19">
-        <v>0.3198863636363636</v>
+        <v>0.3537161733998858</v>
       </c>
       <c r="AY19">
-        <v>0.3302272727272726</v>
+        <v>0.3618017618398934</v>
       </c>
       <c r="AZ19">
-        <v>0.3405681818181818</v>
+        <v>0.3698873502799011</v>
       </c>
       <c r="BA19">
-        <v>0.3509090909090909</v>
+        <v>0.3779729387199087</v>
       </c>
       <c r="BB19">
-        <v>0.36125</v>
+        <v>0.3860585271599162</v>
       </c>
       <c r="BC19">
-        <v>0.371590909090909</v>
+        <v>0.3941441155999238</v>
       </c>
       <c r="BD19">
-        <v>0.3819318181818182</v>
+        <v>0.4022297040399315</v>
       </c>
       <c r="BE19">
-        <v>0.3922727272727273</v>
+        <v>0.4103152924799391</v>
       </c>
       <c r="BF19">
-        <v>0.4026136363636363</v>
+        <v>0.4184008809199467</v>
       </c>
       <c r="BG19">
-        <v>0.4129545454545455</v>
+        <v>0.4264864693599543</v>
       </c>
       <c r="BH19">
-        <v>0.4232954545454545</v>
+        <v>0.4345720577999619</v>
       </c>
       <c r="BI19">
-        <v>0.4336363636363636</v>
+        <v>0.4426576462399695</v>
       </c>
       <c r="BJ19">
-        <v>0.4439772727272727</v>
+        <v>0.4507432346799771</v>
       </c>
       <c r="BK19">
-        <v>0.4543181818181818</v>
+        <v>0.4588288231199848</v>
       </c>
       <c r="BL19">
-        <v>0.4646590909090909</v>
+        <v>0.4669144115599924</v>
       </c>
       <c r="BM19">
         <v>0.475</v>
@@ -60551,169 +60551,169 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U20">
-        <v>0.4</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V20">
-        <v>0.4017045454545455</v>
+        <v>0.1273196970796727</v>
       </c>
       <c r="W20">
-        <v>0.4034090909090909</v>
+        <v>0.1354052855196803</v>
       </c>
       <c r="X20">
-        <v>0.4051136363636364</v>
+        <v>0.1434908739596879</v>
       </c>
       <c r="Y20">
-        <v>0.4068181818181819</v>
+        <v>0.1515764623996955</v>
       </c>
       <c r="Z20">
-        <v>0.4085227272727273</v>
+        <v>0.1596620508397031</v>
       </c>
       <c r="AA20">
-        <v>0.4102272727272727</v>
+        <v>0.1677476392797107</v>
       </c>
       <c r="AB20">
-        <v>0.4119318181818182</v>
+        <v>0.1758332277197183</v>
       </c>
       <c r="AC20">
-        <v>0.4136363636363636</v>
+        <v>0.1839188161597259</v>
       </c>
       <c r="AD20">
-        <v>0.4153409090909091</v>
+        <v>0.1920044045997336</v>
       </c>
       <c r="AE20">
-        <v>0.4170454545454545</v>
+        <v>0.2000899930397412</v>
       </c>
       <c r="AF20">
-        <v>0.4187500000000001</v>
+        <v>0.2081755814797488</v>
       </c>
       <c r="AG20">
-        <v>0.4204545454545455</v>
+        <v>0.2162611699197564</v>
       </c>
       <c r="AH20">
-        <v>0.422159090909091</v>
+        <v>0.224346758359764</v>
       </c>
       <c r="AI20">
-        <v>0.4238636363636364</v>
+        <v>0.2324323467997716</v>
       </c>
       <c r="AJ20">
-        <v>0.4255681818181818</v>
+        <v>0.2405179352397792</v>
       </c>
       <c r="AK20">
-        <v>0.4272727272727273</v>
+        <v>0.2486035236797869</v>
       </c>
       <c r="AL20">
-        <v>0.4289772727272727</v>
+        <v>0.2566891121197944</v>
       </c>
       <c r="AM20">
-        <v>0.4306818181818182</v>
+        <v>0.2647747005598021</v>
       </c>
       <c r="AN20">
-        <v>0.4323863636363636</v>
+        <v>0.2728602889998097</v>
       </c>
       <c r="AO20">
-        <v>0.4340909090909091</v>
+        <v>0.2809458774398172</v>
       </c>
       <c r="AP20">
-        <v>0.4357954545454545</v>
+        <v>0.2890314658798249</v>
       </c>
       <c r="AQ20">
-        <v>0.4375</v>
+        <v>0.2971170543198325</v>
       </c>
       <c r="AR20">
-        <v>0.4392045454545455</v>
+        <v>0.3052026427598401</v>
       </c>
       <c r="AS20">
-        <v>0.4409090909090909</v>
+        <v>0.3132882311998477</v>
       </c>
       <c r="AT20">
-        <v>0.4426136363636364</v>
+        <v>0.3213738196398554</v>
       </c>
       <c r="AU20">
-        <v>0.4443181818181818</v>
+        <v>0.329459408079863</v>
       </c>
       <c r="AV20">
-        <v>0.4460227272727272</v>
+        <v>0.3375449965198706</v>
       </c>
       <c r="AW20">
-        <v>0.4477272727272728</v>
+        <v>0.3456305849598782</v>
       </c>
       <c r="AX20">
-        <v>0.4494318181818182</v>
+        <v>0.3537161733998858</v>
       </c>
       <c r="AY20">
-        <v>0.4511363636363636</v>
+        <v>0.3618017618398934</v>
       </c>
       <c r="AZ20">
-        <v>0.4528409090909091</v>
+        <v>0.3698873502799011</v>
       </c>
       <c r="BA20">
-        <v>0.4545454545454545</v>
+        <v>0.3779729387199087</v>
       </c>
       <c r="BB20">
-        <v>0.4562499999999999</v>
+        <v>0.3860585271599162</v>
       </c>
       <c r="BC20">
-        <v>0.4579545454545454</v>
+        <v>0.3941441155999238</v>
       </c>
       <c r="BD20">
-        <v>0.4596590909090909</v>
+        <v>0.4022297040399315</v>
       </c>
       <c r="BE20">
-        <v>0.4613636363636364</v>
+        <v>0.4103152924799391</v>
       </c>
       <c r="BF20">
-        <v>0.4630681818181818</v>
+        <v>0.4184008809199467</v>
       </c>
       <c r="BG20">
-        <v>0.4647727272727273</v>
+        <v>0.4264864693599543</v>
       </c>
       <c r="BH20">
-        <v>0.4664772727272727</v>
+        <v>0.4345720577999619</v>
       </c>
       <c r="BI20">
-        <v>0.4681818181818181</v>
+        <v>0.4426576462399695</v>
       </c>
       <c r="BJ20">
-        <v>0.4698863636363636</v>
+        <v>0.4507432346799771</v>
       </c>
       <c r="BK20">
-        <v>0.4715909090909091</v>
+        <v>0.4588288231199848</v>
       </c>
       <c r="BL20">
-        <v>0.4732954545454545</v>
+        <v>0.4669144115599924</v>
       </c>
       <c r="BM20">
         <v>0.475</v>
@@ -60736,169 +60736,169 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="K21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="L21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="M21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="N21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="O21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="P21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="Q21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="R21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="S21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="T21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="U21">
-        <v>0.02</v>
+        <v>0.1192341086396651</v>
       </c>
       <c r="V21">
-        <v>0.03034090909090909</v>
+        <v>0.1273196970796727</v>
       </c>
       <c r="W21">
-        <v>0.04068181818181818</v>
+        <v>0.1354052855196803</v>
       </c>
       <c r="X21">
-        <v>0.05102272727272727</v>
+        <v>0.1434908739596879</v>
       </c>
       <c r="Y21">
-        <v>0.06136363636363636</v>
+        <v>0.1515764623996955</v>
       </c>
       <c r="Z21">
-        <v>0.07170454545454545</v>
+        <v>0.1596620508397031</v>
       </c>
       <c r="AA21">
-        <v>0.08204545454545453</v>
+        <v>0.1677476392797107</v>
       </c>
       <c r="AB21">
-        <v>0.09238636363636363</v>
+        <v>0.1758332277197183</v>
       </c>
       <c r="AC21">
-        <v>0.1027272727272727</v>
+        <v>0.1839188161597259</v>
       </c>
       <c r="AD21">
-        <v>0.1130681818181818</v>
+        <v>0.1920044045997336</v>
       </c>
       <c r="AE21">
-        <v>0.1234090909090909</v>
+        <v>0.2000899930397412</v>
       </c>
       <c r="AF21">
-        <v>0.13375</v>
+        <v>0.2081755814797488</v>
       </c>
       <c r="AG21">
-        <v>0.1440909090909091</v>
+        <v>0.2162611699197564</v>
       </c>
       <c r="AH21">
-        <v>0.1544318181818182</v>
+        <v>0.224346758359764</v>
       </c>
       <c r="AI21">
-        <v>0.1647727272727273</v>
+        <v>0.2324323467997716</v>
       </c>
       <c r="AJ21">
-        <v>0.1751136363636363</v>
+        <v>0.2405179352397792</v>
       </c>
       <c r="AK21">
-        <v>0.1854545454545455</v>
+        <v>0.2486035236797869</v>
       </c>
       <c r="AL21">
-        <v>0.1957954545454545</v>
+        <v>0.2566891121197944</v>
       </c>
       <c r="AM21">
-        <v>0.2061363636363636</v>
+        <v>0.2647747005598021</v>
       </c>
       <c r="AN21">
-        <v>0.2164772727272727</v>
+        <v>0.2728602889998097</v>
       </c>
       <c r="AO21">
-        <v>0.2268181818181818</v>
+        <v>0.2809458774398172</v>
       </c>
       <c r="AP21">
-        <v>0.2371590909090909</v>
+        <v>0.2890314658798249</v>
       </c>
       <c r="AQ21">
-        <v>0.2475</v>
+        <v>0.2971170543198325</v>
       </c>
       <c r="AR21">
-        <v>0.2578409090909091</v>
+        <v>0.3052026427598401</v>
       </c>
       <c r="AS21">
-        <v>0.2681818181818181</v>
+        <v>0.3132882311998477</v>
       </c>
       <c r="AT21">
-        <v>0.2785227272727273</v>
+        <v>0.3213738196398554</v>
       </c>
       <c r="AU21">
-        <v>0.2888636363636364</v>
+        <v>0.329459408079863</v>
       </c>
       <c r="AV21">
-        <v>0.2992045454545454</v>
+        <v>0.3375449965198706</v>
       </c>
       <c r="AW21">
-        <v>0.3095454545454545</v>
+        <v>0.3456305849598782</v>
       </c>
       <c r="AX21">
-        <v>0.3198863636363636</v>
+        <v>0.3537161733998858</v>
       </c>
       <c r="AY21">
-        <v>0.3302272727272726</v>
+        <v>0.3618017618398934</v>
       </c>
       <c r="AZ21">
-        <v>0.3405681818181818</v>
+        <v>0.3698873502799011</v>
       </c>
       <c r="BA21">
-        <v>0.3509090909090909</v>
+        <v>0.3779729387199087</v>
       </c>
       <c r="BB21">
-        <v>0.36125</v>
+        <v>0.3860585271599162</v>
       </c>
       <c r="BC21">
-        <v>0.371590909090909</v>
+        <v>0.3941441155999238</v>
       </c>
       <c r="BD21">
-        <v>0.3819318181818182</v>
+        <v>0.4022297040399315</v>
       </c>
       <c r="BE21">
-        <v>0.3922727272727273</v>
+        <v>0.4103152924799391</v>
       </c>
       <c r="BF21">
-        <v>0.4026136363636363</v>
+        <v>0.4184008809199467</v>
       </c>
       <c r="BG21">
-        <v>0.4129545454545455</v>
+        <v>0.4264864693599543</v>
       </c>
       <c r="BH21">
-        <v>0.4232954545454545</v>
+        <v>0.4345720577999619</v>
       </c>
       <c r="BI21">
-        <v>0.4336363636363636</v>
+        <v>0.4426576462399695</v>
       </c>
       <c r="BJ21">
-        <v>0.4439772727272727</v>
+        <v>0.4507432346799771</v>
       </c>
       <c r="BK21">
-        <v>0.4543181818181818</v>
+        <v>0.4588288231199848</v>
       </c>
       <c r="BL21">
-        <v>0.4646590909090909</v>
+        <v>0.4669144115599924</v>
       </c>
       <c r="BM21">
         <v>0.475</v>
@@ -60921,169 +60921,169 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U22">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V22">
-        <v>0.01651392290909091</v>
+        <v>0.06273110827958121</v>
       </c>
       <c r="W22">
-        <v>0.02717638981818182</v>
+        <v>0.07231875692424211</v>
       </c>
       <c r="X22">
-        <v>0.03783885672727272</v>
+        <v>0.08190640556890301</v>
       </c>
       <c r="Y22">
-        <v>0.04850132363636363</v>
+        <v>0.09149405421356391</v>
       </c>
       <c r="Z22">
-        <v>0.05916379054545454</v>
+        <v>0.1010817028582248</v>
       </c>
       <c r="AA22">
-        <v>0.06982625745454545</v>
+        <v>0.1106693515028857</v>
       </c>
       <c r="AB22">
-        <v>0.08048872436363635</v>
+        <v>0.1202570001475466</v>
       </c>
       <c r="AC22">
-        <v>0.09115119127272728</v>
+        <v>0.1298446487922075</v>
       </c>
       <c r="AD22">
-        <v>0.1018136581818182</v>
+        <v>0.1394322974368684</v>
       </c>
       <c r="AE22">
-        <v>0.1124761250909091</v>
+        <v>0.1490199460815293</v>
       </c>
       <c r="AF22">
-        <v>0.123138592</v>
+        <v>0.1586075947261902</v>
       </c>
       <c r="AG22">
-        <v>0.1338010589090909</v>
+        <v>0.1681952433708511</v>
       </c>
       <c r="AH22">
-        <v>0.1444635258181818</v>
+        <v>0.1777828920155121</v>
       </c>
       <c r="AI22">
-        <v>0.1551259927272727</v>
+        <v>0.1873705406601729</v>
       </c>
       <c r="AJ22">
-        <v>0.1657884596363636</v>
+        <v>0.1969581893048338</v>
       </c>
       <c r="AK22">
-        <v>0.1764509265454546</v>
+        <v>0.2065458379494947</v>
       </c>
       <c r="AL22">
-        <v>0.1871133934545454</v>
+        <v>0.2161334865941556</v>
       </c>
       <c r="AM22">
-        <v>0.1977758603636364</v>
+        <v>0.2257211352388166</v>
       </c>
       <c r="AN22">
-        <v>0.2084383272727273</v>
+        <v>0.2353087838834775</v>
       </c>
       <c r="AO22">
-        <v>0.2191007941818182</v>
+        <v>0.2448964325281383</v>
       </c>
       <c r="AP22">
-        <v>0.2297632610909091</v>
+        <v>0.2544840811727992</v>
       </c>
       <c r="AQ22">
-        <v>0.240425728</v>
+        <v>0.2640717298174601</v>
       </c>
       <c r="AR22">
-        <v>0.2510881949090909</v>
+        <v>0.273659378462121</v>
       </c>
       <c r="AS22">
-        <v>0.2617506618181817</v>
+        <v>0.2832470271067819</v>
       </c>
       <c r="AT22">
-        <v>0.2724131287272727</v>
+        <v>0.2928346757514428</v>
       </c>
       <c r="AU22">
-        <v>0.2830755956363636</v>
+        <v>0.3024223243961038</v>
       </c>
       <c r="AV22">
-        <v>0.2937380625454545</v>
+        <v>0.3120099730407646</v>
       </c>
       <c r="AW22">
-        <v>0.3044005294545454</v>
+        <v>0.3215976216854255</v>
       </c>
       <c r="AX22">
-        <v>0.3150629963636363</v>
+        <v>0.3311852703300864</v>
       </c>
       <c r="AY22">
-        <v>0.3257254632727272</v>
+        <v>0.3407729189747473</v>
       </c>
       <c r="AZ22">
-        <v>0.3363879301818182</v>
+        <v>0.3503605676194083</v>
       </c>
       <c r="BA22">
-        <v>0.3470503970909091</v>
+        <v>0.3599482162640692</v>
       </c>
       <c r="BB22">
-        <v>0.357712864</v>
+        <v>0.36953586490873</v>
       </c>
       <c r="BC22">
-        <v>0.3683753309090909</v>
+        <v>0.379123513553391</v>
       </c>
       <c r="BD22">
-        <v>0.3790377978181818</v>
+        <v>0.3887111621980519</v>
       </c>
       <c r="BE22">
-        <v>0.3897002647272728</v>
+        <v>0.3982988108427128</v>
       </c>
       <c r="BF22">
-        <v>0.4003627316363636</v>
+        <v>0.4078864594873737</v>
       </c>
       <c r="BG22">
-        <v>0.4110251985454546</v>
+        <v>0.4174741081320346</v>
       </c>
       <c r="BH22">
-        <v>0.4216876654545454</v>
+        <v>0.4270617567766955</v>
       </c>
       <c r="BI22">
-        <v>0.4323501323636363</v>
+        <v>0.4366494054213563</v>
       </c>
       <c r="BJ22">
-        <v>0.4430125992727272</v>
+        <v>0.4462370540660173</v>
       </c>
       <c r="BK22">
-        <v>0.4536750661818182</v>
+        <v>0.4558247027106782</v>
       </c>
       <c r="BL22">
-        <v>0.4643375330909091</v>
+        <v>0.4654123513553391</v>
       </c>
       <c r="BM22">
         <v>0.475</v>
@@ -61106,169 +61106,169 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U23">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V23">
-        <v>0.01651392290909091</v>
+        <v>0.06273110827958121</v>
       </c>
       <c r="W23">
-        <v>0.02717638981818182</v>
+        <v>0.07231875692424211</v>
       </c>
       <c r="X23">
-        <v>0.03783885672727272</v>
+        <v>0.08190640556890301</v>
       </c>
       <c r="Y23">
-        <v>0.04850132363636363</v>
+        <v>0.09149405421356391</v>
       </c>
       <c r="Z23">
-        <v>0.05916379054545454</v>
+        <v>0.1010817028582248</v>
       </c>
       <c r="AA23">
-        <v>0.06982625745454545</v>
+        <v>0.1106693515028857</v>
       </c>
       <c r="AB23">
-        <v>0.08048872436363635</v>
+        <v>0.1202570001475466</v>
       </c>
       <c r="AC23">
-        <v>0.09115119127272728</v>
+        <v>0.1298446487922075</v>
       </c>
       <c r="AD23">
-        <v>0.1018136581818182</v>
+        <v>0.1394322974368684</v>
       </c>
       <c r="AE23">
-        <v>0.1124761250909091</v>
+        <v>0.1490199460815293</v>
       </c>
       <c r="AF23">
-        <v>0.123138592</v>
+        <v>0.1586075947261902</v>
       </c>
       <c r="AG23">
-        <v>0.1338010589090909</v>
+        <v>0.1681952433708511</v>
       </c>
       <c r="AH23">
-        <v>0.1444635258181818</v>
+        <v>0.1777828920155121</v>
       </c>
       <c r="AI23">
-        <v>0.1551259927272727</v>
+        <v>0.1873705406601729</v>
       </c>
       <c r="AJ23">
-        <v>0.1657884596363636</v>
+        <v>0.1969581893048338</v>
       </c>
       <c r="AK23">
-        <v>0.1764509265454546</v>
+        <v>0.2065458379494947</v>
       </c>
       <c r="AL23">
-        <v>0.1871133934545454</v>
+        <v>0.2161334865941556</v>
       </c>
       <c r="AM23">
-        <v>0.1977758603636364</v>
+        <v>0.2257211352388166</v>
       </c>
       <c r="AN23">
-        <v>0.2084383272727273</v>
+        <v>0.2353087838834775</v>
       </c>
       <c r="AO23">
-        <v>0.2191007941818182</v>
+        <v>0.2448964325281383</v>
       </c>
       <c r="AP23">
-        <v>0.2297632610909091</v>
+        <v>0.2544840811727992</v>
       </c>
       <c r="AQ23">
-        <v>0.240425728</v>
+        <v>0.2640717298174601</v>
       </c>
       <c r="AR23">
-        <v>0.2510881949090909</v>
+        <v>0.273659378462121</v>
       </c>
       <c r="AS23">
-        <v>0.2617506618181817</v>
+        <v>0.2832470271067819</v>
       </c>
       <c r="AT23">
-        <v>0.2724131287272727</v>
+        <v>0.2928346757514428</v>
       </c>
       <c r="AU23">
-        <v>0.2830755956363636</v>
+        <v>0.3024223243961038</v>
       </c>
       <c r="AV23">
-        <v>0.2937380625454545</v>
+        <v>0.3120099730407646</v>
       </c>
       <c r="AW23">
-        <v>0.3044005294545454</v>
+        <v>0.3215976216854255</v>
       </c>
       <c r="AX23">
-        <v>0.3150629963636363</v>
+        <v>0.3311852703300864</v>
       </c>
       <c r="AY23">
-        <v>0.3257254632727272</v>
+        <v>0.3407729189747473</v>
       </c>
       <c r="AZ23">
-        <v>0.3363879301818182</v>
+        <v>0.3503605676194083</v>
       </c>
       <c r="BA23">
-        <v>0.3470503970909091</v>
+        <v>0.3599482162640692</v>
       </c>
       <c r="BB23">
-        <v>0.357712864</v>
+        <v>0.36953586490873</v>
       </c>
       <c r="BC23">
-        <v>0.3683753309090909</v>
+        <v>0.379123513553391</v>
       </c>
       <c r="BD23">
-        <v>0.3790377978181818</v>
+        <v>0.3887111621980519</v>
       </c>
       <c r="BE23">
-        <v>0.3897002647272728</v>
+        <v>0.3982988108427128</v>
       </c>
       <c r="BF23">
-        <v>0.4003627316363636</v>
+        <v>0.4078864594873737</v>
       </c>
       <c r="BG23">
-        <v>0.4110251985454546</v>
+        <v>0.4174741081320346</v>
       </c>
       <c r="BH23">
-        <v>0.4216876654545454</v>
+        <v>0.4270617567766955</v>
       </c>
       <c r="BI23">
-        <v>0.4323501323636363</v>
+        <v>0.4366494054213563</v>
       </c>
       <c r="BJ23">
-        <v>0.4430125992727272</v>
+        <v>0.4462370540660173</v>
       </c>
       <c r="BK23">
-        <v>0.4536750661818182</v>
+        <v>0.4558247027106782</v>
       </c>
       <c r="BL23">
-        <v>0.4643375330909091</v>
+        <v>0.4654123513553391</v>
       </c>
       <c r="BM23">
         <v>0.475</v>
@@ -61291,169 +61291,169 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="K24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="L24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="M24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="N24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="O24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="P24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="Q24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="R24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="S24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="T24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="U24">
-        <v>0.005851456</v>
+        <v>0.05314345963492031</v>
       </c>
       <c r="V24">
-        <v>0.01651392290909091</v>
+        <v>0.06273110827958121</v>
       </c>
       <c r="W24">
-        <v>0.02717638981818182</v>
+        <v>0.07231875692424211</v>
       </c>
       <c r="X24">
-        <v>0.03783885672727272</v>
+        <v>0.08190640556890301</v>
       </c>
       <c r="Y24">
-        <v>0.04850132363636363</v>
+        <v>0.09149405421356391</v>
       </c>
       <c r="Z24">
-        <v>0.05916379054545454</v>
+        <v>0.1010817028582248</v>
       </c>
       <c r="AA24">
-        <v>0.06982625745454545</v>
+        <v>0.1106693515028857</v>
       </c>
       <c r="AB24">
-        <v>0.08048872436363635</v>
+        <v>0.1202570001475466</v>
       </c>
       <c r="AC24">
-        <v>0.09115119127272728</v>
+        <v>0.1298446487922075</v>
       </c>
       <c r="AD24">
-        <v>0.1018136581818182</v>
+        <v>0.1394322974368684</v>
       </c>
       <c r="AE24">
-        <v>0.1124761250909091</v>
+        <v>0.1490199460815293</v>
       </c>
       <c r="AF24">
-        <v>0.123138592</v>
+        <v>0.1586075947261902</v>
       </c>
       <c r="AG24">
-        <v>0.1338010589090909</v>
+        <v>0.1681952433708511</v>
       </c>
       <c r="AH24">
-        <v>0.1444635258181818</v>
+        <v>0.1777828920155121</v>
       </c>
       <c r="AI24">
-        <v>0.1551259927272727</v>
+        <v>0.1873705406601729</v>
       </c>
       <c r="AJ24">
-        <v>0.1657884596363636</v>
+        <v>0.1969581893048338</v>
       </c>
       <c r="AK24">
-        <v>0.1764509265454546</v>
+        <v>0.2065458379494947</v>
       </c>
       <c r="AL24">
-        <v>0.1871133934545454</v>
+        <v>0.2161334865941556</v>
       </c>
       <c r="AM24">
-        <v>0.1977758603636364</v>
+        <v>0.2257211352388166</v>
       </c>
       <c r="AN24">
-        <v>0.2084383272727273</v>
+        <v>0.2353087838834775</v>
       </c>
       <c r="AO24">
-        <v>0.2191007941818182</v>
+        <v>0.2448964325281383</v>
       </c>
       <c r="AP24">
-        <v>0.2297632610909091</v>
+        <v>0.2544840811727992</v>
       </c>
       <c r="AQ24">
-        <v>0.240425728</v>
+        <v>0.2640717298174601</v>
       </c>
       <c r="AR24">
-        <v>0.2510881949090909</v>
+        <v>0.273659378462121</v>
       </c>
       <c r="AS24">
-        <v>0.2617506618181817</v>
+        <v>0.2832470271067819</v>
       </c>
       <c r="AT24">
-        <v>0.2724131287272727</v>
+        <v>0.2928346757514428</v>
       </c>
       <c r="AU24">
-        <v>0.2830755956363636</v>
+        <v>0.3024223243961038</v>
       </c>
       <c r="AV24">
-        <v>0.2937380625454545</v>
+        <v>0.3120099730407646</v>
       </c>
       <c r="AW24">
-        <v>0.3044005294545454</v>
+        <v>0.3215976216854255</v>
       </c>
       <c r="AX24">
-        <v>0.3150629963636363</v>
+        <v>0.3311852703300864</v>
       </c>
       <c r="AY24">
-        <v>0.3257254632727272</v>
+        <v>0.3407729189747473</v>
       </c>
       <c r="AZ24">
-        <v>0.3363879301818182</v>
+        <v>0.3503605676194083</v>
       </c>
       <c r="BA24">
-        <v>0.3470503970909091</v>
+        <v>0.3599482162640692</v>
       </c>
       <c r="BB24">
-        <v>0.357712864</v>
+        <v>0.36953586490873</v>
       </c>
       <c r="BC24">
-        <v>0.3683753309090909</v>
+        <v>0.379123513553391</v>
       </c>
       <c r="BD24">
-        <v>0.3790377978181818</v>
+        <v>0.3887111621980519</v>
       </c>
       <c r="BE24">
-        <v>0.3897002647272728</v>
+        <v>0.3982988108427128</v>
       </c>
       <c r="BF24">
-        <v>0.4003627316363636</v>
+        <v>0.4078864594873737</v>
       </c>
       <c r="BG24">
-        <v>0.4110251985454546</v>
+        <v>0.4174741081320346</v>
       </c>
       <c r="BH24">
-        <v>0.4216876654545454</v>
+        <v>0.4270617567766955</v>
       </c>
       <c r="BI24">
-        <v>0.4323501323636363</v>
+        <v>0.4366494054213563</v>
       </c>
       <c r="BJ24">
-        <v>0.4430125992727272</v>
+        <v>0.4462370540660173</v>
       </c>
       <c r="BK24">
-        <v>0.4536750661818182</v>
+        <v>0.4558247027106782</v>
       </c>
       <c r="BL24">
-        <v>0.4643375330909091</v>
+        <v>0.4654123513553391</v>
       </c>
       <c r="BM24">
         <v>0.475</v>
@@ -61661,172 +61661,172 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>0.3333370577799702</v>
       </c>
       <c r="V26">
-        <v>0.01945429886363636</v>
+        <v>0.3484483594513472</v>
       </c>
       <c r="W26">
-        <v>0.03890859772727272</v>
+        <v>0.3635596611227241</v>
       </c>
       <c r="X26">
-        <v>0.05836289659090908</v>
+        <v>0.378670962794101</v>
       </c>
       <c r="Y26">
-        <v>0.07781719545454545</v>
+        <v>0.3937822644654779</v>
       </c>
       <c r="Z26">
-        <v>0.09727149431818181</v>
+        <v>0.4088935661368547</v>
       </c>
       <c r="AA26">
-        <v>0.1167257931818182</v>
+        <v>0.4240048678082317</v>
       </c>
       <c r="AB26">
-        <v>0.1361800920454545</v>
+        <v>0.4391161694796086</v>
       </c>
       <c r="AC26">
-        <v>0.1556343909090909</v>
+        <v>0.4542274711509855</v>
       </c>
       <c r="AD26">
-        <v>0.1750886897727273</v>
+        <v>0.4693387728223624</v>
       </c>
       <c r="AE26">
-        <v>0.1945429886363636</v>
+        <v>0.4844500744937393</v>
       </c>
       <c r="AF26">
-        <v>0.2139972875</v>
+        <v>0.4995613761651162</v>
       </c>
       <c r="AG26">
-        <v>0.2334515863636363</v>
+        <v>0.5146726778364931</v>
       </c>
       <c r="AH26">
-        <v>0.2529058852272728</v>
+        <v>0.52978397950787</v>
       </c>
       <c r="AI26">
-        <v>0.2723601840909091</v>
+        <v>0.5448952811792469</v>
       </c>
       <c r="AJ26">
-        <v>0.2918144829545454</v>
+        <v>0.5600065828506238</v>
       </c>
       <c r="AK26">
-        <v>0.3112687818181818</v>
+        <v>0.5751178845220007</v>
       </c>
       <c r="AL26">
-        <v>0.3307230806818182</v>
+        <v>0.5902291861933776</v>
       </c>
       <c r="AM26">
-        <v>0.3501773795454546</v>
+        <v>0.6053404878647546</v>
       </c>
       <c r="AN26">
-        <v>0.3696316784090909</v>
+        <v>0.6204517895361314</v>
       </c>
       <c r="AO26">
-        <v>0.3890859772727273</v>
+        <v>0.6355630912075083</v>
       </c>
       <c r="AP26">
-        <v>0.4085402761363636</v>
+        <v>0.6506743928788852</v>
       </c>
       <c r="AQ26">
-        <v>0.427994575</v>
+        <v>0.6657856945502622</v>
       </c>
       <c r="AR26">
-        <v>0.4474488738636364</v>
+        <v>0.6808969962216391</v>
       </c>
       <c r="AS26">
-        <v>0.4669031727272727</v>
+        <v>0.6960082978930159</v>
       </c>
       <c r="AT26">
-        <v>0.4863574715909091</v>
+        <v>0.711119599564393</v>
       </c>
       <c r="AU26">
-        <v>0.5058117704545455</v>
+        <v>0.7262309012357698</v>
       </c>
       <c r="AV26">
-        <v>0.5252660693181818</v>
+        <v>0.7413422029071467</v>
       </c>
       <c r="AW26">
-        <v>0.5447203681818181</v>
+        <v>0.7564535045785237</v>
       </c>
       <c r="AX26">
-        <v>0.5641746670454545</v>
+        <v>0.7715648062499005</v>
       </c>
       <c r="AY26">
-        <v>0.5836289659090909</v>
+        <v>0.7866761079212773</v>
       </c>
       <c r="AZ26">
-        <v>0.6030832647727273</v>
+        <v>0.8017874095926544</v>
       </c>
       <c r="BA26">
-        <v>0.6225375636363636</v>
+        <v>0.8168987112640312</v>
       </c>
       <c r="BB26">
-        <v>0.6419918625</v>
+        <v>0.8320100129354081</v>
       </c>
       <c r="BC26">
-        <v>0.6614461613636363</v>
+        <v>0.8471213146067851</v>
       </c>
       <c r="BD26">
-        <v>0.6809004602272727</v>
+        <v>0.8622326162781619</v>
       </c>
       <c r="BE26">
-        <v>0.7003547590909092</v>
+        <v>0.8773439179495388</v>
       </c>
       <c r="BF26">
-        <v>0.7198090579545454</v>
+        <v>0.8924552196209158</v>
       </c>
       <c r="BG26">
-        <v>0.7392633568181818</v>
+        <v>0.9075665212922926</v>
       </c>
       <c r="BH26">
-        <v>0.7587176556818181</v>
+        <v>0.9226778229636695</v>
       </c>
       <c r="BI26">
-        <v>0.7781719545454545</v>
+        <v>0.9377891246350465</v>
       </c>
       <c r="BJ26">
-        <v>0.7976262534090909</v>
+        <v>0.9529004263064234</v>
       </c>
       <c r="BK26">
-        <v>0.8170805522727272</v>
+        <v>0.9680117279778002</v>
       </c>
       <c r="BL26">
-        <v>0.8365348511363636</v>
+        <v>0.9831230296491772</v>
       </c>
       <c r="BM26">
-        <v>0.85598915</v>
+        <v>0.9982343313205541</v>
       </c>
     </row>
     <row r="27" spans="1:65">
@@ -61846,169 +61846,169 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="K27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="L27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="M27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="N27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="O27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="P27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="Q27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="R27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="S27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="T27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="U27">
-        <v>0.85598915</v>
+        <v>0.6648972735405838</v>
       </c>
       <c r="V27">
-        <v>0.8365348511363636</v>
+        <v>0.6497859718692069</v>
       </c>
       <c r="W27">
-        <v>0.8170805522727272</v>
+        <v>0.6346746701978301</v>
       </c>
       <c r="X27">
-        <v>0.797626253409091</v>
+        <v>0.6195633685264531</v>
       </c>
       <c r="Y27">
-        <v>0.7781719545454545</v>
+        <v>0.6044520668550761</v>
       </c>
       <c r="Z27">
-        <v>0.7587176556818181</v>
+        <v>0.5893407651836993</v>
       </c>
       <c r="AA27">
-        <v>0.7392633568181818</v>
+        <v>0.5742294635123224</v>
       </c>
       <c r="AB27">
-        <v>0.7198090579545454</v>
+        <v>0.5591181618409455</v>
       </c>
       <c r="AC27">
-        <v>0.7003547590909091</v>
+        <v>0.5440068601695686</v>
       </c>
       <c r="AD27">
-        <v>0.6809004602272727</v>
+        <v>0.5288955584981916</v>
       </c>
       <c r="AE27">
-        <v>0.6614461613636363</v>
+        <v>0.5137842568268147</v>
       </c>
       <c r="AF27">
-        <v>0.6419918625</v>
+        <v>0.4986729551554379</v>
       </c>
       <c r="AG27">
-        <v>0.6225375636363636</v>
+        <v>0.483561653484061</v>
       </c>
       <c r="AH27">
-        <v>0.6030832647727273</v>
+        <v>0.4684503518126841</v>
       </c>
       <c r="AI27">
-        <v>0.583628965909091</v>
+        <v>0.4533390501413072</v>
       </c>
       <c r="AJ27">
-        <v>0.5641746670454546</v>
+        <v>0.4382277484699303</v>
       </c>
       <c r="AK27">
-        <v>0.5447203681818181</v>
+        <v>0.4231164467985533</v>
       </c>
       <c r="AL27">
-        <v>0.5252660693181818</v>
+        <v>0.4080051451271764</v>
       </c>
       <c r="AM27">
-        <v>0.5058117704545454</v>
+        <v>0.3928938434557995</v>
       </c>
       <c r="AN27">
-        <v>0.486357471590909</v>
+        <v>0.3777825417844226</v>
       </c>
       <c r="AO27">
-        <v>0.4669031727272727</v>
+        <v>0.3626712401130457</v>
       </c>
       <c r="AP27">
-        <v>0.4474488738636364</v>
+        <v>0.3475599384416688</v>
       </c>
       <c r="AQ27">
-        <v>0.427994575</v>
+        <v>0.3324486367702919</v>
       </c>
       <c r="AR27">
-        <v>0.4085402761363636</v>
+        <v>0.317337335098915</v>
       </c>
       <c r="AS27">
-        <v>0.3890859772727273</v>
+        <v>0.3022260334275381</v>
       </c>
       <c r="AT27">
-        <v>0.3696316784090908</v>
+        <v>0.2871147317561611</v>
       </c>
       <c r="AU27">
-        <v>0.3501773795454545</v>
+        <v>0.2720034300847843</v>
       </c>
       <c r="AV27">
-        <v>0.3307230806818182</v>
+        <v>0.2568921284134074</v>
       </c>
       <c r="AW27">
-        <v>0.3112687818181818</v>
+        <v>0.2417808267420305</v>
       </c>
       <c r="AX27">
-        <v>0.2918144829545455</v>
+        <v>0.2266695250706536</v>
       </c>
       <c r="AY27">
-        <v>0.2723601840909091</v>
+        <v>0.2115582233992767</v>
       </c>
       <c r="AZ27">
-        <v>0.2529058852272727</v>
+        <v>0.1964469217278997</v>
       </c>
       <c r="BA27">
-        <v>0.2334515863636363</v>
+        <v>0.1813356200565228</v>
       </c>
       <c r="BB27">
-        <v>0.2139972875</v>
+        <v>0.166224318385146</v>
       </c>
       <c r="BC27">
-        <v>0.1945429886363637</v>
+        <v>0.1511130167137691</v>
       </c>
       <c r="BD27">
-        <v>0.1750886897727273</v>
+        <v>0.1360017150423922</v>
       </c>
       <c r="BE27">
-        <v>0.1556343909090909</v>
+        <v>0.1208904133710152</v>
       </c>
       <c r="BF27">
-        <v>0.1361800920454545</v>
+        <v>0.1057791116996383</v>
       </c>
       <c r="BG27">
-        <v>0.1167257931818182</v>
+        <v>0.09066781002826142</v>
       </c>
       <c r="BH27">
-        <v>0.09727149431818183</v>
+        <v>0.07555650835688453</v>
       </c>
       <c r="BI27">
-        <v>0.07781719545454548</v>
+        <v>0.06044520668550764</v>
       </c>
       <c r="BJ27">
-        <v>0.05836289659090913</v>
+        <v>0.04533390501413075</v>
       </c>
       <c r="BK27">
-        <v>0.03890859772727269</v>
+        <v>0.03022260334275378</v>
       </c>
       <c r="BL27">
-        <v>0.01945429886363634</v>
+        <v>0.01511130167137689</v>
       </c>
       <c r="BM27">
         <v>0</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ce_calibrated.xlsx
@@ -2555,7 +2555,7 @@
         <v>74</v>
       </c>
       <c r="C8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         <v>75</v>
       </c>
       <c r="C9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         <v>79</v>
       </c>
       <c r="C13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -3656,7 +3656,7 @@
         <v>80</v>
       </c>
       <c r="C14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -4023,7 +4023,7 @@
         <v>82</v>
       </c>
       <c r="C16">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>83</v>
       </c>
       <c r="C17">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -4393,7 +4393,7 @@
         <v>84</v>
       </c>
       <c r="C18">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -4578,7 +4578,7 @@
         <v>85</v>
       </c>
       <c r="C19">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -4945,7 +4945,7 @@
         <v>87</v>
       </c>
       <c r="C21">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         <v>88</v>
       </c>
       <c r="C22">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -5497,7 +5497,7 @@
         <v>90</v>
       </c>
       <c r="C24">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -6046,7 +6046,7 @@
         <v>93</v>
       </c>
       <c r="C27">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -6777,7 +6777,7 @@
         <v>97</v>
       </c>
       <c r="C31">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -6962,7 +6962,7 @@
         <v>98</v>
       </c>
       <c r="C32">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -7329,7 +7329,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -7514,7 +7514,7 @@
         <v>101</v>
       </c>
       <c r="C35">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -17163,7 +17163,7 @@
         <v>154</v>
       </c>
       <c r="C88">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -19350,7 +19350,7 @@
         <v>166</v>
       </c>
       <c r="C100">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -19535,7 +19535,7 @@
         <v>167</v>
       </c>
       <c r="C101">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -19720,7 +19720,7 @@
         <v>168</v>
       </c>
       <c r="C102">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -19905,7 +19905,7 @@
         <v>169</v>
       </c>
       <c r="C103">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -20272,7 +20272,7 @@
         <v>171</v>
       </c>
       <c r="C105">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -20457,7 +20457,7 @@
         <v>172</v>
       </c>
       <c r="C106">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -25374,7 +25374,7 @@
         <v>199</v>
       </c>
       <c r="C133">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -25559,7 +25559,7 @@
         <v>200</v>
       </c>
       <c r="C134">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -25744,7 +25744,7 @@
         <v>201</v>
       </c>
       <c r="C135">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -25929,7 +25929,7 @@
         <v>202</v>
       </c>
       <c r="C136">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -26296,7 +26296,7 @@
         <v>204</v>
       </c>
       <c r="C138">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -26481,7 +26481,7 @@
         <v>205</v>
       </c>
       <c r="C139">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -26666,7 +26666,7 @@
         <v>206</v>
       </c>
       <c r="C140">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -26851,7 +26851,7 @@
         <v>207</v>
       </c>
       <c r="C141">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -27036,7 +27036,7 @@
         <v>208</v>
       </c>
       <c r="C142">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -27221,7 +27221,7 @@
         <v>209</v>
       </c>
       <c r="C143">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -27406,7 +27406,7 @@
         <v>210</v>
       </c>
       <c r="C144">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -27591,7 +27591,7 @@
         <v>211</v>
       </c>
       <c r="C145">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>212</v>
       </c>
       <c r="C146">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -33967,7 +33967,7 @@
         <v>246</v>
       </c>
       <c r="C180">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -39612,7 +39612,7 @@
         <v>277</v>
       </c>
       <c r="C211">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -39797,7 +39797,7 @@
         <v>278</v>
       </c>
       <c r="C212">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -39982,7 +39982,7 @@
         <v>279</v>
       </c>
       <c r="C213">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -40167,7 +40167,7 @@
         <v>280</v>
       </c>
       <c r="C214">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -42743,7 +42743,7 @@
         <v>74</v>
       </c>
       <c r="C2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -42928,7 +42928,7 @@
         <v>75</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -43113,7 +43113,7 @@
         <v>79</v>
       </c>
       <c r="C4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -43298,7 +43298,7 @@
         <v>80</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -43483,7 +43483,7 @@
         <v>82</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -43668,7 +43668,7 @@
         <v>83</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -43853,7 +43853,7 @@
         <v>84</v>
       </c>
       <c r="C8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -44038,7 +44038,7 @@
         <v>85</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -44223,7 +44223,7 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -44408,7 +44408,7 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -44593,7 +44593,7 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -44778,7 +44778,7 @@
         <v>93</v>
       </c>
       <c r="C13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -44963,7 +44963,7 @@
         <v>97</v>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -45148,7 +45148,7 @@
         <v>98</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -45333,7 +45333,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -45518,7 +45518,7 @@
         <v>101</v>
       </c>
       <c r="C17">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -45703,7 +45703,7 @@
         <v>154</v>
       </c>
       <c r="C18">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -45888,7 +45888,7 @@
         <v>166</v>
       </c>
       <c r="C19">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -46073,7 +46073,7 @@
         <v>167</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -46258,7 +46258,7 @@
         <v>168</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -46443,7 +46443,7 @@
         <v>169</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -46628,7 +46628,7 @@
         <v>171</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -46813,7 +46813,7 @@
         <v>172</v>
       </c>
       <c r="C24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -46998,7 +46998,7 @@
         <v>199</v>
       </c>
       <c r="C25">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -47183,7 +47183,7 @@
         <v>200</v>
       </c>
       <c r="C26">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -47368,7 +47368,7 @@
         <v>201</v>
       </c>
       <c r="C27">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -47553,7 +47553,7 @@
         <v>202</v>
       </c>
       <c r="C28">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -47738,7 +47738,7 @@
         <v>204</v>
       </c>
       <c r="C29">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -47923,7 +47923,7 @@
         <v>205</v>
       </c>
       <c r="C30">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -48108,7 +48108,7 @@
         <v>206</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -48293,7 +48293,7 @@
         <v>207</v>
       </c>
       <c r="C32">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -48478,7 +48478,7 @@
         <v>208</v>
       </c>
       <c r="C33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -48663,7 +48663,7 @@
         <v>209</v>
       </c>
       <c r="C34">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -48848,7 +48848,7 @@
         <v>210</v>
       </c>
       <c r="C35">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -49033,7 +49033,7 @@
         <v>211</v>
       </c>
       <c r="C36">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -49218,7 +49218,7 @@
         <v>212</v>
       </c>
       <c r="C37">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -49585,7 +49585,7 @@
         <v>246</v>
       </c>
       <c r="C39">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -49770,7 +49770,7 @@
         <v>277</v>
       </c>
       <c r="C40">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -49955,7 +49955,7 @@
         <v>278</v>
       </c>
       <c r="C41">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -50140,7 +50140,7 @@
         <v>279</v>
       </c>
       <c r="C42">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -50325,7 +50325,7 @@
         <v>280</v>
       </c>
       <c r="C43">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -50717,7 +50717,7 @@
         <v>74</v>
       </c>
       <c r="C2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -50902,7 +50902,7 @@
         <v>75</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -51087,7 +51087,7 @@
         <v>79</v>
       </c>
       <c r="C4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -51272,7 +51272,7 @@
         <v>80</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -51457,7 +51457,7 @@
         <v>82</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -51642,7 +51642,7 @@
         <v>83</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -51827,7 +51827,7 @@
         <v>84</v>
       </c>
       <c r="C8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -52012,7 +52012,7 @@
         <v>85</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -52197,7 +52197,7 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -52382,7 +52382,7 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -52567,7 +52567,7 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -52752,7 +52752,7 @@
         <v>93</v>
       </c>
       <c r="C13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -52937,7 +52937,7 @@
         <v>97</v>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -53122,7 +53122,7 @@
         <v>98</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -53307,7 +53307,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -53492,7 +53492,7 @@
         <v>101</v>
       </c>
       <c r="C17">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -53677,7 +53677,7 @@
         <v>154</v>
       </c>
       <c r="C18">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -53862,7 +53862,7 @@
         <v>166</v>
       </c>
       <c r="C19">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -54047,7 +54047,7 @@
         <v>167</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -54232,7 +54232,7 @@
         <v>168</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -54417,7 +54417,7 @@
         <v>169</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -54602,7 +54602,7 @@
         <v>171</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -54787,7 +54787,7 @@
         <v>172</v>
       </c>
       <c r="C24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -54972,7 +54972,7 @@
         <v>200</v>
       </c>
       <c r="C25">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -55157,7 +55157,7 @@
         <v>204</v>
       </c>
       <c r="C26">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -55342,7 +55342,7 @@
         <v>205</v>
       </c>
       <c r="C27">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -55527,7 +55527,7 @@
         <v>206</v>
       </c>
       <c r="C28">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -55712,7 +55712,7 @@
         <v>207</v>
       </c>
       <c r="C29">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -55897,7 +55897,7 @@
         <v>208</v>
       </c>
       <c r="C30">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -56082,7 +56082,7 @@
         <v>209</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -56267,7 +56267,7 @@
         <v>210</v>
       </c>
       <c r="C32">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -56452,7 +56452,7 @@
         <v>211</v>
       </c>
       <c r="C33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -56637,7 +56637,7 @@
         <v>212</v>
       </c>
       <c r="C34">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -56822,7 +56822,7 @@
         <v>246</v>
       </c>
       <c r="C35">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -57214,7 +57214,7 @@
         <v>74</v>
       </c>
       <c r="C2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -57399,7 +57399,7 @@
         <v>75</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -57584,7 +57584,7 @@
         <v>79</v>
       </c>
       <c r="C4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -57769,7 +57769,7 @@
         <v>80</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -57954,7 +57954,7 @@
         <v>82</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -58139,7 +58139,7 @@
         <v>83</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -58324,7 +58324,7 @@
         <v>84</v>
       </c>
       <c r="C8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -58509,7 +58509,7 @@
         <v>85</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -58694,7 +58694,7 @@
         <v>87</v>
       </c>
       <c r="C10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -58879,7 +58879,7 @@
         <v>88</v>
       </c>
       <c r="C11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -59064,7 +59064,7 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -59249,7 +59249,7 @@
         <v>93</v>
       </c>
       <c r="C13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -59434,7 +59434,7 @@
         <v>97</v>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -59619,7 +59619,7 @@
         <v>98</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -59804,7 +59804,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -59989,7 +59989,7 @@
         <v>101</v>
       </c>
       <c r="C17">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -60174,7 +60174,7 @@
         <v>154</v>
       </c>
       <c r="C18">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -60359,7 +60359,7 @@
         <v>166</v>
       </c>
       <c r="C19">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -60544,7 +60544,7 @@
         <v>167</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -60729,7 +60729,7 @@
         <v>168</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -60914,7 +60914,7 @@
         <v>169</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -61099,7 +61099,7 @@
         <v>171</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -61284,7 +61284,7 @@
         <v>172</v>
       </c>
       <c r="C24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -61469,7 +61469,7 @@
         <v>200</v>
       </c>
       <c r="C25">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -61654,7 +61654,7 @@
         <v>204</v>
       </c>
       <c r="C26">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -61839,7 +61839,7 @@
         <v>205</v>
       </c>
       <c r="C27">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -62024,7 +62024,7 @@
         <v>206</v>
       </c>
       <c r="C28">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -62209,7 +62209,7 @@
         <v>207</v>
       </c>
       <c r="C29">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -62394,7 +62394,7 @@
         <v>208</v>
       </c>
       <c r="C30">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -62579,7 +62579,7 @@
         <v>209</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -62764,7 +62764,7 @@
         <v>210</v>
       </c>
       <c r="C32">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -62949,7 +62949,7 @@
         <v>211</v>
       </c>
       <c r="C33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -63134,7 +63134,7 @@
         <v>212</v>
       </c>
       <c r="C34">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -63501,7 +63501,7 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -63893,7 +63893,7 @@
         <v>166</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -64078,7 +64078,7 @@
         <v>167</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -64263,7 +64263,7 @@
         <v>168</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -64448,7 +64448,7 @@
         <v>169</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -64633,7 +64633,7 @@
         <v>171</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -64818,7 +64818,7 @@
         <v>172</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -65003,7 +65003,7 @@
         <v>200</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -65188,7 +65188,7 @@
         <v>204</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -65373,7 +65373,7 @@
         <v>205</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -65947,7 +65947,7 @@
         <v>166</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -66132,7 +66132,7 @@
         <v>167</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -66317,7 +66317,7 @@
         <v>168</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -66502,7 +66502,7 @@
         <v>169</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -66687,7 +66687,7 @@
         <v>171</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -66872,7 +66872,7 @@
         <v>172</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -67057,7 +67057,7 @@
         <v>200</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -67242,7 +67242,7 @@
         <v>204</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -67427,7 +67427,7 @@
         <v>205</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10">
         <v>1</v>
